--- a/avito-feed-main/fleet-main.xlsx
+++ b/avito-feed-main/fleet-main.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW42"/>
+  <dimension ref="A1:AL38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,170 +495,115 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>BodyType</t>
+          <t>Brakes</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Brakes</t>
+          <t>CompanyName</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CabinSuspension</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CabinType</t>
+          <t>CurrencyPrice</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CompanyName</t>
+          <t>DeliveryType</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>DisplayAreas</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CurrencyPrice</t>
+          <t>GrossVehicleWeight</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>DeliveryType</t>
+          <t>Make</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>DisplayAreas</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>EmissionClass</t>
+          <t>OfficialGuarantee</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>EngineCapacity</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>EngineType</t>
+          <t>PriceWithVAT</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>GrossVehicleWeight</t>
+          <t>SuspensionChassis</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Make</t>
+          <t>TechnicalPassport</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>TrailerLength</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>TrailerVolume</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>OfficialGuarantee</t>
+          <t>TypeOfTrailer</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>TypeOfVehicle</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>PriceWithVAT</t>
+          <t>LeasingDiscount</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>RearSuspension</t>
+          <t>DealerDiscount</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>SuspensionChassis</t>
+          <t>AdditionalGuarantee</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>TechnicalPassport</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>TrailerLength</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>TrailerVolume</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>Transmission</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>TypeOfTrailer</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>TypeOfVehicle</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>WheelFormula</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>LeasingDiscount</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>DealerDiscount</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>AdditionalGuarantee</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
@@ -768,120 +713,109 @@
           <t>3</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr"/>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>Барабанные</t>
+        </is>
+      </c>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+          <t>ООО БелКар</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>3150000</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr">
         <is>
-          <t>ООО БелКар</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="U2" s="1" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V2" s="1" t="inlineStr">
         <is>
-          <t>3150000</t>
+          <t>31800</t>
         </is>
       </c>
       <c r="W2" s="1" t="inlineStr">
         <is>
+          <t>Тонар</t>
+        </is>
+      </c>
+      <c r="X2" s="1" t="inlineStr">
+        <is>
+          <t>B3-13 (9888)</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
+          <t>3 года или больше</t>
+        </is>
+      </c>
+      <c r="Z2" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
+      <c r="AA2" s="1" t="inlineStr">
+        <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
-        <is>
-          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
-        </is>
-      </c>
-      <c r="Y2" s="1" t="inlineStr"/>
-      <c r="Z2" s="1" t="inlineStr"/>
-      <c r="AA2" s="1" t="inlineStr"/>
       <c r="AB2" s="1" t="inlineStr">
         <is>
-          <t>31800</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AC2" s="1" t="inlineStr">
         <is>
-          <t>Тонар</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AD2" s="1" t="inlineStr">
         <is>
-          <t>B3-13 (9888)</t>
+          <t>13625</t>
         </is>
       </c>
       <c r="AE2" s="1" t="inlineStr"/>
       <c r="AF2" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Бортовой</t>
         </is>
       </c>
       <c r="AG2" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="AH2" s="1" t="inlineStr"/>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AH2" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="AI2" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="AJ2" s="1" t="inlineStr"/>
-      <c r="AK2" s="1" t="inlineStr">
-        <is>
-          <t>Пневматическая</t>
-        </is>
-      </c>
+          <t>315000</t>
+        </is>
+      </c>
+      <c r="AJ2" s="1" t="inlineStr">
+        <is>
+          <t>315000</t>
+        </is>
+      </c>
+      <c r="AK2" s="1" t="inlineStr"/>
       <c r="AL2" s="1" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AM2" s="1" t="inlineStr">
-        <is>
-          <t>13625</t>
-        </is>
-      </c>
-      <c r="AN2" s="1" t="inlineStr"/>
-      <c r="AO2" s="1" t="inlineStr"/>
-      <c r="AP2" s="1" t="inlineStr">
-        <is>
-          <t>Бортовой</t>
-        </is>
-      </c>
-      <c r="AQ2" s="1" t="inlineStr">
-        <is>
-          <t>Полуприцеп</t>
-        </is>
-      </c>
-      <c r="AR2" s="1" t="inlineStr"/>
-      <c r="AS2" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AT2" s="1" t="inlineStr">
-        <is>
-          <t>315000</t>
-        </is>
-      </c>
-      <c r="AU2" s="1" t="inlineStr">
-        <is>
-          <t>315000</t>
-        </is>
-      </c>
-      <c r="AV2" s="1" t="inlineStr"/>
-      <c r="AW2" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-b3-13-9888</t>
         </is>
@@ -1002,120 +936,109 @@
           <t>4</t>
         </is>
       </c>
-      <c r="P3" s="1" t="inlineStr"/>
+      <c r="P3" s="1" t="inlineStr">
+        <is>
+          <t>Барабанные</t>
+        </is>
+      </c>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
-        </is>
-      </c>
-      <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+          <t>ООО БелКар</t>
+        </is>
+      </c>
+      <c r="R3" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>5700000</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr">
         <is>
-          <t>ООО БелКар</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="U3" s="1" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V3" s="1" t="inlineStr">
         <is>
-          <t>5700000</t>
+          <t>35050</t>
         </is>
       </c>
       <c r="W3" s="1" t="inlineStr">
         <is>
+          <t>Тонар</t>
+        </is>
+      </c>
+      <c r="X3" s="1" t="inlineStr">
+        <is>
+          <t>9599</t>
+        </is>
+      </c>
+      <c r="Y3" s="1" t="inlineStr">
+        <is>
+          <t>3 года или больше</t>
+        </is>
+      </c>
+      <c r="Z3" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
+      <c r="AA3" s="1" t="inlineStr">
+        <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X3" s="1" t="inlineStr">
-        <is>
-          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
-        </is>
-      </c>
-      <c r="Y3" s="1" t="inlineStr"/>
-      <c r="Z3" s="1" t="inlineStr"/>
-      <c r="AA3" s="1" t="inlineStr"/>
       <c r="AB3" s="1" t="inlineStr">
         <is>
-          <t>35050</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AC3" s="1" t="inlineStr">
         <is>
-          <t>Тонар</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AD3" s="1" t="inlineStr">
         <is>
-          <t>9599</t>
-        </is>
-      </c>
-      <c r="AE3" s="1" t="inlineStr"/>
+          <t>12190</t>
+        </is>
+      </c>
+      <c r="AE3" s="1" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="AF3" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Зерновоз</t>
         </is>
       </c>
       <c r="AG3" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="AH3" s="1" t="inlineStr"/>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AH3" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="AI3" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="AJ3" s="1" t="inlineStr"/>
-      <c r="AK3" s="1" t="inlineStr">
-        <is>
-          <t>Пневматическая</t>
-        </is>
-      </c>
+      <c r="AK3" s="1" t="inlineStr"/>
       <c r="AL3" s="1" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AM3" s="1" t="inlineStr">
-        <is>
-          <t>12190</t>
-        </is>
-      </c>
-      <c r="AN3" s="1" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="AO3" s="1" t="inlineStr"/>
-      <c r="AP3" s="1" t="inlineStr">
-        <is>
-          <t>Зерновоз</t>
-        </is>
-      </c>
-      <c r="AQ3" s="1" t="inlineStr">
-        <is>
-          <t>Полуприцеп</t>
-        </is>
-      </c>
-      <c r="AR3" s="1" t="inlineStr"/>
-      <c r="AS3" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AT3" s="1" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
-      </c>
-      <c r="AU3" s="1" t="inlineStr"/>
-      <c r="AV3" s="1" t="inlineStr"/>
-      <c r="AW3" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-9599</t>
         </is>
@@ -1240,120 +1163,109 @@
           <t>3</t>
         </is>
       </c>
-      <c r="P4" s="1" t="inlineStr"/>
+      <c r="P4" s="1" t="inlineStr">
+        <is>
+          <t>Дисковые</t>
+        </is>
+      </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
-        </is>
-      </c>
-      <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+          <t>ООО БелКар</t>
+        </is>
+      </c>
+      <c r="R4" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>4850000</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr">
         <is>
-          <t>ООО БелКар</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="U4" s="1" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V4" s="1" t="inlineStr">
         <is>
-          <t>4850000</t>
+          <t>38080</t>
         </is>
       </c>
       <c r="W4" s="1" t="inlineStr">
         <is>
+          <t>Тонар</t>
+        </is>
+      </c>
+      <c r="X4" s="1" t="inlineStr">
+        <is>
+          <t>R3-13</t>
+        </is>
+      </c>
+      <c r="Y4" s="1" t="inlineStr">
+        <is>
+          <t>3 года или больше</t>
+        </is>
+      </c>
+      <c r="Z4" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
+      <c r="AA4" s="1" t="inlineStr">
+        <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X4" s="1" t="inlineStr">
-        <is>
-          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
-        </is>
-      </c>
-      <c r="Y4" s="1" t="inlineStr"/>
-      <c r="Z4" s="1" t="inlineStr"/>
-      <c r="AA4" s="1" t="inlineStr"/>
       <c r="AB4" s="1" t="inlineStr">
         <is>
-          <t>38080</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AC4" s="1" t="inlineStr">
         <is>
-          <t>Тонар</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AD4" s="1" t="inlineStr">
         <is>
-          <t>R3-13</t>
-        </is>
-      </c>
-      <c r="AE4" s="1" t="inlineStr"/>
+          <t>13500</t>
+        </is>
+      </c>
+      <c r="AE4" s="1" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="AF4" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Изотермический</t>
         </is>
       </c>
       <c r="AG4" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="AH4" s="1" t="inlineStr"/>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AH4" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="AI4" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>485000</t>
         </is>
       </c>
       <c r="AJ4" s="1" t="inlineStr"/>
-      <c r="AK4" s="1" t="inlineStr">
-        <is>
-          <t>Пневматическая</t>
-        </is>
-      </c>
+      <c r="AK4" s="1" t="inlineStr"/>
       <c r="AL4" s="1" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AM4" s="1" t="inlineStr">
-        <is>
-          <t>13500</t>
-        </is>
-      </c>
-      <c r="AN4" s="1" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="AO4" s="1" t="inlineStr"/>
-      <c r="AP4" s="1" t="inlineStr">
-        <is>
-          <t>Изотермический</t>
-        </is>
-      </c>
-      <c r="AQ4" s="1" t="inlineStr">
-        <is>
-          <t>Полуприцеп</t>
-        </is>
-      </c>
-      <c r="AR4" s="1" t="inlineStr"/>
-      <c r="AS4" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AT4" s="1" t="inlineStr">
-        <is>
-          <t>485000</t>
-        </is>
-      </c>
-      <c r="AU4" s="1" t="inlineStr"/>
-      <c r="AV4" s="1" t="inlineStr"/>
-      <c r="AW4" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-r3-13</t>
         </is>
@@ -1480,124 +1392,113 @@
           <t>3</t>
         </is>
       </c>
-      <c r="P5" s="1" t="inlineStr"/>
+      <c r="P5" s="1" t="inlineStr">
+        <is>
+          <t>Дисковые</t>
+        </is>
+      </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
-        </is>
-      </c>
-      <c r="R5" s="1" t="inlineStr"/>
-      <c r="S5" s="1" t="inlineStr"/>
+          <t>ООО БелКар</t>
+        </is>
+      </c>
+      <c r="R5" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>4150000</t>
+        </is>
+      </c>
       <c r="T5" s="1" t="inlineStr">
         <is>
-          <t>ООО БелКар</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="U5" s="1" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V5" s="1" t="inlineStr">
         <is>
-          <t>4150000</t>
+          <t>30300</t>
         </is>
       </c>
       <c r="W5" s="1" t="inlineStr">
         <is>
+          <t>Тонар</t>
+        </is>
+      </c>
+      <c r="X5" s="1" t="inlineStr">
+        <is>
+          <t>T3-16 (98881)</t>
+        </is>
+      </c>
+      <c r="Y5" s="1" t="inlineStr">
+        <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X5" s="1" t="inlineStr">
-        <is>
-          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
-        </is>
-      </c>
-      <c r="Y5" s="1" t="inlineStr"/>
-      <c r="Z5" s="1" t="inlineStr"/>
-      <c r="AA5" s="1" t="inlineStr"/>
+      <c r="Z5" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
+      <c r="AA5" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="AB5" s="1" t="inlineStr">
         <is>
-          <t>30300</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AC5" s="1" t="inlineStr">
         <is>
-          <t>Тонар</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AD5" s="1" t="inlineStr">
         <is>
-          <t>T3-16 (98881)</t>
-        </is>
-      </c>
-      <c r="AE5" s="1" t="inlineStr"/>
+          <t>16500</t>
+        </is>
+      </c>
+      <c r="AE5" s="1" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
       <c r="AF5" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Шторно-бортовой</t>
         </is>
       </c>
       <c r="AG5" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="AH5" s="1" t="inlineStr"/>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AH5" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="AI5" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="AJ5" s="1" t="inlineStr"/>
-      <c r="AK5" s="1" t="inlineStr">
-        <is>
-          <t>Пневматическая</t>
-        </is>
-      </c>
+          <t>415000</t>
+        </is>
+      </c>
+      <c r="AJ5" s="1" t="inlineStr">
+        <is>
+          <t>415000</t>
+        </is>
+      </c>
+      <c r="AK5" s="1" t="inlineStr"/>
       <c r="AL5" s="1" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AM5" s="1" t="inlineStr">
-        <is>
-          <t>16500</t>
-        </is>
-      </c>
-      <c r="AN5" s="1" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AO5" s="1" t="inlineStr"/>
-      <c r="AP5" s="1" t="inlineStr">
-        <is>
-          <t>Шторно-бортовой</t>
-        </is>
-      </c>
-      <c r="AQ5" s="1" t="inlineStr">
-        <is>
-          <t>Полуприцеп</t>
-        </is>
-      </c>
-      <c r="AR5" s="1" t="inlineStr"/>
-      <c r="AS5" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AT5" s="1" t="inlineStr">
-        <is>
-          <t>415000</t>
-        </is>
-      </c>
-      <c r="AU5" s="1" t="inlineStr">
-        <is>
-          <t>415000</t>
-        </is>
-      </c>
-      <c r="AV5" s="1" t="inlineStr"/>
-      <c r="AW5" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-t3-16-98881</t>
         </is>
@@ -1717,124 +1618,113 @@
           <t>3</t>
         </is>
       </c>
-      <c r="P6" s="1" t="inlineStr"/>
+      <c r="P6" s="1" t="inlineStr">
+        <is>
+          <t>Барабанные</t>
+        </is>
+      </c>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
-        </is>
-      </c>
-      <c r="R6" s="1" t="inlineStr"/>
-      <c r="S6" s="1" t="inlineStr"/>
+          <t>ООО БелКар</t>
+        </is>
+      </c>
+      <c r="R6" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="S6" s="1" t="inlineStr">
+        <is>
+          <t>3200000</t>
+        </is>
+      </c>
       <c r="T6" s="1" t="inlineStr">
         <is>
-          <t>ООО БелКар</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="U6" s="1" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V6" s="1" t="inlineStr">
         <is>
-          <t>3200000</t>
+          <t>43000</t>
         </is>
       </c>
       <c r="W6" s="1" t="inlineStr">
         <is>
+          <t>Тонар</t>
+        </is>
+      </c>
+      <c r="X6" s="1" t="inlineStr">
+        <is>
+          <t>L3 (9445)</t>
+        </is>
+      </c>
+      <c r="Y6" s="1" t="inlineStr">
+        <is>
+          <t>3 года или больше</t>
+        </is>
+      </c>
+      <c r="Z6" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
+      <c r="AA6" s="1" t="inlineStr">
+        <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X6" s="1" t="inlineStr">
-        <is>
-          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
-        </is>
-      </c>
-      <c r="Y6" s="1" t="inlineStr"/>
-      <c r="Z6" s="1" t="inlineStr"/>
-      <c r="AA6" s="1" t="inlineStr"/>
       <c r="AB6" s="1" t="inlineStr">
         <is>
-          <t>43000</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AC6" s="1" t="inlineStr">
         <is>
-          <t>Тонар</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AD6" s="1" t="inlineStr">
         <is>
-          <t>L3 (9445)</t>
-        </is>
-      </c>
-      <c r="AE6" s="1" t="inlineStr"/>
+          <t>12800</t>
+        </is>
+      </c>
+      <c r="AE6" s="1" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="AF6" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Лесовоз (сортиментовоз)</t>
         </is>
       </c>
       <c r="AG6" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="AH6" s="1" t="inlineStr"/>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AH6" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="AI6" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="AJ6" s="1" t="inlineStr"/>
-      <c r="AK6" s="1" t="inlineStr">
-        <is>
-          <t>Пневматическая</t>
-        </is>
-      </c>
+          <t>320000</t>
+        </is>
+      </c>
+      <c r="AJ6" s="1" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="AK6" s="1" t="inlineStr"/>
       <c r="AL6" s="1" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AM6" s="1" t="inlineStr">
-        <is>
-          <t>12800</t>
-        </is>
-      </c>
-      <c r="AN6" s="1" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="AO6" s="1" t="inlineStr"/>
-      <c r="AP6" s="1" t="inlineStr">
-        <is>
-          <t>Лесовоз (сортиментовоз)</t>
-        </is>
-      </c>
-      <c r="AQ6" s="1" t="inlineStr">
-        <is>
-          <t>Полуприцеп</t>
-        </is>
-      </c>
-      <c r="AR6" s="1" t="inlineStr"/>
-      <c r="AS6" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AT6" s="1" t="inlineStr">
-        <is>
-          <t>320000</t>
-        </is>
-      </c>
-      <c r="AU6" s="1" t="inlineStr">
-        <is>
-          <t>160000</t>
-        </is>
-      </c>
-      <c r="AV6" s="1" t="inlineStr"/>
-      <c r="AW6" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-l3-9445</t>
         </is>
@@ -1946,124 +1836,113 @@
           <t>4</t>
         </is>
       </c>
-      <c r="P7" s="1" t="inlineStr"/>
+      <c r="P7" s="1" t="inlineStr">
+        <is>
+          <t>Дисковые</t>
+        </is>
+      </c>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
-        </is>
-      </c>
-      <c r="R7" s="1" t="inlineStr"/>
-      <c r="S7" s="1" t="inlineStr"/>
+          <t>ООО БелКар</t>
+        </is>
+      </c>
+      <c r="R7" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="S7" s="1" t="inlineStr">
+        <is>
+          <t>4750000</t>
+        </is>
+      </c>
       <c r="T7" s="1" t="inlineStr">
         <is>
-          <t>ООО БелКар</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="U7" s="1" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V7" s="1" t="inlineStr">
         <is>
-          <t>4750000</t>
+          <t>27000</t>
         </is>
       </c>
       <c r="W7" s="1" t="inlineStr">
         <is>
+          <t>Тонар</t>
+        </is>
+      </c>
+      <c r="X7" s="1" t="inlineStr">
+        <is>
+          <t>T4-16V</t>
+        </is>
+      </c>
+      <c r="Y7" s="1" t="inlineStr">
+        <is>
+          <t>3 года или больше</t>
+        </is>
+      </c>
+      <c r="Z7" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
+      <c r="AA7" s="1" t="inlineStr">
+        <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X7" s="1" t="inlineStr">
-        <is>
-          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
-        </is>
-      </c>
-      <c r="Y7" s="1" t="inlineStr"/>
-      <c r="Z7" s="1" t="inlineStr"/>
-      <c r="AA7" s="1" t="inlineStr"/>
       <c r="AB7" s="1" t="inlineStr">
         <is>
-          <t>27000</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AC7" s="1" t="inlineStr">
         <is>
-          <t>Тонар</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AD7" s="1" t="inlineStr">
         <is>
-          <t>T4-16V</t>
-        </is>
-      </c>
-      <c r="AE7" s="1" t="inlineStr"/>
+          <t>16500</t>
+        </is>
+      </c>
+      <c r="AE7" s="1" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
       <c r="AF7" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Шторно-бортовой</t>
         </is>
       </c>
       <c r="AG7" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="AH7" s="1" t="inlineStr"/>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AH7" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="AI7" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="AJ7" s="1" t="inlineStr"/>
-      <c r="AK7" s="1" t="inlineStr">
-        <is>
-          <t>Пневматическая</t>
-        </is>
-      </c>
+          <t>475000</t>
+        </is>
+      </c>
+      <c r="AJ7" s="1" t="inlineStr">
+        <is>
+          <t>475000</t>
+        </is>
+      </c>
+      <c r="AK7" s="1" t="inlineStr"/>
       <c r="AL7" s="1" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AM7" s="1" t="inlineStr">
-        <is>
-          <t>16500</t>
-        </is>
-      </c>
-      <c r="AN7" s="1" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AO7" s="1" t="inlineStr"/>
-      <c r="AP7" s="1" t="inlineStr">
-        <is>
-          <t>Шторно-бортовой</t>
-        </is>
-      </c>
-      <c r="AQ7" s="1" t="inlineStr">
-        <is>
-          <t>Полуприцеп</t>
-        </is>
-      </c>
-      <c r="AR7" s="1" t="inlineStr"/>
-      <c r="AS7" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AT7" s="1" t="inlineStr">
-        <is>
-          <t>475000</t>
-        </is>
-      </c>
-      <c r="AU7" s="1" t="inlineStr">
-        <is>
-          <t>475000</t>
-        </is>
-      </c>
-      <c r="AV7" s="1" t="inlineStr"/>
-      <c r="AW7" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-t4-16v</t>
         </is>
@@ -2204,108 +2083,97 @@
           <t>4</t>
         </is>
       </c>
-      <c r="P8" s="1" t="inlineStr"/>
+      <c r="P8" s="1" t="inlineStr">
+        <is>
+          <t>Барабанные</t>
+        </is>
+      </c>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
-        </is>
-      </c>
-      <c r="R8" s="1" t="inlineStr"/>
-      <c r="S8" s="1" t="inlineStr"/>
-      <c r="T8" s="1" t="inlineStr">
-        <is>
           <t>ООО БелКар</t>
         </is>
       </c>
-      <c r="U8" s="1" t="inlineStr">
+      <c r="R8" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
+      <c r="S8" s="1" t="inlineStr">
+        <is>
+          <t>2980000</t>
+        </is>
+      </c>
+      <c r="T8" s="1" t="inlineStr"/>
+      <c r="U8" s="1" t="inlineStr"/>
       <c r="V8" s="1" t="inlineStr">
         <is>
-          <t>2980000</t>
-        </is>
-      </c>
-      <c r="W8" s="1" t="inlineStr"/>
-      <c r="X8" s="1" t="inlineStr"/>
+          <t>47000</t>
+        </is>
+      </c>
+      <c r="W8" s="1" t="inlineStr">
+        <is>
+          <t>ИнтерПрицеп</t>
+        </is>
+      </c>
+      <c r="X8" s="1" t="inlineStr">
+        <is>
+          <t>853371</t>
+        </is>
+      </c>
       <c r="Y8" s="1" t="inlineStr"/>
-      <c r="Z8" s="1" t="inlineStr"/>
-      <c r="AA8" s="1" t="inlineStr"/>
+      <c r="Z8" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
+      <c r="AA8" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="AB8" s="1" t="inlineStr">
         <is>
-          <t>47000</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AC8" s="1" t="inlineStr">
         <is>
-          <t>ИнтерПрицеп</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AD8" s="1" t="inlineStr">
         <is>
-          <t>853371</t>
-        </is>
-      </c>
-      <c r="AE8" s="1" t="inlineStr"/>
-      <c r="AF8" s="1" t="inlineStr"/>
+          <t>12600</t>
+        </is>
+      </c>
+      <c r="AE8" s="1" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AF8" s="1" t="inlineStr">
+        <is>
+          <t>Зерновоз</t>
+        </is>
+      </c>
       <c r="AG8" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="AH8" s="1" t="inlineStr"/>
-      <c r="AI8" s="1" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AH8" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AI8" s="1" t="inlineStr"/>
       <c r="AJ8" s="1" t="inlineStr"/>
       <c r="AK8" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>Без ограничения по пробегу</t>
         </is>
       </c>
       <c r="AL8" s="1" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="AM8" s="1" t="inlineStr">
-        <is>
-          <t>12600</t>
-        </is>
-      </c>
-      <c r="AN8" s="1" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="AO8" s="1" t="inlineStr"/>
-      <c r="AP8" s="1" t="inlineStr">
-        <is>
-          <t>Зерновоз</t>
-        </is>
-      </c>
-      <c r="AQ8" s="1" t="inlineStr">
-        <is>
-          <t>Полуприцеп</t>
-        </is>
-      </c>
-      <c r="AR8" s="1" t="inlineStr"/>
-      <c r="AS8" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AT8" s="1" t="inlineStr"/>
-      <c r="AU8" s="1" t="inlineStr"/>
-      <c r="AV8" s="1" t="inlineStr">
-        <is>
-          <t>Без ограничения по пробегу</t>
-        </is>
-      </c>
-      <c r="AW8" s="1" t="inlineStr">
         <is>
           <t>bk-interpricep-853371</t>
         </is>
@@ -2430,116 +2298,105 @@
           <t>3</t>
         </is>
       </c>
-      <c r="P9" s="1" t="inlineStr"/>
+      <c r="P9" s="1" t="inlineStr">
+        <is>
+          <t>Барабанные</t>
+        </is>
+      </c>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
-        </is>
-      </c>
-      <c r="R9" s="1" t="inlineStr"/>
-      <c r="S9" s="1" t="inlineStr"/>
+          <t>ООО БелКар</t>
+        </is>
+      </c>
+      <c r="R9" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="S9" s="1" t="inlineStr">
+        <is>
+          <t>5400000</t>
+        </is>
+      </c>
       <c r="T9" s="1" t="inlineStr">
         <is>
-          <t>ООО БелКар</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="U9" s="1" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V9" s="1" t="inlineStr">
         <is>
-          <t>5400000</t>
+          <t>33200</t>
         </is>
       </c>
       <c r="W9" s="1" t="inlineStr">
         <is>
+          <t>Тонар</t>
+        </is>
+      </c>
+      <c r="X9" s="1" t="inlineStr">
+        <is>
+          <t>95941</t>
+        </is>
+      </c>
+      <c r="Y9" s="1" t="inlineStr"/>
+      <c r="Z9" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
+      <c r="AA9" s="1" t="inlineStr">
+        <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X9" s="1" t="inlineStr">
-        <is>
-          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
-        </is>
-      </c>
-      <c r="Y9" s="1" t="inlineStr"/>
-      <c r="Z9" s="1" t="inlineStr"/>
-      <c r="AA9" s="1" t="inlineStr"/>
       <c r="AB9" s="1" t="inlineStr">
         <is>
-          <t>33200</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AC9" s="1" t="inlineStr">
         <is>
-          <t>Тонар</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AD9" s="1" t="inlineStr">
         <is>
-          <t>95941</t>
-        </is>
-      </c>
-      <c r="AE9" s="1" t="inlineStr"/>
-      <c r="AF9" s="1" t="inlineStr"/>
+          <t>12166</t>
+        </is>
+      </c>
+      <c r="AE9" s="1" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AF9" s="1" t="inlineStr">
+        <is>
+          <t>Зерновоз</t>
+        </is>
+      </c>
       <c r="AG9" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="AH9" s="1" t="inlineStr"/>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AH9" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="AI9" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="AJ9" s="1" t="inlineStr"/>
-      <c r="AK9" s="1" t="inlineStr">
-        <is>
-          <t>Пневматическая</t>
-        </is>
-      </c>
+      <c r="AK9" s="1" t="inlineStr"/>
       <c r="AL9" s="1" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AM9" s="1" t="inlineStr">
-        <is>
-          <t>12166</t>
-        </is>
-      </c>
-      <c r="AN9" s="1" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="AO9" s="1" t="inlineStr"/>
-      <c r="AP9" s="1" t="inlineStr">
-        <is>
-          <t>Зерновоз</t>
-        </is>
-      </c>
-      <c r="AQ9" s="1" t="inlineStr">
-        <is>
-          <t>Полуприцеп</t>
-        </is>
-      </c>
-      <c r="AR9" s="1" t="inlineStr"/>
-      <c r="AS9" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AT9" s="1" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
-      </c>
-      <c r="AU9" s="1" t="inlineStr"/>
-      <c r="AV9" s="1" t="inlineStr"/>
-      <c r="AW9" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-95941-12166</t>
         </is>
@@ -2664,120 +2521,109 @@
           <t>3</t>
         </is>
       </c>
-      <c r="P10" s="1" t="inlineStr"/>
+      <c r="P10" s="1" t="inlineStr">
+        <is>
+          <t>Дисковые</t>
+        </is>
+      </c>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
-        </is>
-      </c>
-      <c r="R10" s="1" t="inlineStr"/>
-      <c r="S10" s="1" t="inlineStr"/>
+          <t>ООО БелКар</t>
+        </is>
+      </c>
+      <c r="R10" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="S10" s="1" t="inlineStr">
+        <is>
+          <t>7365000</t>
+        </is>
+      </c>
       <c r="T10" s="1" t="inlineStr">
         <is>
-          <t>ООО БелКар</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="U10" s="1" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V10" s="1" t="inlineStr">
         <is>
-          <t>7365000</t>
+          <t>38080</t>
         </is>
       </c>
       <c r="W10" s="1" t="inlineStr">
         <is>
+          <t>Тонар</t>
+        </is>
+      </c>
+      <c r="X10" s="1" t="inlineStr">
+        <is>
+          <t>R3-13</t>
+        </is>
+      </c>
+      <c r="Y10" s="1" t="inlineStr">
+        <is>
+          <t>3 года или больше</t>
+        </is>
+      </c>
+      <c r="Z10" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
+      <c r="AA10" s="1" t="inlineStr">
+        <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X10" s="1" t="inlineStr">
-        <is>
-          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
-        </is>
-      </c>
-      <c r="Y10" s="1" t="inlineStr"/>
-      <c r="Z10" s="1" t="inlineStr"/>
-      <c r="AA10" s="1" t="inlineStr"/>
       <c r="AB10" s="1" t="inlineStr">
         <is>
-          <t>38080</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AC10" s="1" t="inlineStr">
         <is>
-          <t>Тонар</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AD10" s="1" t="inlineStr">
         <is>
-          <t>R3-13</t>
-        </is>
-      </c>
-      <c r="AE10" s="1" t="inlineStr"/>
+          <t>13500</t>
+        </is>
+      </c>
+      <c r="AE10" s="1" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="AF10" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Рефрижератор</t>
         </is>
       </c>
       <c r="AG10" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="AH10" s="1" t="inlineStr"/>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AH10" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="AI10" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="AJ10" s="1" t="inlineStr"/>
-      <c r="AK10" s="1" t="inlineStr">
-        <is>
-          <t>Пневматическая</t>
-        </is>
-      </c>
+      <c r="AK10" s="1" t="inlineStr"/>
       <c r="AL10" s="1" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AM10" s="1" t="inlineStr">
-        <is>
-          <t>13500</t>
-        </is>
-      </c>
-      <c r="AN10" s="1" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="AO10" s="1" t="inlineStr"/>
-      <c r="AP10" s="1" t="inlineStr">
-        <is>
-          <t>Рефрижератор</t>
-        </is>
-      </c>
-      <c r="AQ10" s="1" t="inlineStr">
-        <is>
-          <t>Полуприцеп</t>
-        </is>
-      </c>
-      <c r="AR10" s="1" t="inlineStr"/>
-      <c r="AS10" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AT10" s="1" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
-      </c>
-      <c r="AU10" s="1" t="inlineStr"/>
-      <c r="AV10" s="1" t="inlineStr"/>
-      <c r="AW10" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-r3-13-13500</t>
         </is>
@@ -2898,116 +2744,105 @@
           <t>3</t>
         </is>
       </c>
-      <c r="P11" s="1" t="inlineStr"/>
+      <c r="P11" s="1" t="inlineStr">
+        <is>
+          <t>Барабанные</t>
+        </is>
+      </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
-        </is>
-      </c>
-      <c r="R11" s="1" t="inlineStr"/>
-      <c r="S11" s="1" t="inlineStr"/>
+          <t>ООО БелКар</t>
+        </is>
+      </c>
+      <c r="R11" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="S11" s="1" t="inlineStr">
+        <is>
+          <t>5400000</t>
+        </is>
+      </c>
       <c r="T11" s="1" t="inlineStr">
         <is>
-          <t>ООО БелКар</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="U11" s="1" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V11" s="1" t="inlineStr">
         <is>
-          <t>5400000</t>
+          <t>31000</t>
         </is>
       </c>
       <c r="W11" s="1" t="inlineStr">
         <is>
+          <t>Тонар</t>
+        </is>
+      </c>
+      <c r="X11" s="1" t="inlineStr">
+        <is>
+          <t>95941</t>
+        </is>
+      </c>
+      <c r="Y11" s="1" t="inlineStr"/>
+      <c r="Z11" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
+      <c r="AA11" s="1" t="inlineStr">
+        <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X11" s="1" t="inlineStr">
-        <is>
-          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
-        </is>
-      </c>
-      <c r="Y11" s="1" t="inlineStr"/>
-      <c r="Z11" s="1" t="inlineStr"/>
-      <c r="AA11" s="1" t="inlineStr"/>
       <c r="AB11" s="1" t="inlineStr">
         <is>
-          <t>31000</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AC11" s="1" t="inlineStr">
         <is>
-          <t>Тонар</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AD11" s="1" t="inlineStr">
         <is>
-          <t>95941</t>
-        </is>
-      </c>
-      <c r="AE11" s="1" t="inlineStr"/>
-      <c r="AF11" s="1" t="inlineStr"/>
+          <t>9834</t>
+        </is>
+      </c>
+      <c r="AE11" s="1" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AF11" s="1" t="inlineStr">
+        <is>
+          <t>Зерновоз</t>
+        </is>
+      </c>
       <c r="AG11" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="AH11" s="1" t="inlineStr"/>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AH11" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="AI11" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="AJ11" s="1" t="inlineStr"/>
-      <c r="AK11" s="1" t="inlineStr">
-        <is>
-          <t>Пневматическая</t>
-        </is>
-      </c>
+      <c r="AK11" s="1" t="inlineStr"/>
       <c r="AL11" s="1" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AM11" s="1" t="inlineStr">
-        <is>
-          <t>9834</t>
-        </is>
-      </c>
-      <c r="AN11" s="1" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="AO11" s="1" t="inlineStr"/>
-      <c r="AP11" s="1" t="inlineStr">
-        <is>
-          <t>Зерновоз</t>
-        </is>
-      </c>
-      <c r="AQ11" s="1" t="inlineStr">
-        <is>
-          <t>Полуприцеп</t>
-        </is>
-      </c>
-      <c r="AR11" s="1" t="inlineStr"/>
-      <c r="AS11" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AT11" s="1" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
-      </c>
-      <c r="AU11" s="1" t="inlineStr"/>
-      <c r="AV11" s="1" t="inlineStr"/>
-      <c r="AW11" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-95941</t>
         </is>
@@ -3148,108 +2983,97 @@
           <t>4</t>
         </is>
       </c>
-      <c r="P12" s="1" t="inlineStr"/>
+      <c r="P12" s="1" t="inlineStr">
+        <is>
+          <t>Барабанные</t>
+        </is>
+      </c>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
-        </is>
-      </c>
-      <c r="R12" s="1" t="inlineStr"/>
-      <c r="S12" s="1" t="inlineStr"/>
-      <c r="T12" s="1" t="inlineStr">
-        <is>
           <t>ООО БелКар</t>
         </is>
       </c>
-      <c r="U12" s="1" t="inlineStr">
+      <c r="R12" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
+      <c r="S12" s="1" t="inlineStr">
+        <is>
+          <t>3690000</t>
+        </is>
+      </c>
+      <c r="T12" s="1" t="inlineStr"/>
+      <c r="U12" s="1" t="inlineStr"/>
       <c r="V12" s="1" t="inlineStr">
         <is>
-          <t>3690000</t>
-        </is>
-      </c>
-      <c r="W12" s="1" t="inlineStr"/>
-      <c r="X12" s="1" t="inlineStr"/>
+          <t>47000</t>
+        </is>
+      </c>
+      <c r="W12" s="1" t="inlineStr">
+        <is>
+          <t>ИнтерПрицеп</t>
+        </is>
+      </c>
+      <c r="X12" s="1" t="inlineStr">
+        <is>
+          <t>853372</t>
+        </is>
+      </c>
       <c r="Y12" s="1" t="inlineStr"/>
-      <c r="Z12" s="1" t="inlineStr"/>
-      <c r="AA12" s="1" t="inlineStr"/>
+      <c r="Z12" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
+      <c r="AA12" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="AB12" s="1" t="inlineStr">
         <is>
-          <t>47000</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AC12" s="1" t="inlineStr">
         <is>
-          <t>ИнтерПрицеп</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AD12" s="1" t="inlineStr">
         <is>
-          <t>853372</t>
-        </is>
-      </c>
-      <c r="AE12" s="1" t="inlineStr"/>
-      <c r="AF12" s="1" t="inlineStr"/>
+          <t>12250</t>
+        </is>
+      </c>
+      <c r="AE12" s="1" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AF12" s="1" t="inlineStr">
+        <is>
+          <t>Самосвальный</t>
+        </is>
+      </c>
       <c r="AG12" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="AH12" s="1" t="inlineStr"/>
-      <c r="AI12" s="1" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AH12" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AI12" s="1" t="inlineStr"/>
       <c r="AJ12" s="1" t="inlineStr"/>
       <c r="AK12" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>Без ограничения по пробегу</t>
         </is>
       </c>
       <c r="AL12" s="1" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="AM12" s="1" t="inlineStr">
-        <is>
-          <t>12250</t>
-        </is>
-      </c>
-      <c r="AN12" s="1" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="AO12" s="1" t="inlineStr"/>
-      <c r="AP12" s="1" t="inlineStr">
-        <is>
-          <t>Самосвальный</t>
-        </is>
-      </c>
-      <c r="AQ12" s="1" t="inlineStr">
-        <is>
-          <t>Полуприцеп</t>
-        </is>
-      </c>
-      <c r="AR12" s="1" t="inlineStr"/>
-      <c r="AS12" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AT12" s="1" t="inlineStr"/>
-      <c r="AU12" s="1" t="inlineStr"/>
-      <c r="AV12" s="1" t="inlineStr">
-        <is>
-          <t>Без ограничения по пробегу</t>
-        </is>
-      </c>
-      <c r="AW12" s="1" t="inlineStr">
         <is>
           <t>bk-interpricep-853372</t>
         </is>
@@ -3387,104 +3211,93 @@
           <t>4</t>
         </is>
       </c>
-      <c r="P13" s="1" t="inlineStr"/>
+      <c r="P13" s="1" t="inlineStr">
+        <is>
+          <t>Барабанные</t>
+        </is>
+      </c>
       <c r="Q13" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
-        </is>
-      </c>
-      <c r="R13" s="1" t="inlineStr"/>
-      <c r="S13" s="1" t="inlineStr"/>
-      <c r="T13" s="1" t="inlineStr">
-        <is>
           <t>ООО БелКар</t>
         </is>
       </c>
-      <c r="U13" s="1" t="inlineStr">
+      <c r="R13" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
+      <c r="S13" s="1" t="inlineStr">
+        <is>
+          <t>2280000</t>
+        </is>
+      </c>
+      <c r="T13" s="1" t="inlineStr"/>
+      <c r="U13" s="1" t="inlineStr"/>
       <c r="V13" s="1" t="inlineStr">
         <is>
-          <t>2280000</t>
-        </is>
-      </c>
-      <c r="W13" s="1" t="inlineStr"/>
-      <c r="X13" s="1" t="inlineStr"/>
+          <t>47000</t>
+        </is>
+      </c>
+      <c r="W13" s="1" t="inlineStr">
+        <is>
+          <t>ИнтерПрицеп</t>
+        </is>
+      </c>
+      <c r="X13" s="1" t="inlineStr">
+        <is>
+          <t>853375</t>
+        </is>
+      </c>
       <c r="Y13" s="1" t="inlineStr"/>
-      <c r="Z13" s="1" t="inlineStr"/>
-      <c r="AA13" s="1" t="inlineStr"/>
+      <c r="Z13" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
+      <c r="AA13" s="1" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="AB13" s="1" t="inlineStr">
         <is>
-          <t>47000</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AC13" s="1" t="inlineStr">
         <is>
-          <t>ИнтерПрицеп</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AD13" s="1" t="inlineStr">
         <is>
-          <t>853375</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="AE13" s="1" t="inlineStr"/>
-      <c r="AF13" s="1" t="inlineStr"/>
+      <c r="AF13" s="1" t="inlineStr">
+        <is>
+          <t>Контейнеровоз</t>
+        </is>
+      </c>
       <c r="AG13" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="AH13" s="1" t="inlineStr"/>
-      <c r="AI13" s="1" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AH13" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AI13" s="1" t="inlineStr"/>
       <c r="AJ13" s="1" t="inlineStr"/>
       <c r="AK13" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>Без ограничения по пробегу</t>
         </is>
       </c>
       <c r="AL13" s="1" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="AM13" s="1" t="inlineStr">
-        <is>
-          <t>12600</t>
-        </is>
-      </c>
-      <c r="AN13" s="1" t="inlineStr"/>
-      <c r="AO13" s="1" t="inlineStr"/>
-      <c r="AP13" s="1" t="inlineStr">
-        <is>
-          <t>Контейнеровоз</t>
-        </is>
-      </c>
-      <c r="AQ13" s="1" t="inlineStr">
-        <is>
-          <t>Полуприцеп</t>
-        </is>
-      </c>
-      <c r="AR13" s="1" t="inlineStr"/>
-      <c r="AS13" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AT13" s="1" t="inlineStr"/>
-      <c r="AU13" s="1" t="inlineStr"/>
-      <c r="AV13" s="1" t="inlineStr">
-        <is>
-          <t>Без ограничения по пробегу</t>
-        </is>
-      </c>
-      <c r="AW13" s="1" t="inlineStr">
         <is>
           <t>bk-interpricep-853375</t>
         </is>
@@ -3595,120 +3408,109 @@
           <t>3</t>
         </is>
       </c>
-      <c r="P14" s="1" t="inlineStr"/>
+      <c r="P14" s="1" t="inlineStr">
+        <is>
+          <t>Барабанные</t>
+        </is>
+      </c>
       <c r="Q14" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
-        </is>
-      </c>
-      <c r="R14" s="1" t="inlineStr"/>
-      <c r="S14" s="1" t="inlineStr"/>
+          <t>ООО БелКар</t>
+        </is>
+      </c>
+      <c r="R14" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="S14" s="1" t="inlineStr">
+        <is>
+          <t>3900000</t>
+        </is>
+      </c>
       <c r="T14" s="1" t="inlineStr">
         <is>
-          <t>ООО БелКар</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="U14" s="1" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V14" s="1" t="inlineStr">
         <is>
-          <t>3900000</t>
+          <t>17700</t>
         </is>
       </c>
       <c r="W14" s="1" t="inlineStr">
         <is>
+          <t>Тонар</t>
+        </is>
+      </c>
+      <c r="X14" s="1" t="inlineStr">
+        <is>
+          <t>SP3-17</t>
+        </is>
+      </c>
+      <c r="Y14" s="1" t="inlineStr"/>
+      <c r="Z14" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
+      <c r="AA14" s="1" t="inlineStr">
+        <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X14" s="1" t="inlineStr">
-        <is>
-          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
-        </is>
-      </c>
-      <c r="Y14" s="1" t="inlineStr"/>
-      <c r="Z14" s="1" t="inlineStr"/>
-      <c r="AA14" s="1" t="inlineStr"/>
       <c r="AB14" s="1" t="inlineStr">
         <is>
-          <t>17700</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AC14" s="1" t="inlineStr">
         <is>
-          <t>Тонар</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AD14" s="1" t="inlineStr">
         <is>
-          <t>SP3-17</t>
-        </is>
-      </c>
-      <c r="AE14" s="1" t="inlineStr"/>
-      <c r="AF14" s="1" t="inlineStr"/>
+          <t>9450</t>
+        </is>
+      </c>
+      <c r="AE14" s="1" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF14" s="1" t="inlineStr">
+        <is>
+          <t>Самосвальный</t>
+        </is>
+      </c>
       <c r="AG14" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="AH14" s="1" t="inlineStr"/>
+          <t>Прицеп</t>
+        </is>
+      </c>
+      <c r="AH14" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="AI14" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="AJ14" s="1" t="inlineStr"/>
       <c r="AK14" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>Без ограничения по пробегу</t>
         </is>
       </c>
       <c r="AL14" s="1" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AM14" s="1" t="inlineStr">
-        <is>
-          <t>9450</t>
-        </is>
-      </c>
-      <c r="AN14" s="1" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AO14" s="1" t="inlineStr"/>
-      <c r="AP14" s="1" t="inlineStr">
-        <is>
-          <t>Самосвальный</t>
-        </is>
-      </c>
-      <c r="AQ14" s="1" t="inlineStr">
-        <is>
-          <t>Прицеп</t>
-        </is>
-      </c>
-      <c r="AR14" s="1" t="inlineStr"/>
-      <c r="AS14" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AT14" s="1" t="inlineStr">
-        <is>
-          <t>390000</t>
-        </is>
-      </c>
-      <c r="AU14" s="1" t="inlineStr"/>
-      <c r="AV14" s="1" t="inlineStr">
-        <is>
-          <t>Без ограничения по пробегу</t>
-        </is>
-      </c>
-      <c r="AW14" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-sp3-17</t>
         </is>
@@ -3829,120 +3631,109 @@
           <t>4</t>
         </is>
       </c>
-      <c r="P15" s="1" t="inlineStr"/>
+      <c r="P15" s="1" t="inlineStr">
+        <is>
+          <t>Барабанные</t>
+        </is>
+      </c>
       <c r="Q15" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
-        </is>
-      </c>
-      <c r="R15" s="1" t="inlineStr"/>
-      <c r="S15" s="1" t="inlineStr"/>
+          <t>ООО БелКар</t>
+        </is>
+      </c>
+      <c r="R15" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="S15" s="1" t="inlineStr">
+        <is>
+          <t>3800000</t>
+        </is>
+      </c>
       <c r="T15" s="1" t="inlineStr">
         <is>
-          <t>ООО БелКар</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="U15" s="1" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V15" s="1" t="inlineStr">
         <is>
-          <t>3800000</t>
+          <t>31800</t>
         </is>
       </c>
       <c r="W15" s="1" t="inlineStr">
         <is>
+          <t>Тонар</t>
+        </is>
+      </c>
+      <c r="X15" s="1" t="inlineStr">
+        <is>
+          <t>B4-16V (97882)</t>
+        </is>
+      </c>
+      <c r="Y15" s="1" t="inlineStr">
+        <is>
+          <t>3 года или больше</t>
+        </is>
+      </c>
+      <c r="Z15" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
+      <c r="AA15" s="1" t="inlineStr">
+        <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X15" s="1" t="inlineStr">
-        <is>
-          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
-        </is>
-      </c>
-      <c r="Y15" s="1" t="inlineStr"/>
-      <c r="Z15" s="1" t="inlineStr"/>
-      <c r="AA15" s="1" t="inlineStr"/>
       <c r="AB15" s="1" t="inlineStr">
         <is>
-          <t>31800</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AC15" s="1" t="inlineStr">
         <is>
-          <t>Тонар</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AD15" s="1" t="inlineStr">
         <is>
-          <t>B4-16V (97882)</t>
+          <t>16510</t>
         </is>
       </c>
       <c r="AE15" s="1" t="inlineStr"/>
       <c r="AF15" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Бортовой</t>
         </is>
       </c>
       <c r="AG15" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="AH15" s="1" t="inlineStr"/>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AH15" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="AI15" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="AJ15" s="1" t="inlineStr"/>
-      <c r="AK15" s="1" t="inlineStr">
-        <is>
-          <t>Пневматическая</t>
-        </is>
-      </c>
+          <t>380000</t>
+        </is>
+      </c>
+      <c r="AJ15" s="1" t="inlineStr">
+        <is>
+          <t>380000</t>
+        </is>
+      </c>
+      <c r="AK15" s="1" t="inlineStr"/>
       <c r="AL15" s="1" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AM15" s="1" t="inlineStr">
-        <is>
-          <t>16510</t>
-        </is>
-      </c>
-      <c r="AN15" s="1" t="inlineStr"/>
-      <c r="AO15" s="1" t="inlineStr"/>
-      <c r="AP15" s="1" t="inlineStr">
-        <is>
-          <t>Бортовой</t>
-        </is>
-      </c>
-      <c r="AQ15" s="1" t="inlineStr">
-        <is>
-          <t>Полуприцеп</t>
-        </is>
-      </c>
-      <c r="AR15" s="1" t="inlineStr"/>
-      <c r="AS15" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AT15" s="1" t="inlineStr">
-        <is>
-          <t>380000</t>
-        </is>
-      </c>
-      <c r="AU15" s="1" t="inlineStr">
-        <is>
-          <t>380000</t>
-        </is>
-      </c>
-      <c r="AV15" s="1" t="inlineStr"/>
-      <c r="AW15" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-b4-16v-97882</t>
         </is>
@@ -4058,120 +3849,109 @@
           <t>3</t>
         </is>
       </c>
-      <c r="P16" s="1" t="inlineStr"/>
+      <c r="P16" s="1" t="inlineStr">
+        <is>
+          <t>Барабанные</t>
+        </is>
+      </c>
       <c r="Q16" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
-        </is>
-      </c>
-      <c r="R16" s="1" t="inlineStr"/>
-      <c r="S16" s="1" t="inlineStr"/>
+          <t>ООО БелКар</t>
+        </is>
+      </c>
+      <c r="R16" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="S16" s="1" t="inlineStr">
+        <is>
+          <t>2850000</t>
+        </is>
+      </c>
       <c r="T16" s="1" t="inlineStr">
         <is>
-          <t>ООО БелКар</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="U16" s="1" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V16" s="1" t="inlineStr">
         <is>
-          <t>2850000</t>
+          <t>38000</t>
         </is>
       </c>
       <c r="W16" s="1" t="inlineStr">
         <is>
+          <t>Тонар</t>
+        </is>
+      </c>
+      <c r="X16" s="1" t="inlineStr">
+        <is>
+          <t>K3-U (99882)</t>
+        </is>
+      </c>
+      <c r="Y16" s="1" t="inlineStr">
+        <is>
+          <t>3 года или больше</t>
+        </is>
+      </c>
+      <c r="Z16" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
+      <c r="AA16" s="1" t="inlineStr">
+        <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X16" s="1" t="inlineStr">
-        <is>
-          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
-        </is>
-      </c>
-      <c r="Y16" s="1" t="inlineStr"/>
-      <c r="Z16" s="1" t="inlineStr"/>
-      <c r="AA16" s="1" t="inlineStr"/>
       <c r="AB16" s="1" t="inlineStr">
         <is>
-          <t>38000</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AC16" s="1" t="inlineStr">
         <is>
-          <t>Тонар</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AD16" s="1" t="inlineStr">
         <is>
-          <t>K3-U (99882)</t>
+          <t>12750</t>
         </is>
       </c>
       <c r="AE16" s="1" t="inlineStr"/>
       <c r="AF16" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Контейнеровоз</t>
         </is>
       </c>
       <c r="AG16" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="AH16" s="1" t="inlineStr"/>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AH16" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="AI16" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="AJ16" s="1" t="inlineStr"/>
-      <c r="AK16" s="1" t="inlineStr">
-        <is>
-          <t>Пневматическая</t>
-        </is>
-      </c>
+          <t>285000</t>
+        </is>
+      </c>
+      <c r="AJ16" s="1" t="inlineStr">
+        <is>
+          <t>142500</t>
+        </is>
+      </c>
+      <c r="AK16" s="1" t="inlineStr"/>
       <c r="AL16" s="1" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AM16" s="1" t="inlineStr">
-        <is>
-          <t>12750</t>
-        </is>
-      </c>
-      <c r="AN16" s="1" t="inlineStr"/>
-      <c r="AO16" s="1" t="inlineStr"/>
-      <c r="AP16" s="1" t="inlineStr">
-        <is>
-          <t>Контейнеровоз</t>
-        </is>
-      </c>
-      <c r="AQ16" s="1" t="inlineStr">
-        <is>
-          <t>Полуприцеп</t>
-        </is>
-      </c>
-      <c r="AR16" s="1" t="inlineStr"/>
-      <c r="AS16" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AT16" s="1" t="inlineStr">
-        <is>
-          <t>285000</t>
-        </is>
-      </c>
-      <c r="AU16" s="1" t="inlineStr">
-        <is>
-          <t>142500</t>
-        </is>
-      </c>
-      <c r="AV16" s="1" t="inlineStr"/>
-      <c r="AW16" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-k3-u-99882</t>
         </is>
@@ -4287,120 +4067,109 @@
           <t>4</t>
         </is>
       </c>
-      <c r="P17" s="1" t="inlineStr"/>
+      <c r="P17" s="1" t="inlineStr">
+        <is>
+          <t>Барабанные</t>
+        </is>
+      </c>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>Барабанные</t>
-        </is>
-      </c>
-      <c r="R17" s="1" t="inlineStr"/>
-      <c r="S17" s="1" t="inlineStr"/>
+          <t>ООО БелКар</t>
+        </is>
+      </c>
+      <c r="R17" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="S17" s="1" t="inlineStr">
+        <is>
+          <t>3250000</t>
+        </is>
+      </c>
       <c r="T17" s="1" t="inlineStr">
         <is>
-          <t>ООО БелКар</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="U17" s="1" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V17" s="1" t="inlineStr">
         <is>
-          <t>3250000</t>
+          <t>44000</t>
         </is>
       </c>
       <c r="W17" s="1" t="inlineStr">
         <is>
+          <t>Тонар</t>
+        </is>
+      </c>
+      <c r="X17" s="1" t="inlineStr">
+        <is>
+          <t>K4-U (99894) ДОПОГ</t>
+        </is>
+      </c>
+      <c r="Y17" s="1" t="inlineStr">
+        <is>
+          <t>3 года или больше</t>
+        </is>
+      </c>
+      <c r="Z17" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
+      <c r="AA17" s="1" t="inlineStr">
+        <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X17" s="1" t="inlineStr">
-        <is>
-          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
-        </is>
-      </c>
-      <c r="Y17" s="1" t="inlineStr"/>
-      <c r="Z17" s="1" t="inlineStr"/>
-      <c r="AA17" s="1" t="inlineStr"/>
       <c r="AB17" s="1" t="inlineStr">
         <is>
-          <t>44000</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AC17" s="1" t="inlineStr">
         <is>
-          <t>Тонар</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AD17" s="1" t="inlineStr">
         <is>
-          <t>K4-U (99894) ДОПОГ</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="AE17" s="1" t="inlineStr"/>
       <c r="AF17" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Контейнеровоз</t>
         </is>
       </c>
       <c r="AG17" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="AH17" s="1" t="inlineStr"/>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AH17" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="AI17" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="AJ17" s="1" t="inlineStr"/>
-      <c r="AK17" s="1" t="inlineStr">
-        <is>
-          <t>Пневматическая</t>
-        </is>
-      </c>
+          <t>325000</t>
+        </is>
+      </c>
+      <c r="AJ17" s="1" t="inlineStr">
+        <is>
+          <t>162500</t>
+        </is>
+      </c>
+      <c r="AK17" s="1" t="inlineStr"/>
       <c r="AL17" s="1" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AM17" s="1" t="inlineStr">
-        <is>
-          <t>12192</t>
-        </is>
-      </c>
-      <c r="AN17" s="1" t="inlineStr"/>
-      <c r="AO17" s="1" t="inlineStr"/>
-      <c r="AP17" s="1" t="inlineStr">
-        <is>
-          <t>Контейнеровоз</t>
-        </is>
-      </c>
-      <c r="AQ17" s="1" t="inlineStr">
-        <is>
-          <t>Полуприцеп</t>
-        </is>
-      </c>
-      <c r="AR17" s="1" t="inlineStr"/>
-      <c r="AS17" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AT17" s="1" t="inlineStr">
-        <is>
-          <t>325000</t>
-        </is>
-      </c>
-      <c r="AU17" s="1" t="inlineStr">
-        <is>
-          <t>162500</t>
-        </is>
-      </c>
-      <c r="AV17" s="1" t="inlineStr"/>
-      <c r="AW17" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-k4-u-99894</t>
         </is>
@@ -4528,120 +4297,109 @@
           <t>3</t>
         </is>
       </c>
-      <c r="P18" s="1" t="inlineStr"/>
+      <c r="P18" s="1" t="inlineStr">
+        <is>
+          <t>Дисковые</t>
+        </is>
+      </c>
       <c r="Q18" s="1" t="inlineStr">
         <is>
-          <t>Дисковые</t>
-        </is>
-      </c>
-      <c r="R18" s="1" t="inlineStr"/>
-      <c r="S18" s="1" t="inlineStr"/>
+          <t>ООО БелКар</t>
+        </is>
+      </c>
+      <c r="R18" s="1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="S18" s="1" t="inlineStr">
+        <is>
+          <t>3800000</t>
+        </is>
+      </c>
       <c r="T18" s="1" t="inlineStr">
         <is>
-          <t>ООО БелКар</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="U18" s="1" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V18" s="1" t="inlineStr">
         <is>
-          <t>3800000</t>
+          <t>31800</t>
         </is>
       </c>
       <c r="W18" s="1" t="inlineStr">
         <is>
+          <t>Тонар</t>
+        </is>
+      </c>
+      <c r="X18" s="1" t="inlineStr">
+        <is>
+          <t>T3-13 (9888)</t>
+        </is>
+      </c>
+      <c r="Y18" s="1" t="inlineStr">
+        <is>
+          <t>3 года или больше</t>
+        </is>
+      </c>
+      <c r="Z18" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
+      <c r="AA18" s="1" t="inlineStr">
+        <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X18" s="1" t="inlineStr">
-        <is>
-          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
-        </is>
-      </c>
-      <c r="Y18" s="1" t="inlineStr"/>
-      <c r="Z18" s="1" t="inlineStr"/>
-      <c r="AA18" s="1" t="inlineStr"/>
       <c r="AB18" s="1" t="inlineStr">
         <is>
-          <t>31800</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AC18" s="1" t="inlineStr">
         <is>
-          <t>Тонар</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AD18" s="1" t="inlineStr">
         <is>
-          <t>T3-13 (9888)</t>
+          <t>13600</t>
         </is>
       </c>
       <c r="AE18" s="1" t="inlineStr"/>
       <c r="AF18" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Шторно-бортовой</t>
         </is>
       </c>
       <c r="AG18" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="AH18" s="1" t="inlineStr"/>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="AH18" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="AI18" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="AJ18" s="1" t="inlineStr"/>
-      <c r="AK18" s="1" t="inlineStr">
-        <is>
-          <t>Пневматическая</t>
-        </is>
-      </c>
+          <t>380000</t>
+        </is>
+      </c>
+      <c r="AJ18" s="1" t="inlineStr">
+        <is>
+          <t>380000</t>
+        </is>
+      </c>
+      <c r="AK18" s="1" t="inlineStr"/>
       <c r="AL18" s="1" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AM18" s="1" t="inlineStr">
-        <is>
-          <t>13600</t>
-        </is>
-      </c>
-      <c r="AN18" s="1" t="inlineStr"/>
-      <c r="AO18" s="1" t="inlineStr"/>
-      <c r="AP18" s="1" t="inlineStr">
-        <is>
-          <t>Шторно-бортовой</t>
-        </is>
-      </c>
-      <c r="AQ18" s="1" t="inlineStr">
-        <is>
-          <t>Полуприцеп</t>
-        </is>
-      </c>
-      <c r="AR18" s="1" t="inlineStr"/>
-      <c r="AS18" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AT18" s="1" t="inlineStr">
-        <is>
-          <t>380000</t>
-        </is>
-      </c>
-      <c r="AU18" s="1" t="inlineStr">
-        <is>
-          <t>380000</t>
-        </is>
-      </c>
-      <c r="AV18" s="1" t="inlineStr"/>
-      <c r="AW18" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-t3-13-9888</t>
         </is>
@@ -4655,457 +4413,15 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>Седельные тягачи</t>
+          <t>Прицепы</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>Седельный тягач МАЗ 643028, 2023</t>
+          <t>Полуприцеп самосвальный Тонар SL4-34G (9595), 2026</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
-        <is>
-          <t>&lt;strong&gt;Седельные тягачи МАЗ 643028 / 2023 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
-&lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
-- &lt;strong&gt;Двигатель:&lt;/strong&gt; WP12.430E50
-- &lt;strong&gt;Коробка передач:&lt;/strong&gt; 16JSDX240TA
-- &lt;strong&gt;Колесная формула:&lt;/strong&gt;  6х4
-- &lt;strong&gt;Экологический класс:&lt;/strong&gt; Euro 5
-- &lt;strong&gt;Технически допустимая полная масса автомобиля:&lt;/strong&gt; 26000 кг
-- &lt;strong&gt;Технически допустимая полная масса автопоезда:&lt;/strong&gt; 52000 кг
-- &lt;strong&gt;Модель двигателя:&lt;/strong&gt; Евро-5
-- &lt;strong&gt;Мощность двигателя:&lt;/strong&gt; 428 л.с. (315 кВт)
-- &lt;strong&gt;Коробка передач:&lt;/strong&gt; механическая, 16 ступеней
-- &lt;strong&gt;Высота ССУ:&lt;/strong&gt; 1150 мм
-- &lt;strong&gt;Допустимая нагрузка на ССУ:&lt;/strong&gt; 15500 кг
-- &lt;strong&gt;Нагрузка на переднюю ось:&lt;/strong&gt; 7000 кг
-- &lt;strong&gt;Нагрузка на задний мост:&lt;/strong&gt; 19000 кг
-&lt;strong&gt;ДОПОЛНИТЕЛЬНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
-- &lt;strong&gt;Тип кабины:&lt;/strong&gt; большая с высокой крышей «6431»
-- &lt;strong&gt;Объём топливного бака:&lt;/strong&gt; 500 л
-- &lt;strong&gt;Передняя подвеска:&lt;/strong&gt; рессорная
-- &lt;strong&gt;Задняя подвеска:&lt;/strong&gt; пневматическая
-- &lt;strong&gt;Размер шин:&lt;/strong&gt; 315/70R22.5
-• &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 7 250 000 ₽
-&lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
-        </is>
-      </c>
-      <c r="E19" s="1" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="F19" s="1" t="inlineStr">
-        <is>
-          <t>7250000</t>
-        </is>
-      </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-20/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-20/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-20/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-20/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-20/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-20/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-20/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-20/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-20/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-20/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-20/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-20/12.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-20/13.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-20/14.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-20/15.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-20/16.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-20/17.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-20/18.jpg</t>
-        </is>
-      </c>
-      <c r="H19" s="1" t="inlineStr">
-        <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="I19" s="1" t="inlineStr">
-        <is>
-          <t>Иван</t>
-        </is>
-      </c>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>info@bel-car.com</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>79031369484</t>
-        </is>
-      </c>
-      <c r="L19" s="1" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="M19" s="1" t="inlineStr"/>
-      <c r="N19" s="1" t="inlineStr">
-        <is>
-          <t>Под заказ</t>
-        </is>
-      </c>
-      <c r="O19" s="1" t="inlineStr"/>
-      <c r="P19" s="1" t="inlineStr">
-        <is>
-          <t>Седельный</t>
-        </is>
-      </c>
-      <c r="Q19" s="1" t="inlineStr"/>
-      <c r="R19" s="1" t="inlineStr">
-        <is>
-          <t>Механическая</t>
-        </is>
-      </c>
-      <c r="S19" s="1" t="inlineStr">
-        <is>
-          <t>2-х местная с 1 спальным</t>
-        </is>
-      </c>
-      <c r="T19" s="1" t="inlineStr">
-        <is>
-          <t>ООО БелКар</t>
-        </is>
-      </c>
-      <c r="U19" s="1" t="inlineStr">
-        <is>
-          <t>RUB</t>
-        </is>
-      </c>
-      <c r="V19" s="1" t="inlineStr">
-        <is>
-          <t>7250000</t>
-        </is>
-      </c>
-      <c r="W19" s="1" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="X19" s="1" t="inlineStr">
-        <is>
-          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
-        </is>
-      </c>
-      <c r="Y19" s="1" t="inlineStr">
-        <is>
-          <t>Евро 5</t>
-        </is>
-      </c>
-      <c r="Z19" s="1" t="inlineStr">
-        <is>
-          <t>11946</t>
-        </is>
-      </c>
-      <c r="AA19" s="1" t="inlineStr">
-        <is>
-          <t>Дизель</t>
-        </is>
-      </c>
-      <c r="AB19" s="1" t="inlineStr"/>
-      <c r="AC19" s="1" t="inlineStr">
-        <is>
-          <t>МАЗ</t>
-        </is>
-      </c>
-      <c r="AD19" s="1" t="inlineStr">
-        <is>
-          <t>643028</t>
-        </is>
-      </c>
-      <c r="AE19" s="1" t="inlineStr">
-        <is>
-          <t>643028</t>
-        </is>
-      </c>
-      <c r="AF19" s="1" t="inlineStr"/>
-      <c r="AG19" s="1" t="inlineStr">
-        <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="AH19" s="1" t="inlineStr">
-        <is>
-          <t>423</t>
-        </is>
-      </c>
-      <c r="AI19" s="1" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="AJ19" s="1" t="inlineStr">
-        <is>
-          <t>Пневматическая</t>
-        </is>
-      </c>
-      <c r="AK19" s="1" t="inlineStr"/>
-      <c r="AL19" s="1" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AM19" s="1" t="inlineStr"/>
-      <c r="AN19" s="1" t="inlineStr"/>
-      <c r="AO19" s="1" t="inlineStr">
-        <is>
-          <t>Механика</t>
-        </is>
-      </c>
-      <c r="AP19" s="1" t="inlineStr"/>
-      <c r="AQ19" s="1" t="inlineStr"/>
-      <c r="AR19" s="1" t="inlineStr">
-        <is>
-          <t>6×4</t>
-        </is>
-      </c>
-      <c r="AS19" s="1" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="AT19" s="1" t="inlineStr"/>
-      <c r="AU19" s="1" t="inlineStr"/>
-      <c r="AV19" s="1" t="inlineStr"/>
-      <c r="AW19" s="1" t="inlineStr">
-        <is>
-          <t>bk-maz-643028-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Грузовики и спецтехника</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>Седельные тягачи</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>Седельный тягач МАЗ 643028, 2023</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>&lt;strong&gt;Седельные тягачи МАЗ 643028 / 2023 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
-&lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
-- &lt;strong&gt;Двигатель:&lt;/strong&gt; WP12.430E50
-- &lt;strong&gt;Коробка передач:&lt;/strong&gt; WP12.430E50
-- &lt;strong&gt;Колесная формула:&lt;/strong&gt; 6×4
-- &lt;strong&gt;Экологический класс:&lt;/strong&gt; Euro 5
-- &lt;strong&gt;Технически допустимая полная масса автомобиля:&lt;/strong&gt; 26000 кг
-- &lt;strong&gt;Технически допустимая полная масса автопоезда:&lt;/strong&gt; 52000 кг
-- &lt;strong&gt;Модель двигателя:&lt;/strong&gt; Евро-5
-- &lt;strong&gt;Мощность двигателя:&lt;/strong&gt; 428 л.с. (315 кВт)
-- &lt;strong&gt;Коробка передач:&lt;/strong&gt; механическая, 16 ступеней
-- &lt;strong&gt;Высота ССУ:&lt;/strong&gt; 1250 мм
-- &lt;strong&gt;Допустимая нагрузка на ССУ:&lt;/strong&gt; 15500 кг
-- &lt;strong&gt;Нагрузка на переднюю ось:&lt;/strong&gt; 7000 кг
-- &lt;strong&gt;Нагрузка на задний мост:&lt;/strong&gt; 19000 кг
-&lt;strong&gt;ДОПОЛНИТЕЛЬНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
-- &lt;strong&gt;Тип кабины:&lt;/strong&gt; большая с высокой крышей «6431»
-- &lt;strong&gt;Объём топливного бака:&lt;/strong&gt; 500 л
-- &lt;strong&gt;Передняя подвеска:&lt;/strong&gt; рессорная
-- &lt;strong&gt;Задняя подвеска:&lt;/strong&gt; пневматическая
-- &lt;strong&gt;Размер шин:&lt;/strong&gt; 315/80R22.5
-• &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 7 450 000 ₽
-&lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>7450000</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-21/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-21/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-21/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-21/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-21/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-21/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-21/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-21/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-21/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-21/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-21/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-21/12.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-21/13.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-21/14.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-21/15.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-21/16.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-21/17.jpg</t>
-        </is>
-      </c>
-      <c r="H20" s="1" t="inlineStr">
-        <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>Иван</t>
-        </is>
-      </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>info@bel-car.com</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>79031369484</t>
-        </is>
-      </c>
-      <c r="L20" s="1" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="M20" s="1" t="inlineStr"/>
-      <c r="N20" s="1" t="inlineStr">
-        <is>
-          <t>Под заказ</t>
-        </is>
-      </c>
-      <c r="O20" s="1" t="inlineStr"/>
-      <c r="P20" s="1" t="inlineStr">
-        <is>
-          <t>Седельный</t>
-        </is>
-      </c>
-      <c r="Q20" s="1" t="inlineStr"/>
-      <c r="R20" s="1" t="inlineStr">
-        <is>
-          <t>Механическая</t>
-        </is>
-      </c>
-      <c r="S20" s="1" t="inlineStr">
-        <is>
-          <t>2-х местная с 1 спальным</t>
-        </is>
-      </c>
-      <c r="T20" s="1" t="inlineStr">
-        <is>
-          <t>ООО БелКар</t>
-        </is>
-      </c>
-      <c r="U20" s="1" t="inlineStr">
-        <is>
-          <t>RUB</t>
-        </is>
-      </c>
-      <c r="V20" s="1" t="inlineStr">
-        <is>
-          <t>7450000</t>
-        </is>
-      </c>
-      <c r="W20" s="1" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="X20" s="1" t="inlineStr">
-        <is>
-          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
-        </is>
-      </c>
-      <c r="Y20" s="1" t="inlineStr">
-        <is>
-          <t>Евро 5</t>
-        </is>
-      </c>
-      <c r="Z20" s="1" t="inlineStr">
-        <is>
-          <t>11946</t>
-        </is>
-      </c>
-      <c r="AA20" s="1" t="inlineStr">
-        <is>
-          <t>Дизель</t>
-        </is>
-      </c>
-      <c r="AB20" s="1" t="inlineStr"/>
-      <c r="AC20" s="1" t="inlineStr">
-        <is>
-          <t>МАЗ</t>
-        </is>
-      </c>
-      <c r="AD20" s="1" t="inlineStr">
-        <is>
-          <t>643028</t>
-        </is>
-      </c>
-      <c r="AE20" s="1" t="inlineStr">
-        <is>
-          <t>643028</t>
-        </is>
-      </c>
-      <c r="AF20" s="1" t="inlineStr"/>
-      <c r="AG20" s="1" t="inlineStr">
-        <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="AH20" s="1" t="inlineStr">
-        <is>
-          <t>423</t>
-        </is>
-      </c>
-      <c r="AI20" s="1" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="AJ20" s="1" t="inlineStr">
-        <is>
-          <t>Рессорная</t>
-        </is>
-      </c>
-      <c r="AK20" s="1" t="inlineStr"/>
-      <c r="AL20" s="1" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AM20" s="1" t="inlineStr"/>
-      <c r="AN20" s="1" t="inlineStr"/>
-      <c r="AO20" s="1" t="inlineStr">
-        <is>
-          <t>Механика</t>
-        </is>
-      </c>
-      <c r="AP20" s="1" t="inlineStr"/>
-      <c r="AQ20" s="1" t="inlineStr"/>
-      <c r="AR20" s="1" t="inlineStr">
-        <is>
-          <t>6×4</t>
-        </is>
-      </c>
-      <c r="AS20" s="1" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="AT20" s="1" t="inlineStr"/>
-      <c r="AU20" s="1" t="inlineStr"/>
-      <c r="AV20" s="1" t="inlineStr"/>
-      <c r="AW20" s="1" t="inlineStr">
-        <is>
-          <t>bk-maz-643028</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>Грузовики и спецтехника</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>Прицепы</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>Полуприцеп самосвальный Тонар SL4-34G (9595), 2026</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар SL4-34G (9595) / 2026 года выпуска&lt;/strong&gt;
 &lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
@@ -5149,193 +4465,182 @@
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
         </is>
       </c>
-      <c r="E21" s="1" t="inlineStr">
+      <c r="E19" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="F21" s="1" t="inlineStr">
+      <c r="F19" s="1" t="inlineStr">
         <is>
           <t>4200000</t>
         </is>
       </c>
-      <c r="G21" s="1" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-3/01.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-3/02.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-3/03.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-3/04.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-3/05.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-3/06.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-3/07.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-3/08.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-3/09.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-3/10.webp</t>
         </is>
       </c>
-      <c r="H21" s="1" t="inlineStr">
+      <c r="H19" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="I21" s="1" t="inlineStr">
+      <c r="I19" s="1" t="inlineStr">
         <is>
           <t>Иван</t>
         </is>
       </c>
-      <c r="J21" s="1" t="inlineStr">
+      <c r="J19" s="1" t="inlineStr">
         <is>
           <t>info@bel-car.com</t>
         </is>
       </c>
-      <c r="K21" s="1" t="inlineStr">
+      <c r="K19" s="1" t="inlineStr">
         <is>
           <t>79031369484</t>
         </is>
       </c>
-      <c r="L21" s="1" t="inlineStr">
+      <c r="L19" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M21" s="1" t="inlineStr">
+      <c r="M19" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="N21" s="1" t="inlineStr">
+      <c r="N19" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="O21" s="1" t="inlineStr">
+      <c r="O19" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P21" s="1" t="inlineStr"/>
-      <c r="Q21" s="1" t="inlineStr">
+      <c r="P19" s="1" t="inlineStr">
         <is>
           <t>Барабанные</t>
         </is>
       </c>
-      <c r="R21" s="1" t="inlineStr"/>
-      <c r="S21" s="1" t="inlineStr"/>
-      <c r="T21" s="1" t="inlineStr">
+      <c r="Q19" s="1" t="inlineStr">
         <is>
           <t>ООО БелКар</t>
         </is>
       </c>
-      <c r="U21" s="1" t="inlineStr">
+      <c r="R19" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="V21" s="1" t="inlineStr">
+      <c r="S19" s="1" t="inlineStr">
         <is>
           <t>4200000</t>
         </is>
       </c>
-      <c r="W21" s="1" t="inlineStr">
+      <c r="T19" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X21" s="1" t="inlineStr">
+      <c r="U19" s="1" t="inlineStr">
         <is>
           <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
-      <c r="Y21" s="1" t="inlineStr"/>
-      <c r="Z21" s="1" t="inlineStr"/>
-      <c r="AA21" s="1" t="inlineStr"/>
-      <c r="AB21" s="1" t="inlineStr">
+      <c r="V19" s="1" t="inlineStr">
         <is>
           <t>31800</t>
         </is>
       </c>
-      <c r="AC21" s="1" t="inlineStr">
+      <c r="W19" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AD21" s="1" t="inlineStr">
+      <c r="X19" s="1" t="inlineStr">
         <is>
           <t>SL4-34G (9595)</t>
         </is>
       </c>
-      <c r="AE21" s="1" t="inlineStr"/>
-      <c r="AF21" s="1" t="inlineStr">
+      <c r="Y19" s="1" t="inlineStr">
         <is>
           <t>3 года или больше</t>
         </is>
       </c>
-      <c r="AG21" s="1" t="inlineStr">
+      <c r="Z19" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="AH21" s="1" t="inlineStr"/>
-      <c r="AI21" s="1" t="inlineStr">
+      <c r="AA19" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AJ21" s="1" t="inlineStr"/>
-      <c r="AK21" s="1" t="inlineStr">
+      <c r="AB19" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AL21" s="1" t="inlineStr">
+      <c r="AC19" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AM21" s="1" t="inlineStr">
+      <c r="AD19" s="1" t="inlineStr">
         <is>
           <t>10450</t>
         </is>
       </c>
-      <c r="AN21" s="1" t="inlineStr"/>
-      <c r="AO21" s="1" t="inlineStr"/>
-      <c r="AP21" s="1" t="inlineStr">
+      <c r="AE19" s="1" t="inlineStr"/>
+      <c r="AF19" s="1" t="inlineStr">
         <is>
           <t>Самосвальный</t>
         </is>
       </c>
-      <c r="AQ21" s="1" t="inlineStr">
+      <c r="AG19" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AR21" s="1" t="inlineStr"/>
-      <c r="AS21" s="1" t="inlineStr">
+      <c r="AH19" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AT21" s="1" t="inlineStr">
+      <c r="AI19" s="1" t="inlineStr">
         <is>
           <t>420000</t>
         </is>
       </c>
-      <c r="AU21" s="1" t="inlineStr"/>
-      <c r="AV21" s="1" t="inlineStr"/>
-      <c r="AW21" s="1" t="inlineStr">
+      <c r="AJ19" s="1" t="inlineStr"/>
+      <c r="AK19" s="1" t="inlineStr"/>
+      <c r="AL19" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-sl4-34g-9595</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп самосвальный Тонар 9595, 2026</t>
         </is>
       </c>
-      <c r="D22" s="1" t="inlineStr">
+      <c r="D20" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар 9595 / 2026 года выпуска&lt;/strong&gt;
 &lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
@@ -5385,197 +4690,186 @@
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
         </is>
       </c>
-      <c r="E22" s="1" t="inlineStr">
+      <c r="E20" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="F22" s="1" t="inlineStr">
+      <c r="F20" s="1" t="inlineStr">
         <is>
           <t>4200000</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-4/01.png | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-4/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-4/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-4/04.jpg</t>
         </is>
       </c>
-      <c r="H22" s="1" t="inlineStr">
+      <c r="H20" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="I22" s="1" t="inlineStr">
+      <c r="I20" s="1" t="inlineStr">
         <is>
           <t>Иван</t>
         </is>
       </c>
-      <c r="J22" s="1" t="inlineStr">
+      <c r="J20" s="1" t="inlineStr">
         <is>
           <t>info@bel-car.com</t>
         </is>
       </c>
-      <c r="K22" s="1" t="inlineStr">
+      <c r="K20" s="1" t="inlineStr">
         <is>
           <t>79031369484</t>
         </is>
       </c>
-      <c r="L22" s="1" t="inlineStr">
+      <c r="L20" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M22" s="1" t="inlineStr">
+      <c r="M20" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="N22" s="1" t="inlineStr">
+      <c r="N20" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="O22" s="1" t="inlineStr">
+      <c r="O20" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P22" s="1" t="inlineStr"/>
-      <c r="Q22" s="1" t="inlineStr">
+      <c r="P20" s="1" t="inlineStr">
         <is>
           <t>Барабанные</t>
         </is>
       </c>
-      <c r="R22" s="1" t="inlineStr"/>
-      <c r="S22" s="1" t="inlineStr"/>
-      <c r="T22" s="1" t="inlineStr">
+      <c r="Q20" s="1" t="inlineStr">
         <is>
           <t>ООО БелКар</t>
         </is>
       </c>
-      <c r="U22" s="1" t="inlineStr">
+      <c r="R20" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="V22" s="1" t="inlineStr">
+      <c r="S20" s="1" t="inlineStr">
         <is>
           <t>4200000</t>
         </is>
       </c>
-      <c r="W22" s="1" t="inlineStr">
+      <c r="T20" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X22" s="1" t="inlineStr">
+      <c r="U20" s="1" t="inlineStr">
         <is>
           <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
-      <c r="Y22" s="1" t="inlineStr"/>
-      <c r="Z22" s="1" t="inlineStr"/>
-      <c r="AA22" s="1" t="inlineStr"/>
-      <c r="AB22" s="1" t="inlineStr">
+      <c r="V20" s="1" t="inlineStr">
         <is>
           <t>28550</t>
         </is>
       </c>
-      <c r="AC22" s="1" t="inlineStr">
+      <c r="W20" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AD22" s="1" t="inlineStr">
+      <c r="X20" s="1" t="inlineStr">
         <is>
           <t>9595</t>
         </is>
       </c>
-      <c r="AE22" s="1" t="inlineStr"/>
-      <c r="AF22" s="1" t="inlineStr">
+      <c r="Y20" s="1" t="inlineStr">
         <is>
           <t>3 года или больше</t>
         </is>
       </c>
-      <c r="AG22" s="1" t="inlineStr">
+      <c r="Z20" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="AH22" s="1" t="inlineStr"/>
-      <c r="AI22" s="1" t="inlineStr">
+      <c r="AA20" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AJ22" s="1" t="inlineStr"/>
-      <c r="AK22" s="1" t="inlineStr">
+      <c r="AB20" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AL22" s="1" t="inlineStr">
+      <c r="AC20" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AM22" s="1" t="inlineStr">
+      <c r="AD20" s="1" t="inlineStr">
         <is>
           <t>10110</t>
         </is>
       </c>
-      <c r="AN22" s="1" t="inlineStr">
+      <c r="AE20" s="1" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="AO22" s="1" t="inlineStr"/>
-      <c r="AP22" s="1" t="inlineStr">
+      <c r="AF20" s="1" t="inlineStr">
         <is>
           <t>Самосвальный</t>
         </is>
       </c>
-      <c r="AQ22" s="1" t="inlineStr">
+      <c r="AG20" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AR22" s="1" t="inlineStr"/>
-      <c r="AS22" s="1" t="inlineStr">
+      <c r="AH20" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AT22" s="1" t="inlineStr">
+      <c r="AI20" s="1" t="inlineStr">
         <is>
           <t>420000</t>
         </is>
       </c>
-      <c r="AU22" s="1" t="inlineStr"/>
-      <c r="AV22" s="1" t="inlineStr"/>
-      <c r="AW22" s="1" t="inlineStr">
+      <c r="AJ20" s="1" t="inlineStr"/>
+      <c r="AK20" s="1" t="inlineStr"/>
+      <c r="AL20" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-9595</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп ломовоз Тонар SH4-74M (97465), 2026</t>
         </is>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D21" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар SH4-74M (97465) / 2026 года выпуска&lt;/strong&gt;
 &lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
@@ -5617,197 +4911,186 @@
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
         </is>
       </c>
-      <c r="E23" s="1" t="inlineStr">
+      <c r="E21" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="F23" s="1" t="inlineStr">
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>5200000</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-5/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-5/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-5/03.jpg</t>
         </is>
       </c>
-      <c r="H23" s="1" t="inlineStr">
+      <c r="H21" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="I23" s="1" t="inlineStr">
+      <c r="I21" s="1" t="inlineStr">
         <is>
           <t>Иван</t>
         </is>
       </c>
-      <c r="J23" s="1" t="inlineStr">
+      <c r="J21" s="1" t="inlineStr">
         <is>
           <t>info@bel-car.com</t>
         </is>
       </c>
-      <c r="K23" s="1" t="inlineStr">
+      <c r="K21" s="1" t="inlineStr">
         <is>
           <t>79031369484</t>
         </is>
       </c>
-      <c r="L23" s="1" t="inlineStr">
+      <c r="L21" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M23" s="1" t="inlineStr">
+      <c r="M21" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="N23" s="1" t="inlineStr">
+      <c r="N21" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="O23" s="1" t="inlineStr">
+      <c r="O21" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P23" s="1" t="inlineStr"/>
-      <c r="Q23" s="1" t="inlineStr">
+      <c r="P21" s="1" t="inlineStr">
         <is>
           <t>Барабанные</t>
         </is>
       </c>
-      <c r="R23" s="1" t="inlineStr"/>
-      <c r="S23" s="1" t="inlineStr"/>
-      <c r="T23" s="1" t="inlineStr">
+      <c r="Q21" s="1" t="inlineStr">
         <is>
           <t>ООО БелКар</t>
         </is>
       </c>
-      <c r="U23" s="1" t="inlineStr">
+      <c r="R21" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="V23" s="1" t="inlineStr">
+      <c r="S21" s="1" t="inlineStr">
         <is>
           <t>5200000</t>
         </is>
       </c>
-      <c r="W23" s="1" t="inlineStr">
+      <c r="T21" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X23" s="1" t="inlineStr">
+      <c r="U21" s="1" t="inlineStr">
         <is>
           <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
-      <c r="Y23" s="1" t="inlineStr"/>
-      <c r="Z23" s="1" t="inlineStr"/>
-      <c r="AA23" s="1" t="inlineStr"/>
-      <c r="AB23" s="1" t="inlineStr">
+      <c r="V21" s="1" t="inlineStr">
         <is>
           <t>49000</t>
         </is>
       </c>
-      <c r="AC23" s="1" t="inlineStr">
+      <c r="W21" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AD23" s="1" t="inlineStr">
+      <c r="X21" s="1" t="inlineStr">
         <is>
           <t>SH4-74M (97465)</t>
         </is>
       </c>
-      <c r="AE23" s="1" t="inlineStr"/>
-      <c r="AF23" s="1" t="inlineStr">
+      <c r="Y21" s="1" t="inlineStr">
         <is>
           <t>3 года или больше</t>
         </is>
       </c>
-      <c r="AG23" s="1" t="inlineStr">
+      <c r="Z21" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="AH23" s="1" t="inlineStr"/>
-      <c r="AI23" s="1" t="inlineStr">
+      <c r="AA21" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AJ23" s="1" t="inlineStr"/>
-      <c r="AK23" s="1" t="inlineStr">
+      <c r="AB21" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AL23" s="1" t="inlineStr">
+      <c r="AC21" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AM23" s="1" t="inlineStr">
+      <c r="AD21" s="1" t="inlineStr">
         <is>
           <t>14134</t>
         </is>
       </c>
-      <c r="AN23" s="1" t="inlineStr">
+      <c r="AE21" s="1" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="AO23" s="1" t="inlineStr"/>
-      <c r="AP23" s="1" t="inlineStr">
+      <c r="AF21" s="1" t="inlineStr">
         <is>
           <t>Ломовоз</t>
         </is>
       </c>
-      <c r="AQ23" s="1" t="inlineStr">
+      <c r="AG21" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AR23" s="1" t="inlineStr"/>
-      <c r="AS23" s="1" t="inlineStr">
+      <c r="AH21" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AT23" s="1" t="inlineStr">
+      <c r="AI21" s="1" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="AU23" s="1" t="inlineStr"/>
-      <c r="AV23" s="1" t="inlineStr"/>
-      <c r="AW23" s="1" t="inlineStr">
+      <c r="AJ21" s="1" t="inlineStr"/>
+      <c r="AK21" s="1" t="inlineStr"/>
+      <c r="AL21" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-sh4-74m-97465</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп контейнеровоз Тонар K4-U (99891), 2026</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr">
+      <c r="D22" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар K4-U (99891) / 2026 года выпуска&lt;/strong&gt;
 &lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
@@ -5846,197 +5129,186 @@
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
         </is>
       </c>
-      <c r="E24" s="1" t="inlineStr">
+      <c r="E22" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F22" s="1" t="inlineStr">
         <is>
           <t>3200000</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-9/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-9/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-9/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-9/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-9/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-9/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-9/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-9/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-9/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-9/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-9/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-9/12.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-9/13.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-9/14.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-9/15.jpg</t>
         </is>
       </c>
-      <c r="H24" s="1" t="inlineStr">
+      <c r="H22" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="I22" s="1" t="inlineStr">
         <is>
           <t>Иван</t>
         </is>
       </c>
-      <c r="J24" s="1" t="inlineStr">
+      <c r="J22" s="1" t="inlineStr">
         <is>
           <t>info@bel-car.com</t>
         </is>
       </c>
-      <c r="K24" s="1" t="inlineStr">
+      <c r="K22" s="1" t="inlineStr">
         <is>
           <t>79031369484</t>
         </is>
       </c>
-      <c r="L24" s="1" t="inlineStr">
+      <c r="L22" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M24" s="1" t="inlineStr">
+      <c r="M22" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="N24" s="1" t="inlineStr">
+      <c r="N22" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="O24" s="1" t="inlineStr">
+      <c r="O22" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P24" s="1" t="inlineStr"/>
-      <c r="Q24" s="1" t="inlineStr">
+      <c r="P22" s="1" t="inlineStr">
         <is>
           <t>Барабанные</t>
         </is>
       </c>
-      <c r="R24" s="1" t="inlineStr"/>
-      <c r="S24" s="1" t="inlineStr"/>
-      <c r="T24" s="1" t="inlineStr">
+      <c r="Q22" s="1" t="inlineStr">
         <is>
           <t>ООО БелКар</t>
         </is>
       </c>
-      <c r="U24" s="1" t="inlineStr">
+      <c r="R22" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="V24" s="1" t="inlineStr">
+      <c r="S22" s="1" t="inlineStr">
         <is>
           <t>3200000</t>
         </is>
       </c>
-      <c r="W24" s="1" t="inlineStr">
+      <c r="T22" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X24" s="1" t="inlineStr">
+      <c r="U22" s="1" t="inlineStr">
         <is>
           <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
-      <c r="Y24" s="1" t="inlineStr"/>
-      <c r="Z24" s="1" t="inlineStr"/>
-      <c r="AA24" s="1" t="inlineStr"/>
-      <c r="AB24" s="1" t="inlineStr">
+      <c r="V22" s="1" t="inlineStr">
         <is>
           <t>44000</t>
         </is>
       </c>
-      <c r="AC24" s="1" t="inlineStr">
+      <c r="W22" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AD24" s="1" t="inlineStr">
+      <c r="X22" s="1" t="inlineStr">
         <is>
           <t>K4-U (99891)</t>
         </is>
       </c>
-      <c r="AE24" s="1" t="inlineStr"/>
-      <c r="AF24" s="1" t="inlineStr">
+      <c r="Y22" s="1" t="inlineStr">
         <is>
           <t>3 года или больше</t>
         </is>
       </c>
-      <c r="AG24" s="1" t="inlineStr">
+      <c r="Z22" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="AH24" s="1" t="inlineStr"/>
-      <c r="AI24" s="1" t="inlineStr">
+      <c r="AA22" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AJ24" s="1" t="inlineStr"/>
-      <c r="AK24" s="1" t="inlineStr">
+      <c r="AB22" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AL24" s="1" t="inlineStr">
+      <c r="AC22" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AM24" s="1" t="inlineStr">
+      <c r="AD22" s="1" t="inlineStr">
         <is>
           <t>12192</t>
         </is>
       </c>
-      <c r="AN24" s="1" t="inlineStr"/>
-      <c r="AO24" s="1" t="inlineStr"/>
-      <c r="AP24" s="1" t="inlineStr">
+      <c r="AE22" s="1" t="inlineStr"/>
+      <c r="AF22" s="1" t="inlineStr">
         <is>
           <t>Контейнеровоз</t>
         </is>
       </c>
-      <c r="AQ24" s="1" t="inlineStr">
+      <c r="AG22" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AR24" s="1" t="inlineStr"/>
-      <c r="AS24" s="1" t="inlineStr">
+      <c r="AH22" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AT24" s="1" t="inlineStr">
+      <c r="AI22" s="1" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="AU24" s="1" t="inlineStr">
+      <c r="AJ22" s="1" t="inlineStr">
         <is>
           <t>160000</t>
         </is>
       </c>
-      <c r="AV24" s="1" t="inlineStr"/>
-      <c r="AW24" s="1" t="inlineStr">
+      <c r="AK22" s="1" t="inlineStr"/>
+      <c r="AL22" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-k4-u-99891</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
+      <c r="B23" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп бортовой Тонар B3-16 (98881), 2026</t>
         </is>
       </c>
-      <c r="D25" s="1" t="inlineStr">
+      <c r="D23" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар B3-16 (98881) / 2026 года выпуска&lt;/strong&gt;
 &lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
@@ -6072,189 +5344,178 @@
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
         </is>
       </c>
-      <c r="E25" s="1" t="inlineStr">
+      <c r="E23" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="F23" s="1" t="inlineStr">
         <is>
           <t>3300000</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_1/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_1/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_1/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_1/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_1/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_1/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_1/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_1/08.jpg</t>
         </is>
       </c>
-      <c r="H25" s="1" t="inlineStr">
+      <c r="H23" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="I25" s="1" t="inlineStr">
+      <c r="I23" s="1" t="inlineStr">
         <is>
           <t>Иван</t>
         </is>
       </c>
-      <c r="J25" s="1" t="inlineStr">
+      <c r="J23" s="1" t="inlineStr">
         <is>
           <t>info@bel-car.com</t>
         </is>
       </c>
-      <c r="K25" s="1" t="inlineStr">
+      <c r="K23" s="1" t="inlineStr">
         <is>
           <t>79031369484</t>
         </is>
       </c>
-      <c r="L25" s="1" t="inlineStr">
+      <c r="L23" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M25" s="1" t="inlineStr"/>
-      <c r="N25" s="1" t="inlineStr">
+      <c r="M23" s="1" t="inlineStr"/>
+      <c r="N23" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="O25" s="1" t="inlineStr">
+      <c r="O23" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P25" s="1" t="inlineStr"/>
-      <c r="Q25" s="1" t="inlineStr">
+      <c r="P23" s="1" t="inlineStr">
         <is>
           <t>Барабанные</t>
         </is>
       </c>
-      <c r="R25" s="1" t="inlineStr"/>
-      <c r="S25" s="1" t="inlineStr"/>
-      <c r="T25" s="1" t="inlineStr">
+      <c r="Q23" s="1" t="inlineStr">
         <is>
           <t>ООО БелКар</t>
         </is>
       </c>
-      <c r="U25" s="1" t="inlineStr">
+      <c r="R23" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="V25" s="1" t="inlineStr">
+      <c r="S23" s="1" t="inlineStr">
         <is>
           <t>3300000</t>
         </is>
       </c>
-      <c r="W25" s="1" t="inlineStr">
+      <c r="T23" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X25" s="1" t="inlineStr">
+      <c r="U23" s="1" t="inlineStr">
         <is>
           <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
-      <c r="Y25" s="1" t="inlineStr"/>
-      <c r="Z25" s="1" t="inlineStr"/>
-      <c r="AA25" s="1" t="inlineStr"/>
-      <c r="AB25" s="1" t="inlineStr">
+      <c r="V23" s="1" t="inlineStr">
         <is>
           <t>38600</t>
         </is>
       </c>
-      <c r="AC25" s="1" t="inlineStr">
+      <c r="W23" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AD25" s="1" t="inlineStr">
+      <c r="X23" s="1" t="inlineStr">
         <is>
           <t>B3-16 (98881)</t>
         </is>
       </c>
-      <c r="AE25" s="1" t="inlineStr"/>
-      <c r="AF25" s="1" t="inlineStr"/>
-      <c r="AG25" s="1" t="inlineStr">
+      <c r="Y23" s="1" t="inlineStr"/>
+      <c r="Z23" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="AH25" s="1" t="inlineStr"/>
-      <c r="AI25" s="1" t="inlineStr">
+      <c r="AA23" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AJ25" s="1" t="inlineStr"/>
-      <c r="AK25" s="1" t="inlineStr">
+      <c r="AB23" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AL25" s="1" t="inlineStr">
+      <c r="AC23" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AM25" s="1" t="inlineStr">
+      <c r="AD23" s="1" t="inlineStr">
         <is>
           <t>16500</t>
         </is>
       </c>
-      <c r="AN25" s="1" t="inlineStr"/>
-      <c r="AO25" s="1" t="inlineStr"/>
-      <c r="AP25" s="1" t="inlineStr">
+      <c r="AE23" s="1" t="inlineStr"/>
+      <c r="AF23" s="1" t="inlineStr">
         <is>
           <t>Бортовой</t>
         </is>
       </c>
-      <c r="AQ25" s="1" t="inlineStr">
+      <c r="AG23" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AR25" s="1" t="inlineStr"/>
-      <c r="AS25" s="1" t="inlineStr">
+      <c r="AH23" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AT25" s="1" t="inlineStr">
+      <c r="AI23" s="1" t="inlineStr">
         <is>
           <t>330000</t>
         </is>
       </c>
-      <c r="AU25" s="1" t="inlineStr">
+      <c r="AJ23" s="1" t="inlineStr">
         <is>
           <t>330000</t>
         </is>
       </c>
-      <c r="AV25" s="1" t="inlineStr"/>
-      <c r="AW25" s="1" t="inlineStr">
+      <c r="AK23" s="1" t="inlineStr"/>
+      <c r="AL23" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-b3-16-98881</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
+      <c r="B24" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп самосвальный Тонар SH3-33 (95892), 2026</t>
         </is>
       </c>
-      <c r="D26" s="1" t="inlineStr">
+      <c r="D24" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар SH3-33 (95892) / 2026 года выпуска&lt;/strong&gt;
 &lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
@@ -6302,189 +5563,178 @@
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
         </is>
       </c>
-      <c r="E26" s="1" t="inlineStr">
+      <c r="E24" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="F26" s="1" t="inlineStr">
+      <c r="F24" s="1" t="inlineStr">
         <is>
           <t>3900000</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_11/01.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_11/02.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_11/03.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_11/04.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_11/05.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_11/06.webp</t>
         </is>
       </c>
-      <c r="H26" s="1" t="inlineStr">
+      <c r="H24" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="I26" s="1" t="inlineStr">
+      <c r="I24" s="1" t="inlineStr">
         <is>
           <t>Иван</t>
         </is>
       </c>
-      <c r="J26" s="1" t="inlineStr">
+      <c r="J24" s="1" t="inlineStr">
         <is>
           <t>info@bel-car.com</t>
         </is>
       </c>
-      <c r="K26" s="1" t="inlineStr">
+      <c r="K24" s="1" t="inlineStr">
         <is>
           <t>79031369484</t>
         </is>
       </c>
-      <c r="L26" s="1" t="inlineStr">
+      <c r="L24" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M26" s="1" t="inlineStr"/>
-      <c r="N26" s="1" t="inlineStr">
+      <c r="M24" s="1" t="inlineStr"/>
+      <c r="N24" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="O26" s="1" t="inlineStr">
+      <c r="O24" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P26" s="1" t="inlineStr"/>
-      <c r="Q26" s="1" t="inlineStr">
+      <c r="P24" s="1" t="inlineStr">
         <is>
           <t>Барабанные</t>
         </is>
       </c>
-      <c r="R26" s="1" t="inlineStr"/>
-      <c r="S26" s="1" t="inlineStr"/>
-      <c r="T26" s="1" t="inlineStr">
+      <c r="Q24" s="1" t="inlineStr">
         <is>
           <t>ООО БелКар</t>
         </is>
       </c>
-      <c r="U26" s="1" t="inlineStr">
+      <c r="R24" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="V26" s="1" t="inlineStr">
+      <c r="S24" s="1" t="inlineStr">
         <is>
           <t>3900000</t>
         </is>
       </c>
-      <c r="W26" s="1" t="inlineStr">
+      <c r="T24" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X26" s="1" t="inlineStr">
+      <c r="U24" s="1" t="inlineStr">
         <is>
           <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
-      <c r="Y26" s="1" t="inlineStr"/>
-      <c r="Z26" s="1" t="inlineStr"/>
-      <c r="AA26" s="1" t="inlineStr"/>
-      <c r="AB26" s="1" t="inlineStr">
+      <c r="V24" s="1" t="inlineStr">
         <is>
           <t>37500</t>
         </is>
       </c>
-      <c r="AC26" s="1" t="inlineStr">
+      <c r="W24" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AD26" s="1" t="inlineStr">
+      <c r="X24" s="1" t="inlineStr">
         <is>
           <t>SH3-33 (95892)</t>
         </is>
       </c>
-      <c r="AE26" s="1" t="inlineStr"/>
-      <c r="AF26" s="1" t="inlineStr"/>
-      <c r="AG26" s="1" t="inlineStr">
+      <c r="Y24" s="1" t="inlineStr"/>
+      <c r="Z24" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="AH26" s="1" t="inlineStr"/>
-      <c r="AI26" s="1" t="inlineStr">
+      <c r="AA24" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AJ26" s="1" t="inlineStr"/>
-      <c r="AK26" s="1" t="inlineStr">
+      <c r="AB24" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AL26" s="1" t="inlineStr">
+      <c r="AC24" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AM26" s="1" t="inlineStr">
+      <c r="AD24" s="1" t="inlineStr">
         <is>
           <t>10965</t>
         </is>
       </c>
-      <c r="AN26" s="1" t="inlineStr">
+      <c r="AE24" s="1" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="AO26" s="1" t="inlineStr"/>
-      <c r="AP26" s="1" t="inlineStr">
+      <c r="AF24" s="1" t="inlineStr">
         <is>
           <t>Самосвальный</t>
         </is>
       </c>
-      <c r="AQ26" s="1" t="inlineStr">
+      <c r="AG24" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AR26" s="1" t="inlineStr"/>
-      <c r="AS26" s="1" t="inlineStr">
+      <c r="AH24" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AT26" s="1" t="inlineStr">
+      <c r="AI24" s="1" t="inlineStr">
         <is>
           <t>390000</t>
         </is>
       </c>
-      <c r="AU26" s="1" t="inlineStr"/>
-      <c r="AV26" s="1" t="inlineStr"/>
-      <c r="AW26" s="1" t="inlineStr">
+      <c r="AJ24" s="1" t="inlineStr"/>
+      <c r="AK24" s="1" t="inlineStr"/>
+      <c r="AL24" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-sh3-33-95892-10965</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп самосвальный Тонар SH4-38 (95234), 2026</t>
         </is>
       </c>
-      <c r="D27" s="1" t="inlineStr">
+      <c r="D25" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар SH4-38 (95234) / 2026 года выпуска&lt;/strong&gt;
 &lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
@@ -6530,189 +5780,178 @@
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
         </is>
       </c>
-      <c r="E27" s="1" t="inlineStr">
+      <c r="E25" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="F27" s="1" t="inlineStr">
+      <c r="F25" s="1" t="inlineStr">
         <is>
           <t>4700000</t>
         </is>
       </c>
-      <c r="G27" s="1" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_13/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_13/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_13/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_13/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_13/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_13/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_13/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_13/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_13/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_13/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_13/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_13/12.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_13/13.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_13/14.jpg</t>
         </is>
       </c>
-      <c r="H27" s="1" t="inlineStr">
+      <c r="H25" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="I27" s="1" t="inlineStr">
+      <c r="I25" s="1" t="inlineStr">
         <is>
           <t>Иван</t>
         </is>
       </c>
-      <c r="J27" s="1" t="inlineStr">
+      <c r="J25" s="1" t="inlineStr">
         <is>
           <t>info@bel-car.com</t>
         </is>
       </c>
-      <c r="K27" s="1" t="inlineStr">
+      <c r="K25" s="1" t="inlineStr">
         <is>
           <t>79031369484</t>
         </is>
       </c>
-      <c r="L27" s="1" t="inlineStr">
+      <c r="L25" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M27" s="1" t="inlineStr"/>
-      <c r="N27" s="1" t="inlineStr">
+      <c r="M25" s="1" t="inlineStr"/>
+      <c r="N25" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="O27" s="1" t="inlineStr">
+      <c r="O25" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P27" s="1" t="inlineStr"/>
-      <c r="Q27" s="1" t="inlineStr">
+      <c r="P25" s="1" t="inlineStr">
         <is>
           <t>Барабанные</t>
         </is>
       </c>
-      <c r="R27" s="1" t="inlineStr"/>
-      <c r="S27" s="1" t="inlineStr"/>
-      <c r="T27" s="1" t="inlineStr">
+      <c r="Q25" s="1" t="inlineStr">
         <is>
           <t>ООО БелКар</t>
         </is>
       </c>
-      <c r="U27" s="1" t="inlineStr">
+      <c r="R25" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="V27" s="1" t="inlineStr">
+      <c r="S25" s="1" t="inlineStr">
         <is>
           <t>4700000</t>
         </is>
       </c>
-      <c r="W27" s="1" t="inlineStr">
+      <c r="T25" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X27" s="1" t="inlineStr">
+      <c r="U25" s="1" t="inlineStr">
         <is>
           <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
-      <c r="Y27" s="1" t="inlineStr"/>
-      <c r="Z27" s="1" t="inlineStr"/>
-      <c r="AA27" s="1" t="inlineStr"/>
-      <c r="AB27" s="1" t="inlineStr">
+      <c r="V25" s="1" t="inlineStr">
         <is>
           <t>48070</t>
         </is>
       </c>
-      <c r="AC27" s="1" t="inlineStr">
+      <c r="W25" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AD27" s="1" t="inlineStr">
+      <c r="X25" s="1" t="inlineStr">
         <is>
           <t>SH4-38 (95234)</t>
         </is>
       </c>
-      <c r="AE27" s="1" t="inlineStr"/>
-      <c r="AF27" s="1" t="inlineStr"/>
-      <c r="AG27" s="1" t="inlineStr">
+      <c r="Y25" s="1" t="inlineStr"/>
+      <c r="Z25" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="AH27" s="1" t="inlineStr"/>
-      <c r="AI27" s="1" t="inlineStr">
+      <c r="AA25" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AJ27" s="1" t="inlineStr"/>
-      <c r="AK27" s="1" t="inlineStr">
+      <c r="AB25" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AL27" s="1" t="inlineStr">
+      <c r="AC25" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AM27" s="1" t="inlineStr">
+      <c r="AD25" s="1" t="inlineStr">
         <is>
           <t>11996</t>
         </is>
       </c>
-      <c r="AN27" s="1" t="inlineStr">
+      <c r="AE25" s="1" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="AO27" s="1" t="inlineStr"/>
-      <c r="AP27" s="1" t="inlineStr">
+      <c r="AF25" s="1" t="inlineStr">
         <is>
           <t>Самосвальный</t>
         </is>
       </c>
-      <c r="AQ27" s="1" t="inlineStr">
+      <c r="AG25" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AR27" s="1" t="inlineStr"/>
-      <c r="AS27" s="1" t="inlineStr">
+      <c r="AH25" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AT27" s="1" t="inlineStr">
+      <c r="AI25" s="1" t="inlineStr">
         <is>
           <t>470000</t>
         </is>
       </c>
-      <c r="AU27" s="1" t="inlineStr"/>
-      <c r="AV27" s="1" t="inlineStr"/>
-      <c r="AW27" s="1" t="inlineStr">
+      <c r="AJ25" s="1" t="inlineStr"/>
+      <c r="AK25" s="1" t="inlineStr"/>
+      <c r="AL25" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-sh4-38-95234</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
+      <c r="B26" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп самосвальный Тонар SH4-45 (95234), 2026</t>
         </is>
       </c>
-      <c r="D28" s="1" t="inlineStr">
+      <c r="D26" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар SH4-45 (95234) / 2026 года выпуска&lt;/strong&gt;
 &lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
@@ -6759,189 +5998,178 @@
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
         </is>
       </c>
-      <c r="E28" s="1" t="inlineStr">
+      <c r="E26" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr">
+      <c r="F26" s="1" t="inlineStr">
         <is>
           <t>4800000</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_14/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_14/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_14/03.jpg</t>
         </is>
       </c>
-      <c r="H28" s="1" t="inlineStr">
+      <c r="H26" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="I28" s="1" t="inlineStr">
+      <c r="I26" s="1" t="inlineStr">
         <is>
           <t>Иван</t>
         </is>
       </c>
-      <c r="J28" s="1" t="inlineStr">
+      <c r="J26" s="1" t="inlineStr">
         <is>
           <t>info@bel-car.com</t>
         </is>
       </c>
-      <c r="K28" s="1" t="inlineStr">
+      <c r="K26" s="1" t="inlineStr">
         <is>
           <t>79031369484</t>
         </is>
       </c>
-      <c r="L28" s="1" t="inlineStr">
+      <c r="L26" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M28" s="1" t="inlineStr"/>
-      <c r="N28" s="1" t="inlineStr">
+      <c r="M26" s="1" t="inlineStr"/>
+      <c r="N26" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="O28" s="1" t="inlineStr">
+      <c r="O26" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P28" s="1" t="inlineStr"/>
-      <c r="Q28" s="1" t="inlineStr">
+      <c r="P26" s="1" t="inlineStr">
         <is>
           <t>Барабанные</t>
         </is>
       </c>
-      <c r="R28" s="1" t="inlineStr"/>
-      <c r="S28" s="1" t="inlineStr"/>
-      <c r="T28" s="1" t="inlineStr">
+      <c r="Q26" s="1" t="inlineStr">
         <is>
           <t>ООО БелКар</t>
         </is>
       </c>
-      <c r="U28" s="1" t="inlineStr">
+      <c r="R26" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="V28" s="1" t="inlineStr">
+      <c r="S26" s="1" t="inlineStr">
         <is>
           <t>4800000</t>
         </is>
       </c>
-      <c r="W28" s="1" t="inlineStr">
+      <c r="T26" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X28" s="1" t="inlineStr">
+      <c r="U26" s="1" t="inlineStr">
         <is>
           <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
-      <c r="Y28" s="1" t="inlineStr"/>
-      <c r="Z28" s="1" t="inlineStr"/>
-      <c r="AA28" s="1" t="inlineStr"/>
-      <c r="AB28" s="1" t="inlineStr">
+      <c r="V26" s="1" t="inlineStr">
         <is>
           <t>48070</t>
         </is>
       </c>
-      <c r="AC28" s="1" t="inlineStr">
+      <c r="W26" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AD28" s="1" t="inlineStr">
+      <c r="X26" s="1" t="inlineStr">
         <is>
           <t>SH4-45 (95234)</t>
         </is>
       </c>
-      <c r="AE28" s="1" t="inlineStr"/>
-      <c r="AF28" s="1" t="inlineStr"/>
-      <c r="AG28" s="1" t="inlineStr">
+      <c r="Y26" s="1" t="inlineStr"/>
+      <c r="Z26" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="AH28" s="1" t="inlineStr"/>
-      <c r="AI28" s="1" t="inlineStr">
+      <c r="AA26" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AJ28" s="1" t="inlineStr"/>
-      <c r="AK28" s="1" t="inlineStr">
+      <c r="AB26" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AL28" s="1" t="inlineStr">
+      <c r="AC26" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AM28" s="1" t="inlineStr">
+      <c r="AD26" s="1" t="inlineStr">
         <is>
           <t>11996</t>
         </is>
       </c>
-      <c r="AN28" s="1" t="inlineStr">
+      <c r="AE26" s="1" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="AO28" s="1" t="inlineStr"/>
-      <c r="AP28" s="1" t="inlineStr">
+      <c r="AF26" s="1" t="inlineStr">
         <is>
           <t>Самосвальный</t>
         </is>
       </c>
-      <c r="AQ28" s="1" t="inlineStr">
+      <c r="AG26" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AR28" s="1" t="inlineStr"/>
-      <c r="AS28" s="1" t="inlineStr">
+      <c r="AH26" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AT28" s="1" t="inlineStr">
+      <c r="AI26" s="1" t="inlineStr">
         <is>
           <t>480000</t>
         </is>
       </c>
-      <c r="AU28" s="1" t="inlineStr"/>
-      <c r="AV28" s="1" t="inlineStr"/>
-      <c r="AW28" s="1" t="inlineStr">
+      <c r="AJ26" s="1" t="inlineStr"/>
+      <c r="AK26" s="1" t="inlineStr"/>
+      <c r="AL26" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-sh4-45-95234</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
+      <c r="B27" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп самосвальный Тонар SH4-60M/SH4-60 (952342), 2026</t>
         </is>
       </c>
-      <c r="D29" s="1" t="inlineStr">
+      <c r="D27" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар SH4-60M/SH4-60 (952342) / 2026 года выпуска&lt;/strong&gt;
 &lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
@@ -6984,189 +6212,178 @@
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
         </is>
       </c>
-      <c r="E29" s="1" t="inlineStr">
+      <c r="E27" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="F29" s="1" t="inlineStr">
+      <c r="F27" s="1" t="inlineStr">
         <is>
           <t>5700000</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
+      <c r="G27" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_15/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_15/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_15/03.jpg</t>
         </is>
       </c>
-      <c r="H29" s="1" t="inlineStr">
+      <c r="H27" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="I29" s="1" t="inlineStr">
+      <c r="I27" s="1" t="inlineStr">
         <is>
           <t>Иван</t>
         </is>
       </c>
-      <c r="J29" s="1" t="inlineStr">
+      <c r="J27" s="1" t="inlineStr">
         <is>
           <t>info@bel-car.com</t>
         </is>
       </c>
-      <c r="K29" s="1" t="inlineStr">
+      <c r="K27" s="1" t="inlineStr">
         <is>
           <t>79031369484</t>
         </is>
       </c>
-      <c r="L29" s="1" t="inlineStr">
+      <c r="L27" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M29" s="1" t="inlineStr"/>
-      <c r="N29" s="1" t="inlineStr">
+      <c r="M27" s="1" t="inlineStr"/>
+      <c r="N27" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="O29" s="1" t="inlineStr">
+      <c r="O27" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P29" s="1" t="inlineStr"/>
-      <c r="Q29" s="1" t="inlineStr">
+      <c r="P27" s="1" t="inlineStr">
         <is>
           <t>Барабанные</t>
         </is>
       </c>
-      <c r="R29" s="1" t="inlineStr"/>
-      <c r="S29" s="1" t="inlineStr"/>
-      <c r="T29" s="1" t="inlineStr">
+      <c r="Q27" s="1" t="inlineStr">
         <is>
           <t>ООО БелКар</t>
         </is>
       </c>
-      <c r="U29" s="1" t="inlineStr">
+      <c r="R27" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="V29" s="1" t="inlineStr">
+      <c r="S27" s="1" t="inlineStr">
         <is>
           <t>5700000</t>
         </is>
       </c>
-      <c r="W29" s="1" t="inlineStr">
+      <c r="T27" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X29" s="1" t="inlineStr">
+      <c r="U27" s="1" t="inlineStr">
         <is>
           <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
-      <c r="Y29" s="1" t="inlineStr"/>
-      <c r="Z29" s="1" t="inlineStr"/>
-      <c r="AA29" s="1" t="inlineStr"/>
-      <c r="AB29" s="1" t="inlineStr">
+      <c r="V27" s="1" t="inlineStr">
         <is>
           <t>51500</t>
         </is>
       </c>
-      <c r="AC29" s="1" t="inlineStr">
+      <c r="W27" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AD29" s="1" t="inlineStr">
+      <c r="X27" s="1" t="inlineStr">
         <is>
           <t>SH4-60M/SH4-60 (952342)</t>
         </is>
       </c>
-      <c r="AE29" s="1" t="inlineStr"/>
-      <c r="AF29" s="1" t="inlineStr"/>
-      <c r="AG29" s="1" t="inlineStr">
+      <c r="Y27" s="1" t="inlineStr"/>
+      <c r="Z27" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="AH29" s="1" t="inlineStr"/>
-      <c r="AI29" s="1" t="inlineStr">
+      <c r="AA27" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AJ29" s="1" t="inlineStr"/>
-      <c r="AK29" s="1" t="inlineStr">
+      <c r="AB27" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AL29" s="1" t="inlineStr">
+      <c r="AC27" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AM29" s="1" t="inlineStr">
+      <c r="AD27" s="1" t="inlineStr">
         <is>
           <t>13150</t>
         </is>
       </c>
-      <c r="AN29" s="1" t="inlineStr">
+      <c r="AE27" s="1" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="AO29" s="1" t="inlineStr"/>
-      <c r="AP29" s="1" t="inlineStr">
+      <c r="AF27" s="1" t="inlineStr">
         <is>
           <t>Самосвальный</t>
         </is>
       </c>
-      <c r="AQ29" s="1" t="inlineStr">
+      <c r="AG27" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AR29" s="1" t="inlineStr"/>
-      <c r="AS29" s="1" t="inlineStr">
+      <c r="AH27" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AT29" s="1" t="inlineStr">
+      <c r="AI27" s="1" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="AU29" s="1" t="inlineStr"/>
-      <c r="AV29" s="1" t="inlineStr"/>
-      <c r="AW29" s="1" t="inlineStr">
+      <c r="AJ27" s="1" t="inlineStr"/>
+      <c r="AK27" s="1" t="inlineStr"/>
+      <c r="AL27" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-sh4-60m-sh4-60-952342</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
+      <c r="B28" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп ломовоз Тонар SH3-74M (97464), 2026</t>
         </is>
       </c>
-      <c r="D30" s="1" t="inlineStr">
+      <c r="D28" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар SH3-74M (97464) / 2026 года выпуска&lt;/strong&gt;
 &lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
@@ -7208,189 +6425,178 @@
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
         </is>
       </c>
-      <c r="E30" s="1" t="inlineStr">
+      <c r="E28" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="F30" s="1" t="inlineStr">
+      <c r="F28" s="1" t="inlineStr">
         <is>
           <t>4700000</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_16/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_16/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_16/03.jpg</t>
         </is>
       </c>
-      <c r="H30" s="1" t="inlineStr">
+      <c r="H28" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="I30" s="1" t="inlineStr">
+      <c r="I28" s="1" t="inlineStr">
         <is>
           <t>Иван</t>
         </is>
       </c>
-      <c r="J30" s="1" t="inlineStr">
+      <c r="J28" s="1" t="inlineStr">
         <is>
           <t>info@bel-car.com</t>
         </is>
       </c>
-      <c r="K30" s="1" t="inlineStr">
+      <c r="K28" s="1" t="inlineStr">
         <is>
           <t>79031369484</t>
         </is>
       </c>
-      <c r="L30" s="1" t="inlineStr">
+      <c r="L28" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M30" s="1" t="inlineStr"/>
-      <c r="N30" s="1" t="inlineStr">
+      <c r="M28" s="1" t="inlineStr"/>
+      <c r="N28" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="O30" s="1" t="inlineStr">
+      <c r="O28" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P30" s="1" t="inlineStr"/>
-      <c r="Q30" s="1" t="inlineStr">
+      <c r="P28" s="1" t="inlineStr">
         <is>
           <t>Барабанные</t>
         </is>
       </c>
-      <c r="R30" s="1" t="inlineStr"/>
-      <c r="S30" s="1" t="inlineStr"/>
-      <c r="T30" s="1" t="inlineStr">
+      <c r="Q28" s="1" t="inlineStr">
         <is>
           <t>ООО БелКар</t>
         </is>
       </c>
-      <c r="U30" s="1" t="inlineStr">
+      <c r="R28" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="V30" s="1" t="inlineStr">
+      <c r="S28" s="1" t="inlineStr">
         <is>
           <t>4700000</t>
         </is>
       </c>
-      <c r="W30" s="1" t="inlineStr">
+      <c r="T28" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X30" s="1" t="inlineStr">
+      <c r="U28" s="1" t="inlineStr">
         <is>
           <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
-      <c r="Y30" s="1" t="inlineStr"/>
-      <c r="Z30" s="1" t="inlineStr"/>
-      <c r="AA30" s="1" t="inlineStr"/>
-      <c r="AB30" s="1" t="inlineStr">
+      <c r="V28" s="1" t="inlineStr">
         <is>
           <t>39000</t>
         </is>
       </c>
-      <c r="AC30" s="1" t="inlineStr">
+      <c r="W28" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AD30" s="1" t="inlineStr">
+      <c r="X28" s="1" t="inlineStr">
         <is>
           <t>SH3-74M (97464)</t>
         </is>
       </c>
-      <c r="AE30" s="1" t="inlineStr"/>
-      <c r="AF30" s="1" t="inlineStr"/>
-      <c r="AG30" s="1" t="inlineStr">
+      <c r="Y28" s="1" t="inlineStr"/>
+      <c r="Z28" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="AH30" s="1" t="inlineStr"/>
-      <c r="AI30" s="1" t="inlineStr">
+      <c r="AA28" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AJ30" s="1" t="inlineStr"/>
-      <c r="AK30" s="1" t="inlineStr">
+      <c r="AB28" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AL30" s="1" t="inlineStr">
+      <c r="AC28" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AM30" s="1" t="inlineStr">
+      <c r="AD28" s="1" t="inlineStr">
         <is>
           <t>13865</t>
         </is>
       </c>
-      <c r="AN30" s="1" t="inlineStr">
+      <c r="AE28" s="1" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="AO30" s="1" t="inlineStr"/>
-      <c r="AP30" s="1" t="inlineStr">
+      <c r="AF28" s="1" t="inlineStr">
         <is>
           <t>Ломовоз</t>
         </is>
       </c>
-      <c r="AQ30" s="1" t="inlineStr">
+      <c r="AG28" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AR30" s="1" t="inlineStr"/>
-      <c r="AS30" s="1" t="inlineStr">
+      <c r="AH28" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AT30" s="1" t="inlineStr">
+      <c r="AI28" s="1" t="inlineStr">
         <is>
           <t>470000</t>
         </is>
       </c>
-      <c r="AU30" s="1" t="inlineStr"/>
-      <c r="AV30" s="1" t="inlineStr"/>
-      <c r="AW30" s="1" t="inlineStr">
+      <c r="AJ28" s="1" t="inlineStr"/>
+      <c r="AK28" s="1" t="inlineStr"/>
+      <c r="AL28" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-sh3-74m-97464</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
+      <c r="B29" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп самосвальный Тонар SH3-33G (95892), 2026</t>
         </is>
       </c>
-      <c r="D31" s="1" t="inlineStr">
+      <c r="D29" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар SH3-33G (95892) / 2026 года выпуска&lt;/strong&gt;
 &lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
@@ -7438,193 +6644,182 @@
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
         </is>
       </c>
-      <c r="E31" s="1" t="inlineStr">
+      <c r="E29" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="F31" s="1" t="inlineStr">
+      <c r="F29" s="1" t="inlineStr">
         <is>
           <t>3900000</t>
         </is>
       </c>
-      <c r="G31" s="1" t="inlineStr">
+      <c r="G29" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_19/01.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_19/02.webp</t>
         </is>
       </c>
-      <c r="H31" s="1" t="inlineStr">
+      <c r="H29" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="I31" s="1" t="inlineStr">
+      <c r="I29" s="1" t="inlineStr">
         <is>
           <t>Иван</t>
         </is>
       </c>
-      <c r="J31" s="1" t="inlineStr">
+      <c r="J29" s="1" t="inlineStr">
         <is>
           <t>info@bel-car.com</t>
         </is>
       </c>
-      <c r="K31" s="1" t="inlineStr">
+      <c r="K29" s="1" t="inlineStr">
         <is>
           <t>79031369484</t>
         </is>
       </c>
-      <c r="L31" s="1" t="inlineStr">
+      <c r="L29" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M31" s="1" t="inlineStr"/>
-      <c r="N31" s="1" t="inlineStr">
+      <c r="M29" s="1" t="inlineStr"/>
+      <c r="N29" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="O31" s="1" t="inlineStr">
+      <c r="O29" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P31" s="1" t="inlineStr"/>
-      <c r="Q31" s="1" t="inlineStr">
+      <c r="P29" s="1" t="inlineStr">
         <is>
           <t>Барабанные</t>
         </is>
       </c>
-      <c r="R31" s="1" t="inlineStr"/>
-      <c r="S31" s="1" t="inlineStr"/>
-      <c r="T31" s="1" t="inlineStr">
+      <c r="Q29" s="1" t="inlineStr">
         <is>
           <t>ООО БелКар</t>
         </is>
       </c>
-      <c r="U31" s="1" t="inlineStr">
+      <c r="R29" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="V31" s="1" t="inlineStr">
+      <c r="S29" s="1" t="inlineStr">
         <is>
           <t>3900000</t>
         </is>
       </c>
-      <c r="W31" s="1" t="inlineStr">
+      <c r="T29" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X31" s="1" t="inlineStr">
+      <c r="U29" s="1" t="inlineStr">
         <is>
           <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
-      <c r="Y31" s="1" t="inlineStr"/>
-      <c r="Z31" s="1" t="inlineStr"/>
-      <c r="AA31" s="1" t="inlineStr"/>
-      <c r="AB31" s="1" t="inlineStr">
+      <c r="V29" s="1" t="inlineStr">
         <is>
           <t>28200</t>
         </is>
       </c>
-      <c r="AC31" s="1" t="inlineStr">
+      <c r="W29" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AD31" s="1" t="inlineStr">
+      <c r="X29" s="1" t="inlineStr">
         <is>
           <t>SH3-33 (95892)</t>
         </is>
       </c>
-      <c r="AE31" s="1" t="inlineStr"/>
-      <c r="AF31" s="1" t="inlineStr"/>
-      <c r="AG31" s="1" t="inlineStr">
+      <c r="Y29" s="1" t="inlineStr"/>
+      <c r="Z29" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="AH31" s="1" t="inlineStr"/>
-      <c r="AI31" s="1" t="inlineStr">
+      <c r="AA29" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AJ31" s="1" t="inlineStr"/>
-      <c r="AK31" s="1" t="inlineStr">
+      <c r="AB29" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AL31" s="1" t="inlineStr">
+      <c r="AC29" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AM31" s="1" t="inlineStr">
+      <c r="AD29" s="1" t="inlineStr">
         <is>
           <t>10965</t>
         </is>
       </c>
-      <c r="AN31" s="1" t="inlineStr">
+      <c r="AE29" s="1" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="AO31" s="1" t="inlineStr"/>
-      <c r="AP31" s="1" t="inlineStr">
+      <c r="AF29" s="1" t="inlineStr">
         <is>
           <t>Самосвальный</t>
         </is>
       </c>
-      <c r="AQ31" s="1" t="inlineStr">
+      <c r="AG29" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AR31" s="1" t="inlineStr"/>
-      <c r="AS31" s="1" t="inlineStr">
+      <c r="AH29" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AT31" s="1" t="inlineStr">
+      <c r="AI29" s="1" t="inlineStr">
         <is>
           <t>390000</t>
         </is>
       </c>
-      <c r="AU31" s="1" t="inlineStr"/>
-      <c r="AV31" s="1" t="inlineStr">
+      <c r="AJ29" s="1" t="inlineStr"/>
+      <c r="AK29" s="1" t="inlineStr">
         <is>
           <t>Без ограничения по пробегу</t>
         </is>
       </c>
-      <c r="AW31" s="1" t="inlineStr">
+      <c r="AL29" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-sh3-33-95892</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
+      <c r="B30" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп контейнеровоз Тонар K3-20 (99883), 2026</t>
         </is>
       </c>
-      <c r="D32" s="1" t="inlineStr">
+      <c r="D30" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар K3-20 (99883) / 2026 года выпуска&lt;/strong&gt;
 &lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
@@ -7663,189 +6858,178 @@
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
         </is>
       </c>
-      <c r="E32" s="1" t="inlineStr">
+      <c r="E30" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="F32" s="1" t="inlineStr">
+      <c r="F30" s="1" t="inlineStr">
         <is>
           <t>2250000</t>
         </is>
       </c>
-      <c r="G32" s="1" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_24/01.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_24/02.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_24/03.webp</t>
         </is>
       </c>
-      <c r="H32" s="1" t="inlineStr">
+      <c r="H30" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="I32" s="1" t="inlineStr">
+      <c r="I30" s="1" t="inlineStr">
         <is>
           <t>Иван</t>
         </is>
       </c>
-      <c r="J32" s="1" t="inlineStr">
+      <c r="J30" s="1" t="inlineStr">
         <is>
           <t>info@bel-car.com</t>
         </is>
       </c>
-      <c r="K32" s="1" t="inlineStr">
+      <c r="K30" s="1" t="inlineStr">
         <is>
           <t>79031369484</t>
         </is>
       </c>
-      <c r="L32" s="1" t="inlineStr">
+      <c r="L30" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M32" s="1" t="inlineStr"/>
-      <c r="N32" s="1" t="inlineStr">
+      <c r="M30" s="1" t="inlineStr"/>
+      <c r="N30" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="O32" s="1" t="inlineStr">
+      <c r="O30" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P32" s="1" t="inlineStr"/>
-      <c r="Q32" s="1" t="inlineStr">
+      <c r="P30" s="1" t="inlineStr">
         <is>
           <t>Дисковые</t>
         </is>
       </c>
-      <c r="R32" s="1" t="inlineStr"/>
-      <c r="S32" s="1" t="inlineStr"/>
-      <c r="T32" s="1" t="inlineStr">
+      <c r="Q30" s="1" t="inlineStr">
         <is>
           <t>ООО БелКар</t>
         </is>
       </c>
-      <c r="U32" s="1" t="inlineStr">
+      <c r="R30" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="V32" s="1" t="inlineStr">
+      <c r="S30" s="1" t="inlineStr">
         <is>
           <t>2250000</t>
         </is>
       </c>
-      <c r="W32" s="1" t="inlineStr">
+      <c r="T30" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X32" s="1" t="inlineStr">
+      <c r="U30" s="1" t="inlineStr">
         <is>
           <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
-      <c r="Y32" s="1" t="inlineStr"/>
-      <c r="Z32" s="1" t="inlineStr"/>
-      <c r="AA32" s="1" t="inlineStr"/>
-      <c r="AB32" s="1" t="inlineStr">
+      <c r="V30" s="1" t="inlineStr">
         <is>
           <t>40100</t>
         </is>
       </c>
-      <c r="AC32" s="1" t="inlineStr">
+      <c r="W30" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AD32" s="1" t="inlineStr">
+      <c r="X30" s="1" t="inlineStr">
         <is>
           <t>K3-20 (99883)</t>
         </is>
       </c>
-      <c r="AE32" s="1" t="inlineStr"/>
-      <c r="AF32" s="1" t="inlineStr"/>
-      <c r="AG32" s="1" t="inlineStr">
+      <c r="Y30" s="1" t="inlineStr"/>
+      <c r="Z30" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="AH32" s="1" t="inlineStr"/>
-      <c r="AI32" s="1" t="inlineStr">
+      <c r="AA30" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AJ32" s="1" t="inlineStr"/>
-      <c r="AK32" s="1" t="inlineStr">
+      <c r="AB30" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AL32" s="1" t="inlineStr">
+      <c r="AC30" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AM32" s="1" t="inlineStr">
+      <c r="AD30" s="1" t="inlineStr">
         <is>
           <t>9076</t>
         </is>
       </c>
-      <c r="AN32" s="1" t="inlineStr"/>
-      <c r="AO32" s="1" t="inlineStr"/>
-      <c r="AP32" s="1" t="inlineStr">
+      <c r="AE30" s="1" t="inlineStr"/>
+      <c r="AF30" s="1" t="inlineStr">
         <is>
           <t>Контейнеровоз</t>
         </is>
       </c>
-      <c r="AQ32" s="1" t="inlineStr">
+      <c r="AG30" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AR32" s="1" t="inlineStr"/>
-      <c r="AS32" s="1" t="inlineStr">
+      <c r="AH30" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AT32" s="1" t="inlineStr">
+      <c r="AI30" s="1" t="inlineStr">
         <is>
           <t>225000</t>
         </is>
       </c>
-      <c r="AU32" s="1" t="inlineStr">
+      <c r="AJ30" s="1" t="inlineStr">
         <is>
           <t>112500</t>
         </is>
       </c>
-      <c r="AV32" s="1" t="inlineStr"/>
-      <c r="AW32" s="1" t="inlineStr">
+      <c r="AK30" s="1" t="inlineStr"/>
+      <c r="AL30" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-k3-20-99883</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr">
+      <c r="B31" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп контейнеровоз Тонар K4-20 (9988), 2026</t>
         </is>
       </c>
-      <c r="D33" s="1" t="inlineStr">
+      <c r="D31" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Прицепы Тонар K4-20 (9988) ДОПОГ / 2026 года выпуска&lt;/strong&gt;
 &lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
@@ -7885,189 +7069,178 @@
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
         </is>
       </c>
-      <c r="E33" s="1" t="inlineStr">
+      <c r="E31" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="F33" s="1" t="inlineStr">
+      <c r="F31" s="1" t="inlineStr">
         <is>
           <t>2950000</t>
         </is>
       </c>
-      <c r="G33" s="1" t="inlineStr">
+      <c r="G31" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_26/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_26/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_26/03.jpg</t>
         </is>
       </c>
-      <c r="H33" s="1" t="inlineStr">
+      <c r="H31" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="I33" s="1" t="inlineStr">
+      <c r="I31" s="1" t="inlineStr">
         <is>
           <t>Иван</t>
         </is>
       </c>
-      <c r="J33" s="1" t="inlineStr">
+      <c r="J31" s="1" t="inlineStr">
         <is>
           <t>info@bel-car.com</t>
         </is>
       </c>
-      <c r="K33" s="1" t="inlineStr">
+      <c r="K31" s="1" t="inlineStr">
         <is>
           <t>79031369484</t>
         </is>
       </c>
-      <c r="L33" s="1" t="inlineStr">
+      <c r="L31" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M33" s="1" t="inlineStr"/>
-      <c r="N33" s="1" t="inlineStr">
+      <c r="M31" s="1" t="inlineStr"/>
+      <c r="N31" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="O33" s="1" t="inlineStr">
+      <c r="O31" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P33" s="1" t="inlineStr"/>
-      <c r="Q33" s="1" t="inlineStr">
+      <c r="P31" s="1" t="inlineStr">
         <is>
           <t>Дисковые</t>
         </is>
       </c>
-      <c r="R33" s="1" t="inlineStr"/>
-      <c r="S33" s="1" t="inlineStr"/>
-      <c r="T33" s="1" t="inlineStr">
+      <c r="Q31" s="1" t="inlineStr">
         <is>
           <t>ООО БелКар</t>
         </is>
       </c>
-      <c r="U33" s="1" t="inlineStr">
+      <c r="R31" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="V33" s="1" t="inlineStr">
+      <c r="S31" s="1" t="inlineStr">
         <is>
           <t>2950000</t>
         </is>
       </c>
-      <c r="W33" s="1" t="inlineStr">
+      <c r="T31" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X33" s="1" t="inlineStr">
+      <c r="U31" s="1" t="inlineStr">
         <is>
           <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
-      <c r="Y33" s="1" t="inlineStr"/>
-      <c r="Z33" s="1" t="inlineStr"/>
-      <c r="AA33" s="1" t="inlineStr"/>
-      <c r="AB33" s="1" t="inlineStr">
+      <c r="V31" s="1" t="inlineStr">
         <is>
           <t>42000</t>
         </is>
       </c>
-      <c r="AC33" s="1" t="inlineStr">
+      <c r="W31" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AD33" s="1" t="inlineStr">
+      <c r="X31" s="1" t="inlineStr">
         <is>
           <t>K4-20 (9988)</t>
         </is>
       </c>
-      <c r="AE33" s="1" t="inlineStr"/>
-      <c r="AF33" s="1" t="inlineStr"/>
-      <c r="AG33" s="1" t="inlineStr">
+      <c r="Y31" s="1" t="inlineStr"/>
+      <c r="Z31" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="AH33" s="1" t="inlineStr"/>
-      <c r="AI33" s="1" t="inlineStr">
+      <c r="AA31" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AJ33" s="1" t="inlineStr"/>
-      <c r="AK33" s="1" t="inlineStr">
+      <c r="AB31" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AL33" s="1" t="inlineStr">
+      <c r="AC31" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AM33" s="1" t="inlineStr">
+      <c r="AD31" s="1" t="inlineStr">
         <is>
           <t>9485</t>
         </is>
       </c>
-      <c r="AN33" s="1" t="inlineStr"/>
-      <c r="AO33" s="1" t="inlineStr"/>
-      <c r="AP33" s="1" t="inlineStr">
+      <c r="AE31" s="1" t="inlineStr"/>
+      <c r="AF31" s="1" t="inlineStr">
         <is>
           <t>Контейнеровоз</t>
         </is>
       </c>
-      <c r="AQ33" s="1" t="inlineStr">
+      <c r="AG31" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AR33" s="1" t="inlineStr"/>
-      <c r="AS33" s="1" t="inlineStr">
+      <c r="AH31" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AT33" s="1" t="inlineStr">
+      <c r="AI31" s="1" t="inlineStr">
         <is>
           <t>295000</t>
         </is>
       </c>
-      <c r="AU33" s="1" t="inlineStr">
+      <c r="AJ31" s="1" t="inlineStr">
         <is>
           <t>147500</t>
         </is>
       </c>
-      <c r="AV33" s="1" t="inlineStr"/>
-      <c r="AW33" s="1" t="inlineStr">
+      <c r="AK31" s="1" t="inlineStr"/>
+      <c r="AL31" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-k4-20-9988</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
+      <c r="B32" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп контейнеровоз Тонар K3-40 (99881), 2026</t>
         </is>
       </c>
-      <c r="D34" s="1" t="inlineStr">
+      <c r="D32" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар K3-40 (99881) / 2026 года выпуска&lt;/strong&gt;
 &lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
@@ -8107,189 +7280,178 @@
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
         </is>
       </c>
-      <c r="E34" s="1" t="inlineStr">
+      <c r="E32" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="F34" s="1" t="inlineStr">
+      <c r="F32" s="1" t="inlineStr">
         <is>
           <t>2250000</t>
         </is>
       </c>
-      <c r="G34" s="1" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_27/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_27/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_27/03.jpg</t>
         </is>
       </c>
-      <c r="H34" s="1" t="inlineStr">
+      <c r="H32" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="I34" s="1" t="inlineStr">
+      <c r="I32" s="1" t="inlineStr">
         <is>
           <t>Иван</t>
         </is>
       </c>
-      <c r="J34" s="1" t="inlineStr">
+      <c r="J32" s="1" t="inlineStr">
         <is>
           <t>info@bel-car.com</t>
         </is>
       </c>
-      <c r="K34" s="1" t="inlineStr">
+      <c r="K32" s="1" t="inlineStr">
         <is>
           <t>79031369484</t>
         </is>
       </c>
-      <c r="L34" s="1" t="inlineStr">
+      <c r="L32" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M34" s="1" t="inlineStr"/>
-      <c r="N34" s="1" t="inlineStr">
+      <c r="M32" s="1" t="inlineStr"/>
+      <c r="N32" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="O34" s="1" t="inlineStr">
+      <c r="O32" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P34" s="1" t="inlineStr"/>
-      <c r="Q34" s="1" t="inlineStr">
+      <c r="P32" s="1" t="inlineStr">
         <is>
           <t>Дисковые</t>
         </is>
       </c>
-      <c r="R34" s="1" t="inlineStr"/>
-      <c r="S34" s="1" t="inlineStr"/>
-      <c r="T34" s="1" t="inlineStr">
+      <c r="Q32" s="1" t="inlineStr">
         <is>
           <t>ООО БелКар</t>
         </is>
       </c>
-      <c r="U34" s="1" t="inlineStr">
+      <c r="R32" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="V34" s="1" t="inlineStr">
+      <c r="S32" s="1" t="inlineStr">
         <is>
           <t>2250000</t>
         </is>
       </c>
-      <c r="W34" s="1" t="inlineStr">
+      <c r="T32" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X34" s="1" t="inlineStr">
+      <c r="U32" s="1" t="inlineStr">
         <is>
           <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
-      <c r="Y34" s="1" t="inlineStr"/>
-      <c r="Z34" s="1" t="inlineStr"/>
-      <c r="AA34" s="1" t="inlineStr"/>
-      <c r="AB34" s="1" t="inlineStr">
+      <c r="V32" s="1" t="inlineStr">
         <is>
           <t>42300</t>
         </is>
       </c>
-      <c r="AC34" s="1" t="inlineStr">
+      <c r="W32" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AD34" s="1" t="inlineStr">
+      <c r="X32" s="1" t="inlineStr">
         <is>
           <t>K3-40 (99881)</t>
         </is>
       </c>
-      <c r="AE34" s="1" t="inlineStr"/>
-      <c r="AF34" s="1" t="inlineStr"/>
-      <c r="AG34" s="1" t="inlineStr">
+      <c r="Y32" s="1" t="inlineStr"/>
+      <c r="Z32" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="AH34" s="1" t="inlineStr"/>
-      <c r="AI34" s="1" t="inlineStr">
+      <c r="AA32" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AJ34" s="1" t="inlineStr"/>
-      <c r="AK34" s="1" t="inlineStr">
+      <c r="AB32" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AL34" s="1" t="inlineStr">
+      <c r="AC32" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AM34" s="1" t="inlineStr">
+      <c r="AD32" s="1" t="inlineStr">
         <is>
           <t>12580</t>
         </is>
       </c>
-      <c r="AN34" s="1" t="inlineStr"/>
-      <c r="AO34" s="1" t="inlineStr"/>
-      <c r="AP34" s="1" t="inlineStr">
+      <c r="AE32" s="1" t="inlineStr"/>
+      <c r="AF32" s="1" t="inlineStr">
         <is>
           <t>Контейнеровоз</t>
         </is>
       </c>
-      <c r="AQ34" s="1" t="inlineStr">
+      <c r="AG32" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AR34" s="1" t="inlineStr"/>
-      <c r="AS34" s="1" t="inlineStr">
+      <c r="AH32" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AT34" s="1" t="inlineStr">
+      <c r="AI32" s="1" t="inlineStr">
         <is>
           <t>225000</t>
         </is>
       </c>
-      <c r="AU34" s="1" t="inlineStr">
+      <c r="AJ32" s="1" t="inlineStr">
         <is>
           <t>112500</t>
         </is>
       </c>
-      <c r="AV34" s="1" t="inlineStr"/>
-      <c r="AW34" s="1" t="inlineStr">
+      <c r="AK32" s="1" t="inlineStr"/>
+      <c r="AL32" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-k3-40-99881</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
+      <c r="B33" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп контейнеровоз Тонар K4-40 (99893), 2026</t>
         </is>
       </c>
-      <c r="D35" s="1" t="inlineStr">
+      <c r="D33" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар K4-40 (99893) / 2026 года выпуска&lt;/strong&gt;
 &lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
@@ -8328,189 +7490,178 @@
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
         </is>
       </c>
-      <c r="E35" s="1" t="inlineStr">
+      <c r="E33" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="F35" s="1" t="inlineStr">
+      <c r="F33" s="1" t="inlineStr">
         <is>
           <t>2850000</t>
         </is>
       </c>
-      <c r="G35" s="1" t="inlineStr">
+      <c r="G33" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_28/01.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_28/02.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_28/03.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_28/04.webp</t>
         </is>
       </c>
-      <c r="H35" s="1" t="inlineStr">
+      <c r="H33" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="I35" s="1" t="inlineStr">
+      <c r="I33" s="1" t="inlineStr">
         <is>
           <t>Иван</t>
         </is>
       </c>
-      <c r="J35" s="1" t="inlineStr">
+      <c r="J33" s="1" t="inlineStr">
         <is>
           <t>info@bel-car.com</t>
         </is>
       </c>
-      <c r="K35" s="1" t="inlineStr">
+      <c r="K33" s="1" t="inlineStr">
         <is>
           <t>79031369484</t>
         </is>
       </c>
-      <c r="L35" s="1" t="inlineStr">
+      <c r="L33" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M35" s="1" t="inlineStr"/>
-      <c r="N35" s="1" t="inlineStr">
+      <c r="M33" s="1" t="inlineStr"/>
+      <c r="N33" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="O35" s="1" t="inlineStr">
+      <c r="O33" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P35" s="1" t="inlineStr"/>
-      <c r="Q35" s="1" t="inlineStr">
+      <c r="P33" s="1" t="inlineStr">
         <is>
           <t>Дисковые</t>
         </is>
       </c>
-      <c r="R35" s="1" t="inlineStr"/>
-      <c r="S35" s="1" t="inlineStr"/>
-      <c r="T35" s="1" t="inlineStr">
+      <c r="Q33" s="1" t="inlineStr">
         <is>
           <t>ООО БелКар</t>
         </is>
       </c>
-      <c r="U35" s="1" t="inlineStr">
+      <c r="R33" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="V35" s="1" t="inlineStr">
+      <c r="S33" s="1" t="inlineStr">
         <is>
           <t>2850000</t>
         </is>
       </c>
-      <c r="W35" s="1" t="inlineStr">
+      <c r="T33" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X35" s="1" t="inlineStr">
+      <c r="U33" s="1" t="inlineStr">
         <is>
           <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
-      <c r="Y35" s="1" t="inlineStr"/>
-      <c r="Z35" s="1" t="inlineStr"/>
-      <c r="AA35" s="1" t="inlineStr"/>
-      <c r="AB35" s="1" t="inlineStr">
+      <c r="V33" s="1" t="inlineStr">
         <is>
           <t>38000</t>
         </is>
       </c>
-      <c r="AC35" s="1" t="inlineStr">
+      <c r="W33" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AD35" s="1" t="inlineStr">
+      <c r="X33" s="1" t="inlineStr">
         <is>
           <t>K4-40 (99893)</t>
         </is>
       </c>
-      <c r="AE35" s="1" t="inlineStr"/>
-      <c r="AF35" s="1" t="inlineStr"/>
-      <c r="AG35" s="1" t="inlineStr">
+      <c r="Y33" s="1" t="inlineStr"/>
+      <c r="Z33" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="AH35" s="1" t="inlineStr"/>
-      <c r="AI35" s="1" t="inlineStr">
+      <c r="AA33" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AJ35" s="1" t="inlineStr"/>
-      <c r="AK35" s="1" t="inlineStr">
+      <c r="AB33" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AL35" s="1" t="inlineStr">
+      <c r="AC33" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AM35" s="1" t="inlineStr">
+      <c r="AD33" s="1" t="inlineStr">
         <is>
           <t>12750</t>
         </is>
       </c>
-      <c r="AN35" s="1" t="inlineStr"/>
-      <c r="AO35" s="1" t="inlineStr"/>
-      <c r="AP35" s="1" t="inlineStr">
+      <c r="AE33" s="1" t="inlineStr"/>
+      <c r="AF33" s="1" t="inlineStr">
         <is>
           <t>Контейнеровоз</t>
         </is>
       </c>
-      <c r="AQ35" s="1" t="inlineStr">
+      <c r="AG33" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AR35" s="1" t="inlineStr"/>
-      <c r="AS35" s="1" t="inlineStr">
+      <c r="AH33" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AT35" s="1" t="inlineStr">
+      <c r="AI33" s="1" t="inlineStr">
         <is>
           <t>285000</t>
         </is>
       </c>
-      <c r="AU35" s="1" t="inlineStr">
+      <c r="AJ33" s="1" t="inlineStr">
         <is>
           <t>142500</t>
         </is>
       </c>
-      <c r="AV35" s="1" t="inlineStr"/>
-      <c r="AW35" s="1" t="inlineStr">
+      <c r="AK33" s="1" t="inlineStr"/>
+      <c r="AL33" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-k4-40-99893</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
+      <c r="B34" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп тушевоз Тонар R3-13T (97861), 2026</t>
         </is>
       </c>
-      <c r="D36" s="1" t="inlineStr">
+      <c r="D34" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар R3-13T (97861) / 2026 года выпуска&lt;/strong&gt;
 &lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
@@ -8558,189 +7709,178 @@
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
         </is>
       </c>
-      <c r="E36" s="1" t="inlineStr">
+      <c r="E34" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="F36" s="1" t="inlineStr">
+      <c r="F34" s="1" t="inlineStr">
         <is>
           <t>6450000</t>
         </is>
       </c>
-      <c r="G36" s="1" t="inlineStr">
+      <c r="G34" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_31/01.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_31/02.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_31/03.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_31/04.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_31/05.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_31/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_31/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_31/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_31/09.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_31/10.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_31/11.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_31/12.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_31/13.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_31/14.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_31/15.webp</t>
         </is>
       </c>
-      <c r="H36" s="1" t="inlineStr">
+      <c r="H34" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="I36" s="1" t="inlineStr">
+      <c r="I34" s="1" t="inlineStr">
         <is>
           <t>Иван</t>
         </is>
       </c>
-      <c r="J36" s="1" t="inlineStr">
+      <c r="J34" s="1" t="inlineStr">
         <is>
           <t>info@bel-car.com</t>
         </is>
       </c>
-      <c r="K36" s="1" t="inlineStr">
+      <c r="K34" s="1" t="inlineStr">
         <is>
           <t>79031369484</t>
         </is>
       </c>
-      <c r="L36" s="1" t="inlineStr">
+      <c r="L34" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M36" s="1" t="inlineStr"/>
-      <c r="N36" s="1" t="inlineStr">
+      <c r="M34" s="1" t="inlineStr"/>
+      <c r="N34" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="O36" s="1" t="inlineStr">
+      <c r="O34" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P36" s="1" t="inlineStr"/>
-      <c r="Q36" s="1" t="inlineStr">
+      <c r="P34" s="1" t="inlineStr">
         <is>
           <t>Барабанные</t>
         </is>
       </c>
-      <c r="R36" s="1" t="inlineStr"/>
-      <c r="S36" s="1" t="inlineStr"/>
-      <c r="T36" s="1" t="inlineStr">
+      <c r="Q34" s="1" t="inlineStr">
         <is>
           <t>ООО БелКар</t>
         </is>
       </c>
-      <c r="U36" s="1" t="inlineStr">
+      <c r="R34" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="V36" s="1" t="inlineStr">
+      <c r="S34" s="1" t="inlineStr">
         <is>
           <t>6450000</t>
         </is>
       </c>
-      <c r="W36" s="1" t="inlineStr">
+      <c r="T34" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X36" s="1" t="inlineStr">
+      <c r="U34" s="1" t="inlineStr">
         <is>
           <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
-      <c r="Y36" s="1" t="inlineStr"/>
-      <c r="Z36" s="1" t="inlineStr"/>
-      <c r="AA36" s="1" t="inlineStr"/>
-      <c r="AB36" s="1" t="inlineStr">
+      <c r="V34" s="1" t="inlineStr">
         <is>
           <t>38080</t>
         </is>
       </c>
-      <c r="AC36" s="1" t="inlineStr">
+      <c r="W34" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AD36" s="1" t="inlineStr">
+      <c r="X34" s="1" t="inlineStr">
         <is>
           <t>R3-13T (97861)</t>
         </is>
       </c>
-      <c r="AE36" s="1" t="inlineStr"/>
-      <c r="AF36" s="1" t="inlineStr"/>
-      <c r="AG36" s="1" t="inlineStr">
+      <c r="Y34" s="1" t="inlineStr"/>
+      <c r="Z34" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="AH36" s="1" t="inlineStr"/>
-      <c r="AI36" s="1" t="inlineStr">
+      <c r="AA34" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AJ36" s="1" t="inlineStr"/>
-      <c r="AK36" s="1" t="inlineStr">
+      <c r="AB34" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AL36" s="1" t="inlineStr">
+      <c r="AC34" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AM36" s="1" t="inlineStr">
+      <c r="AD34" s="1" t="inlineStr">
         <is>
           <t>14186</t>
         </is>
       </c>
-      <c r="AN36" s="1" t="inlineStr">
+      <c r="AE34" s="1" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="AO36" s="1" t="inlineStr"/>
-      <c r="AP36" s="1" t="inlineStr">
+      <c r="AF34" s="1" t="inlineStr">
         <is>
           <t>Тушевоз</t>
         </is>
       </c>
-      <c r="AQ36" s="1" t="inlineStr">
+      <c r="AG34" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AR36" s="1" t="inlineStr"/>
-      <c r="AS36" s="1" t="inlineStr">
+      <c r="AH34" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AT36" s="1" t="inlineStr">
+      <c r="AI34" s="1" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="AU36" s="1" t="inlineStr"/>
-      <c r="AV36" s="1" t="inlineStr"/>
-      <c r="AW36" s="1" t="inlineStr">
+      <c r="AJ34" s="1" t="inlineStr"/>
+      <c r="AK34" s="1" t="inlineStr"/>
+      <c r="AL34" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-r3-13t-97861</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
+      <c r="B35" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп изотермический Тонар R3-14 (97863), 2026</t>
         </is>
       </c>
-      <c r="D37" s="1" t="inlineStr">
+      <c r="D35" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар R3-14 (97863) / 2026 года выпуска&lt;/strong&gt;
 &lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
@@ -8788,189 +7928,178 @@
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
         </is>
       </c>
-      <c r="E37" s="1" t="inlineStr">
+      <c r="E35" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="F37" s="1" t="inlineStr">
+      <c r="F35" s="1" t="inlineStr">
         <is>
           <t>5000000</t>
         </is>
       </c>
-      <c r="G37" s="1" t="inlineStr">
+      <c r="G35" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_32/01.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_32/02.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_32/03.webp</t>
         </is>
       </c>
-      <c r="H37" s="1" t="inlineStr">
+      <c r="H35" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="I37" s="1" t="inlineStr">
+      <c r="I35" s="1" t="inlineStr">
         <is>
           <t>Иван</t>
         </is>
       </c>
-      <c r="J37" s="1" t="inlineStr">
+      <c r="J35" s="1" t="inlineStr">
         <is>
           <t>info@bel-car.com</t>
         </is>
       </c>
-      <c r="K37" s="1" t="inlineStr">
+      <c r="K35" s="1" t="inlineStr">
         <is>
           <t>79031369484</t>
         </is>
       </c>
-      <c r="L37" s="1" t="inlineStr">
+      <c r="L35" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M37" s="1" t="inlineStr"/>
-      <c r="N37" s="1" t="inlineStr">
+      <c r="M35" s="1" t="inlineStr"/>
+      <c r="N35" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="O37" s="1" t="inlineStr">
+      <c r="O35" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P37" s="1" t="inlineStr"/>
-      <c r="Q37" s="1" t="inlineStr">
+      <c r="P35" s="1" t="inlineStr">
         <is>
           <t>Дисковые</t>
         </is>
       </c>
-      <c r="R37" s="1" t="inlineStr"/>
-      <c r="S37" s="1" t="inlineStr"/>
-      <c r="T37" s="1" t="inlineStr">
+      <c r="Q35" s="1" t="inlineStr">
         <is>
           <t>ООО БелКар</t>
         </is>
       </c>
-      <c r="U37" s="1" t="inlineStr">
+      <c r="R35" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="V37" s="1" t="inlineStr">
+      <c r="S35" s="1" t="inlineStr">
         <is>
           <t>5000000</t>
         </is>
       </c>
-      <c r="W37" s="1" t="inlineStr">
+      <c r="T35" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X37" s="1" t="inlineStr">
+      <c r="U35" s="1" t="inlineStr">
         <is>
           <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
-      <c r="Y37" s="1" t="inlineStr"/>
-      <c r="Z37" s="1" t="inlineStr"/>
-      <c r="AA37" s="1" t="inlineStr"/>
-      <c r="AB37" s="1" t="inlineStr">
+      <c r="V35" s="1" t="inlineStr">
         <is>
           <t>34500</t>
         </is>
       </c>
-      <c r="AC37" s="1" t="inlineStr">
+      <c r="W35" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AD37" s="1" t="inlineStr">
+      <c r="X35" s="1" t="inlineStr">
         <is>
           <t>R3-14 (97863)</t>
         </is>
       </c>
-      <c r="AE37" s="1" t="inlineStr"/>
-      <c r="AF37" s="1" t="inlineStr"/>
-      <c r="AG37" s="1" t="inlineStr">
+      <c r="Y35" s="1" t="inlineStr"/>
+      <c r="Z35" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="AH37" s="1" t="inlineStr"/>
-      <c r="AI37" s="1" t="inlineStr">
+      <c r="AA35" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AJ37" s="1" t="inlineStr"/>
-      <c r="AK37" s="1" t="inlineStr">
+      <c r="AB35" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AL37" s="1" t="inlineStr">
+      <c r="AC35" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AM37" s="1" t="inlineStr">
+      <c r="AD35" s="1" t="inlineStr">
         <is>
           <t>14610</t>
         </is>
       </c>
-      <c r="AN37" s="1" t="inlineStr">
+      <c r="AE35" s="1" t="inlineStr">
         <is>
           <t>92</t>
         </is>
       </c>
-      <c r="AO37" s="1" t="inlineStr"/>
-      <c r="AP37" s="1" t="inlineStr">
+      <c r="AF35" s="1" t="inlineStr">
         <is>
           <t>Изотермический</t>
         </is>
       </c>
-      <c r="AQ37" s="1" t="inlineStr">
+      <c r="AG35" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AR37" s="1" t="inlineStr"/>
-      <c r="AS37" s="1" t="inlineStr">
+      <c r="AH35" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AT37" s="1" t="inlineStr">
+      <c r="AI35" s="1" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="AU37" s="1" t="inlineStr"/>
-      <c r="AV37" s="1" t="inlineStr"/>
-      <c r="AW37" s="1" t="inlineStr">
+      <c r="AJ35" s="1" t="inlineStr"/>
+      <c r="AK35" s="1" t="inlineStr"/>
+      <c r="AL35" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-r3-14-97863</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
+      <c r="B36" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп изотермический Тонар R3-13D (97861), 2026</t>
         </is>
       </c>
-      <c r="D38" s="1" t="inlineStr">
+      <c r="D36" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар R3-13D (97861) / 2026 года выпуска&lt;/strong&gt;
 &lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
@@ -9018,185 +8147,174 @@
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
         </is>
       </c>
-      <c r="E38" s="1" t="inlineStr">
+      <c r="E36" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="F38" s="1" t="inlineStr">
+      <c r="F36" s="1" t="inlineStr">
         <is>
           <t>5550000</t>
         </is>
       </c>
-      <c r="G38" s="1" t="inlineStr">
+      <c r="G36" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_33/01.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_33/02.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_33/03.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_33/04.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_33/05.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_33/06.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_33/07.webp | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_33/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_33/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_33/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_33/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_33/12.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_33/13.jpg</t>
         </is>
       </c>
-      <c r="H38" s="1" t="inlineStr">
+      <c r="H36" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="I38" s="1" t="inlineStr">
+      <c r="I36" s="1" t="inlineStr">
         <is>
           <t>Иван</t>
         </is>
       </c>
-      <c r="J38" s="1" t="inlineStr">
+      <c r="J36" s="1" t="inlineStr">
         <is>
           <t>info@bel-car.com</t>
         </is>
       </c>
-      <c r="K38" s="1" t="inlineStr">
+      <c r="K36" s="1" t="inlineStr">
         <is>
           <t>79031369484</t>
         </is>
       </c>
-      <c r="L38" s="1" t="inlineStr">
+      <c r="L36" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M38" s="1" t="inlineStr"/>
-      <c r="N38" s="1" t="inlineStr">
+      <c r="M36" s="1" t="inlineStr"/>
+      <c r="N36" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="O38" s="1" t="inlineStr">
+      <c r="O36" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P38" s="1" t="inlineStr"/>
-      <c r="Q38" s="1" t="inlineStr">
+      <c r="P36" s="1" t="inlineStr">
         <is>
           <t>Барабанные</t>
         </is>
       </c>
-      <c r="R38" s="1" t="inlineStr"/>
-      <c r="S38" s="1" t="inlineStr"/>
-      <c r="T38" s="1" t="inlineStr">
+      <c r="Q36" s="1" t="inlineStr">
         <is>
           <t>ООО БелКар</t>
         </is>
       </c>
-      <c r="U38" s="1" t="inlineStr">
+      <c r="R36" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="V38" s="1" t="inlineStr">
+      <c r="S36" s="1" t="inlineStr">
         <is>
           <t>5550000</t>
         </is>
       </c>
-      <c r="W38" s="1" t="inlineStr">
+      <c r="T36" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X38" s="1" t="inlineStr">
+      <c r="U36" s="1" t="inlineStr">
         <is>
           <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
-      <c r="Y38" s="1" t="inlineStr"/>
-      <c r="Z38" s="1" t="inlineStr"/>
-      <c r="AA38" s="1" t="inlineStr"/>
-      <c r="AB38" s="1" t="inlineStr">
+      <c r="V36" s="1" t="inlineStr">
         <is>
           <t>38080</t>
         </is>
       </c>
-      <c r="AC38" s="1" t="inlineStr">
+      <c r="W36" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AD38" s="1" t="inlineStr">
+      <c r="X36" s="1" t="inlineStr">
         <is>
           <t>R3-13D (97861)</t>
         </is>
       </c>
-      <c r="AE38" s="1" t="inlineStr"/>
-      <c r="AF38" s="1" t="inlineStr"/>
-      <c r="AG38" s="1" t="inlineStr">
+      <c r="Y36" s="1" t="inlineStr"/>
+      <c r="Z36" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="AH38" s="1" t="inlineStr"/>
-      <c r="AI38" s="1" t="inlineStr">
+      <c r="AA36" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AJ38" s="1" t="inlineStr"/>
-      <c r="AK38" s="1" t="inlineStr">
+      <c r="AB36" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AL38" s="1" t="inlineStr">
+      <c r="AC36" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AM38" s="1" t="inlineStr">
+      <c r="AD36" s="1" t="inlineStr">
         <is>
           <t>13500</t>
         </is>
       </c>
-      <c r="AN38" s="1" t="inlineStr"/>
-      <c r="AO38" s="1" t="inlineStr"/>
-      <c r="AP38" s="1" t="inlineStr">
+      <c r="AE36" s="1" t="inlineStr"/>
+      <c r="AF36" s="1" t="inlineStr">
         <is>
           <t>Изотермический</t>
         </is>
       </c>
-      <c r="AQ38" s="1" t="inlineStr">
+      <c r="AG36" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AR38" s="1" t="inlineStr"/>
-      <c r="AS38" s="1" t="inlineStr">
+      <c r="AH36" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AT38" s="1" t="inlineStr">
+      <c r="AI36" s="1" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="AU38" s="1" t="inlineStr"/>
-      <c r="AV38" s="1" t="inlineStr"/>
-      <c r="AW38" s="1" t="inlineStr">
+      <c r="AJ36" s="1" t="inlineStr"/>
+      <c r="AK36" s="1" t="inlineStr"/>
+      <c r="AL36" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-r3-13d-97861</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
+      <c r="B37" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп бортовой Тонар B4-13V (97883), 2026</t>
         </is>
       </c>
-      <c r="D39" s="1" t="inlineStr">
+      <c r="D37" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар B4-13V (97883) / 2026 года выпуска&lt;/strong&gt;
 &lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
@@ -9240,189 +8358,178 @@
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
         </is>
       </c>
-      <c r="E39" s="1" t="inlineStr">
+      <c r="E37" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="F39" s="1" t="inlineStr">
+      <c r="F37" s="1" t="inlineStr">
         <is>
           <t>3700000</t>
         </is>
       </c>
-      <c r="G39" s="1" t="inlineStr">
+      <c r="G37" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_4/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_4/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_4/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_4/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_4/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_4/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_4/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_4/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_4/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_4/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_4/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_4/12.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_4/13.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_4/14.jpg</t>
         </is>
       </c>
-      <c r="H39" s="1" t="inlineStr">
+      <c r="H37" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="I39" s="1" t="inlineStr">
+      <c r="I37" s="1" t="inlineStr">
         <is>
           <t>Иван</t>
         </is>
       </c>
-      <c r="J39" s="1" t="inlineStr">
+      <c r="J37" s="1" t="inlineStr">
         <is>
           <t>info@bel-car.com</t>
         </is>
       </c>
-      <c r="K39" s="1" t="inlineStr">
+      <c r="K37" s="1" t="inlineStr">
         <is>
           <t>79031369484</t>
         </is>
       </c>
-      <c r="L39" s="1" t="inlineStr">
+      <c r="L37" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M39" s="1" t="inlineStr"/>
-      <c r="N39" s="1" t="inlineStr">
+      <c r="M37" s="1" t="inlineStr"/>
+      <c r="N37" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="O39" s="1" t="inlineStr">
+      <c r="O37" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P39" s="1" t="inlineStr"/>
-      <c r="Q39" s="1" t="inlineStr">
+      <c r="P37" s="1" t="inlineStr">
         <is>
           <t>Барабанные</t>
         </is>
       </c>
-      <c r="R39" s="1" t="inlineStr"/>
-      <c r="S39" s="1" t="inlineStr"/>
-      <c r="T39" s="1" t="inlineStr">
+      <c r="Q37" s="1" t="inlineStr">
         <is>
           <t>ООО БелКар</t>
         </is>
       </c>
-      <c r="U39" s="1" t="inlineStr">
+      <c r="R37" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="V39" s="1" t="inlineStr">
+      <c r="S37" s="1" t="inlineStr">
         <is>
           <t>3700000</t>
         </is>
       </c>
-      <c r="W39" s="1" t="inlineStr">
+      <c r="T37" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X39" s="1" t="inlineStr">
+      <c r="U37" s="1" t="inlineStr">
         <is>
           <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
-      <c r="Y39" s="1" t="inlineStr"/>
-      <c r="Z39" s="1" t="inlineStr"/>
-      <c r="AA39" s="1" t="inlineStr"/>
-      <c r="AB39" s="1" t="inlineStr">
+      <c r="V37" s="1" t="inlineStr">
         <is>
           <t>37500</t>
         </is>
       </c>
-      <c r="AC39" s="1" t="inlineStr">
+      <c r="W37" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AD39" s="1" t="inlineStr">
+      <c r="X37" s="1" t="inlineStr">
         <is>
           <t>B4-13V (97883)</t>
         </is>
       </c>
-      <c r="AE39" s="1" t="inlineStr"/>
-      <c r="AF39" s="1" t="inlineStr"/>
-      <c r="AG39" s="1" t="inlineStr">
+      <c r="Y37" s="1" t="inlineStr"/>
+      <c r="Z37" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="AH39" s="1" t="inlineStr"/>
-      <c r="AI39" s="1" t="inlineStr">
+      <c r="AA37" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AJ39" s="1" t="inlineStr"/>
-      <c r="AK39" s="1" t="inlineStr">
+      <c r="AB37" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AL39" s="1" t="inlineStr">
+      <c r="AC37" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AM39" s="1" t="inlineStr">
+      <c r="AD37" s="1" t="inlineStr">
         <is>
           <t>13690</t>
         </is>
       </c>
-      <c r="AN39" s="1" t="inlineStr"/>
-      <c r="AO39" s="1" t="inlineStr"/>
-      <c r="AP39" s="1" t="inlineStr">
+      <c r="AE37" s="1" t="inlineStr"/>
+      <c r="AF37" s="1" t="inlineStr">
         <is>
           <t>Бортовой</t>
         </is>
       </c>
-      <c r="AQ39" s="1" t="inlineStr">
+      <c r="AG37" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AR39" s="1" t="inlineStr"/>
-      <c r="AS39" s="1" t="inlineStr">
+      <c r="AH37" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AT39" s="1" t="inlineStr">
+      <c r="AI37" s="1" t="inlineStr">
         <is>
           <t>370000</t>
         </is>
       </c>
-      <c r="AU39" s="1" t="inlineStr">
+      <c r="AJ37" s="1" t="inlineStr">
         <is>
           <t>370000</t>
         </is>
       </c>
-      <c r="AV39" s="1" t="inlineStr"/>
-      <c r="AW39" s="1" t="inlineStr">
+      <c r="AK37" s="1" t="inlineStr"/>
+      <c r="AL37" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-b4-13v-97883</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
         <is>
           <t>Грузовики и спецтехника</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
+      <c r="B38" s="1" t="inlineStr">
         <is>
           <t>Прицепы</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп шторно-бортовой Тонар T4-13V (97883), 2026</t>
         </is>
       </c>
-      <c r="D40" s="1" t="inlineStr">
+      <c r="D38" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар T4-13V (97883) / 2026 года выпуска&lt;/strong&gt;
 &lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
@@ -9474,596 +8581,162 @@
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
         </is>
       </c>
-      <c r="E40" s="1" t="inlineStr">
+      <c r="E38" s="1" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="F40" s="1" t="inlineStr">
+      <c r="F38" s="1" t="inlineStr">
         <is>
           <t>4250000</t>
         </is>
       </c>
-      <c r="G40" s="1" t="inlineStr">
+      <c r="G38" s="1" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_8/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_8/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_8/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_8/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_8/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/novaia_8/06.jpg</t>
         </is>
       </c>
-      <c r="H40" s="1" t="inlineStr">
+      <c r="H38" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="I40" s="1" t="inlineStr">
+      <c r="I38" s="1" t="inlineStr">
         <is>
           <t>Иван</t>
         </is>
       </c>
-      <c r="J40" s="1" t="inlineStr">
+      <c r="J38" s="1" t="inlineStr">
         <is>
           <t>info@bel-car.com</t>
         </is>
       </c>
-      <c r="K40" s="1" t="inlineStr">
+      <c r="K38" s="1" t="inlineStr">
         <is>
           <t>79031369484</t>
         </is>
       </c>
-      <c r="L40" s="1" t="inlineStr">
+      <c r="L38" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M40" s="1" t="inlineStr"/>
-      <c r="N40" s="1" t="inlineStr">
+      <c r="M38" s="1" t="inlineStr"/>
+      <c r="N38" s="1" t="inlineStr">
         <is>
           <t>Под заказ</t>
         </is>
       </c>
-      <c r="O40" s="1" t="inlineStr">
+      <c r="O38" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P40" s="1" t="inlineStr"/>
-      <c r="Q40" s="1" t="inlineStr">
+      <c r="P38" s="1" t="inlineStr">
         <is>
           <t>Дисковые</t>
         </is>
       </c>
-      <c r="R40" s="1" t="inlineStr"/>
-      <c r="S40" s="1" t="inlineStr"/>
-      <c r="T40" s="1" t="inlineStr">
+      <c r="Q38" s="1" t="inlineStr">
         <is>
           <t>ООО БелКар</t>
         </is>
       </c>
-      <c r="U40" s="1" t="inlineStr">
+      <c r="R38" s="1" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="V40" s="1" t="inlineStr">
+      <c r="S38" s="1" t="inlineStr">
         <is>
           <t>4250000</t>
         </is>
       </c>
-      <c r="W40" s="1" t="inlineStr">
+      <c r="T38" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="X40" s="1" t="inlineStr">
+      <c r="U38" s="1" t="inlineStr">
         <is>
           <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
-      <c r="Y40" s="1" t="inlineStr"/>
-      <c r="Z40" s="1" t="inlineStr"/>
-      <c r="AA40" s="1" t="inlineStr"/>
-      <c r="AB40" s="1" t="inlineStr">
+      <c r="V38" s="1" t="inlineStr">
         <is>
           <t>37500</t>
         </is>
       </c>
-      <c r="AC40" s="1" t="inlineStr">
+      <c r="W38" s="1" t="inlineStr">
         <is>
           <t>Тонар</t>
         </is>
       </c>
-      <c r="AD40" s="1" t="inlineStr">
+      <c r="X38" s="1" t="inlineStr">
         <is>
           <t>T4-13V (97883)</t>
         </is>
       </c>
-      <c r="AE40" s="1" t="inlineStr"/>
-      <c r="AF40" s="1" t="inlineStr"/>
-      <c r="AG40" s="1" t="inlineStr">
+      <c r="Y38" s="1" t="inlineStr"/>
+      <c r="Z38" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
-      <c r="AH40" s="1" t="inlineStr"/>
-      <c r="AI40" s="1" t="inlineStr">
+      <c r="AA38" s="1" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="AJ40" s="1" t="inlineStr"/>
-      <c r="AK40" s="1" t="inlineStr">
+      <c r="AB38" s="1" t="inlineStr">
         <is>
           <t>Пневматическая</t>
         </is>
       </c>
-      <c r="AL40" s="1" t="inlineStr">
+      <c r="AC38" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="AM40" s="1" t="inlineStr">
+      <c r="AD38" s="1" t="inlineStr">
         <is>
           <t>13600</t>
         </is>
       </c>
-      <c r="AN40" s="1" t="inlineStr">
+      <c r="AE38" s="1" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="AO40" s="1" t="inlineStr"/>
-      <c r="AP40" s="1" t="inlineStr">
+      <c r="AF38" s="1" t="inlineStr">
         <is>
           <t>Шторно-бортовой</t>
         </is>
       </c>
-      <c r="AQ40" s="1" t="inlineStr">
+      <c r="AG38" s="1" t="inlineStr">
         <is>
           <t>Полуприцеп</t>
         </is>
       </c>
-      <c r="AR40" s="1" t="inlineStr"/>
-      <c r="AS40" s="1" t="inlineStr">
+      <c r="AH38" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AT40" s="1" t="inlineStr">
+      <c r="AI38" s="1" t="inlineStr">
         <is>
           <t>425000</t>
         </is>
       </c>
-      <c r="AU40" s="1" t="inlineStr">
+      <c r="AJ38" s="1" t="inlineStr">
         <is>
           <t>425000</t>
         </is>
       </c>
-      <c r="AV40" s="1" t="inlineStr"/>
-      <c r="AW40" s="1" t="inlineStr">
+      <c r="AK38" s="1" t="inlineStr"/>
+      <c r="AL38" s="1" t="inlineStr">
         <is>
           <t>bk-tonar-t4-13v-97883</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>Грузовики и спецтехника</t>
-        </is>
-      </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>Седельные тягачи</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>Седельный тягач МАЗ 544008, 2024</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>&lt;strong&gt;Седельные тягачи МАЗ 544008 / 2024 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
-&lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
-- &lt;strong&gt;Koлecная формула:&lt;/strong&gt; 4×2
-- &lt;strong&gt;Допуcтимая пoлная маccа:&lt;/strong&gt; 18750 кг
-- &lt;strong&gt;Допустимая полнaя масcа aвтoпoeздa:&lt;/strong&gt; 44000 кг
-- &lt;strong&gt;Мaсса снаряженного автомобиля:&lt;/strong&gt; 8200 кг
-- &lt;strong&gt;Двигатель:&lt;/strong&gt; дизельный с турбонаддувом, с промежуточным охлаждением наддувочного воздуха (Евро-2)
-- &lt;strong&gt;Мощность двигателя:&lt;/strong&gt; 400 л.с.
-- &lt;strong&gt;Коробка передач:&lt;/strong&gt; 12JS200TA механическая
-- &lt;strong&gt;Число передач КП:&lt;/strong&gt; 12
-- &lt;strong&gt;Высота ССУ:&lt;/strong&gt; 1150 мм
-- &lt;strong&gt;Распределение полной массы на переднюю ось:&lt;/strong&gt; 7250 кг
-- &lt;strong&gt;Распределение полной массы на задний мост:&lt;/strong&gt; 11500 кг
-&lt;strong&gt;ДОПОЛНИТЕЛЬНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
-- &lt;strong&gt;Тип кабины:&lt;/strong&gt; большая 6431 рестайлинг, 2 спальных места
-- &lt;strong&gt;Объём топливного бака, л:&lt;/strong&gt; 500
-- &lt;strong&gt;Особенности комплектации:&lt;/strong&gt; Ограничитель скорости, ремни безопасности,  АБС, ПБС
-- &lt;strong&gt;Размер шин:&lt;/strong&gt; 315/70R22,5
-• &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 5 071 000 ₽
-&lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>5071000</t>
-        </is>
-      </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/reload_122/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/reload_122/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/reload_122/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/reload_122/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/reload_122/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/reload_122/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/reload_122/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/reload_122/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/reload_122/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/reload_122/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/reload_122/11.jpg</t>
-        </is>
-      </c>
-      <c r="H41" s="1" t="inlineStr">
-        <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="I41" s="1" t="inlineStr">
-        <is>
-          <t>Иван</t>
-        </is>
-      </c>
-      <c r="J41" s="1" t="inlineStr">
-        <is>
-          <t>info@bel-car.com</t>
-        </is>
-      </c>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>79031369484</t>
-        </is>
-      </c>
-      <c r="L41" s="1" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="M41" s="1" t="inlineStr"/>
-      <c r="N41" s="1" t="inlineStr">
-        <is>
-          <t>Под заказ</t>
-        </is>
-      </c>
-      <c r="O41" s="1" t="inlineStr"/>
-      <c r="P41" s="1" t="inlineStr">
-        <is>
-          <t>Седельный</t>
-        </is>
-      </c>
-      <c r="Q41" s="1" t="inlineStr"/>
-      <c r="R41" s="1" t="inlineStr">
-        <is>
-          <t>Механическая</t>
-        </is>
-      </c>
-      <c r="S41" s="1" t="inlineStr">
-        <is>
-          <t>2-х местная с 1 спальным</t>
-        </is>
-      </c>
-      <c r="T41" s="1" t="inlineStr">
-        <is>
-          <t>ООО БелКар</t>
-        </is>
-      </c>
-      <c r="U41" s="1" t="inlineStr">
-        <is>
-          <t>RUB</t>
-        </is>
-      </c>
-      <c r="V41" s="1" t="inlineStr">
-        <is>
-          <t>5071000</t>
-        </is>
-      </c>
-      <c r="W41" s="1" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="X41" s="1" t="inlineStr">
-        <is>
-          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
-        </is>
-      </c>
-      <c r="Y41" s="1" t="inlineStr">
-        <is>
-          <t>Евро 2</t>
-        </is>
-      </c>
-      <c r="Z41" s="1" t="inlineStr">
-        <is>
-          <t>11946</t>
-        </is>
-      </c>
-      <c r="AA41" s="1" t="inlineStr">
-        <is>
-          <t>Дизель</t>
-        </is>
-      </c>
-      <c r="AB41" s="1" t="inlineStr"/>
-      <c r="AC41" s="1" t="inlineStr">
-        <is>
-          <t>МАЗ</t>
-        </is>
-      </c>
-      <c r="AD41" s="1" t="inlineStr">
-        <is>
-          <t>544008</t>
-        </is>
-      </c>
-      <c r="AE41" s="1" t="inlineStr">
-        <is>
-          <t>544008</t>
-        </is>
-      </c>
-      <c r="AF41" s="1" t="inlineStr"/>
-      <c r="AG41" s="1" t="inlineStr">
-        <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="AH41" s="1" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="AI41" s="1" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="AJ41" s="1" t="inlineStr">
-        <is>
-          <t>Пневматическая</t>
-        </is>
-      </c>
-      <c r="AK41" s="1" t="inlineStr"/>
-      <c r="AL41" s="1" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AM41" s="1" t="inlineStr"/>
-      <c r="AN41" s="1" t="inlineStr"/>
-      <c r="AO41" s="1" t="inlineStr">
-        <is>
-          <t>Механика</t>
-        </is>
-      </c>
-      <c r="AP41" s="1" t="inlineStr"/>
-      <c r="AQ41" s="1" t="inlineStr"/>
-      <c r="AR41" s="1" t="inlineStr">
-        <is>
-          <t>4×2</t>
-        </is>
-      </c>
-      <c r="AS41" s="1" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="AT41" s="1" t="inlineStr"/>
-      <c r="AU41" s="1" t="inlineStr"/>
-      <c r="AV41" s="1" t="inlineStr"/>
-      <c r="AW41" s="1" t="inlineStr">
-        <is>
-          <t>bk-maz-544008</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>Грузовики и спецтехника</t>
-        </is>
-      </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>Прицепы</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>Полуприцеп бортовой МАЗ 975800-2010, 2024</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>&lt;strong&gt;Полуприцеп МАЗ 975800-2010 / 2024 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
-&lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
-- &lt;strong&gt;Количество осей/колес (шт.):&lt;/strong&gt; 3
-- &lt;strong&gt;Масса перевозимого груза, кг:&lt;/strong&gt; 27200
-- &lt;strong&gt;Масса снаряженного полуприцепа, кг:&lt;/strong&gt;7100
-- &lt;strong&gt;Масса полуприцепа полная, не более, кг:&lt;/strong&gt;34500
-- &lt;strong&gt;Распределение полной массы на седельное устройство тягача, кг:&lt;/strong&gt; 10500
-- &lt;strong&gt;Распределение полной массы на тележку, кг:&lt;/strong&gt; 24000
-- &lt;strong&gt;Длинна платформы, мм:&lt;/strong&gt; 13600
-- &lt;strong&gt;Ширина платформы, мм:&lt;/strong&gt; 2460
-- &lt;strong&gt;Высота ССУ, мм:&lt;/strong&gt; 1250
-- &lt;strong&gt;Объем кузова, м3:&lt;/strong&gt; 33
-- &lt;strong&gt;Подвеска:&lt;/strong&gt;пневматическая
-&lt;strong&gt;ДОПОЛНИТЕЛЬНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
-- &lt;strong&gt;Кол-во колес:&lt;/strong&gt; 6+1
-- &lt;strong&gt;Размер шин:&lt;/strong&gt; 385/65R22.5
-- &lt;strong&gt;Платформа:&lt;/strong&gt; Без тента, борта стальные, боковая балка из австрийского профиля
-• &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 2 615 000 ₽
-&lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
-        </is>
-      </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
-          <t>2615000</t>
-        </is>
-      </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/reload_334/01.png | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/reload_334/02.png | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/reload_334/03.png | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/reload_334/04.png | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/reload_334/05.png | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/reload_334/06.png | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/reload_334/07.png | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/reload_334/08.png | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/reload_334/09.png | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/reload_334/10.png</t>
-        </is>
-      </c>
-      <c r="H42" s="1" t="inlineStr">
-        <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="I42" s="1" t="inlineStr">
-        <is>
-          <t>Иван</t>
-        </is>
-      </c>
-      <c r="J42" s="1" t="inlineStr">
-        <is>
-          <t>info@bel-car.com</t>
-        </is>
-      </c>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>79031369484</t>
-        </is>
-      </c>
-      <c r="L42" s="1" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="M42" s="1" t="inlineStr"/>
-      <c r="N42" s="1" t="inlineStr">
-        <is>
-          <t>Под заказ</t>
-        </is>
-      </c>
-      <c r="O42" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P42" s="1" t="inlineStr"/>
-      <c r="Q42" s="1" t="inlineStr">
-        <is>
-          <t>Барабанные</t>
-        </is>
-      </c>
-      <c r="R42" s="1" t="inlineStr"/>
-      <c r="S42" s="1" t="inlineStr"/>
-      <c r="T42" s="1" t="inlineStr">
-        <is>
-          <t>ООО БелКар</t>
-        </is>
-      </c>
-      <c r="U42" s="1" t="inlineStr">
-        <is>
-          <t>RUB</t>
-        </is>
-      </c>
-      <c r="V42" s="1" t="inlineStr">
-        <is>
-          <t>2615000</t>
-        </is>
-      </c>
-      <c r="W42" s="1" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="X42" s="1" t="inlineStr">
-        <is>
-          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
-        </is>
-      </c>
-      <c r="Y42" s="1" t="inlineStr"/>
-      <c r="Z42" s="1" t="inlineStr"/>
-      <c r="AA42" s="1" t="inlineStr"/>
-      <c r="AB42" s="1" t="inlineStr">
-        <is>
-          <t>27200</t>
-        </is>
-      </c>
-      <c r="AC42" s="1" t="inlineStr">
-        <is>
-          <t>МАЗ</t>
-        </is>
-      </c>
-      <c r="AD42" s="1" t="inlineStr">
-        <is>
-          <t>975800-2010</t>
-        </is>
-      </c>
-      <c r="AE42" s="1" t="inlineStr"/>
-      <c r="AF42" s="1" t="inlineStr"/>
-      <c r="AG42" s="1" t="inlineStr">
-        <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
-      <c r="AH42" s="1" t="inlineStr"/>
-      <c r="AI42" s="1" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="AJ42" s="1" t="inlineStr"/>
-      <c r="AK42" s="1" t="inlineStr">
-        <is>
-          <t>Пневматическая</t>
-        </is>
-      </c>
-      <c r="AL42" s="1" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AM42" s="1" t="inlineStr">
-        <is>
-          <t>13600</t>
-        </is>
-      </c>
-      <c r="AN42" s="1" t="inlineStr">
-        <is>
-          <t>56.3</t>
-        </is>
-      </c>
-      <c r="AO42" s="1" t="inlineStr"/>
-      <c r="AP42" s="1" t="inlineStr">
-        <is>
-          <t>Бортовой</t>
-        </is>
-      </c>
-      <c r="AQ42" s="1" t="inlineStr">
-        <is>
-          <t>Полуприцеп</t>
-        </is>
-      </c>
-      <c r="AR42" s="1" t="inlineStr"/>
-      <c r="AS42" s="1" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="AT42" s="1" t="inlineStr"/>
-      <c r="AU42" s="1" t="inlineStr"/>
-      <c r="AV42" s="1" t="inlineStr"/>
-      <c r="AW42" s="1" t="inlineStr">
-        <is>
-          <t>bk-maz-975800-2010</t>
         </is>
       </c>
     </row>

--- a/avito-feed-main/fleet-main.xlsx
+++ b/avito-feed-main/fleet-main.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL38"/>
+  <dimension ref="A1:AM38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -606,6 +606,11 @@
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Id</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>AvitoId</t>
         </is>
       </c>
     </row>
@@ -817,7 +822,12 @@
       <c r="AK2" s="1" t="inlineStr"/>
       <c r="AL2" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-b3-13-9888</t>
+          <t>8118231548</t>
+        </is>
+      </c>
+      <c r="AM2" s="1" t="inlineStr">
+        <is>
+          <t>8118231548</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1050,12 @@
       <c r="AK3" s="1" t="inlineStr"/>
       <c r="AL3" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-9599</t>
+          <t>8118350682</t>
+        </is>
+      </c>
+      <c r="AM3" s="1" t="inlineStr">
+        <is>
+          <t>8118350682</t>
         </is>
       </c>
     </row>
@@ -1270,6 +1285,7 @@
           <t>bk-tonar-r3-13</t>
         </is>
       </c>
+      <c r="AM4" s="1" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1500,7 +1516,12 @@
       <c r="AK5" s="1" t="inlineStr"/>
       <c r="AL5" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-t3-16-98881</t>
+          <t>8118786818</t>
+        </is>
+      </c>
+      <c r="AM5" s="1" t="inlineStr">
+        <is>
+          <t>8118786818</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1747,12 @@
       <c r="AK6" s="1" t="inlineStr"/>
       <c r="AL6" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-l3-9445</t>
+          <t>8118826997</t>
+        </is>
+      </c>
+      <c r="AM6" s="1" t="inlineStr">
+        <is>
+          <t>8118826997</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1970,12 @@
       <c r="AK7" s="1" t="inlineStr"/>
       <c r="AL7" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-t4-16v</t>
+          <t>8150616785</t>
+        </is>
+      </c>
+      <c r="AM7" s="1" t="inlineStr">
+        <is>
+          <t>8150616785</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2206,12 @@
       </c>
       <c r="AL8" s="1" t="inlineStr">
         <is>
-          <t>bk-interpricep-853371</t>
+          <t>V9B8DU2N22</t>
+        </is>
+      </c>
+      <c r="AM8" s="1" t="inlineStr">
+        <is>
+          <t>8252327002</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2434,12 @@
       <c r="AK9" s="1" t="inlineStr"/>
       <c r="AL9" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-95941-12166</t>
+          <t>ad-57304</t>
+        </is>
+      </c>
+      <c r="AM9" s="1" t="inlineStr">
+        <is>
+          <t>8214338881</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2666,12 @@
       <c r="AK10" s="1" t="inlineStr"/>
       <c r="AL10" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-r3-13-13500</t>
+          <t>ad-57373</t>
+        </is>
+      </c>
+      <c r="AM10" s="1" t="inlineStr">
+        <is>
+          <t>8214676066</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2890,12 @@
       <c r="AK11" s="1" t="inlineStr"/>
       <c r="AL11" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-95941</t>
+          <t>b_63</t>
+        </is>
+      </c>
+      <c r="AM11" s="1" t="inlineStr">
+        <is>
+          <t>4438523678</t>
         </is>
       </c>
     </row>
@@ -3078,6 +3129,7 @@
           <t>bk-interpricep-853372</t>
         </is>
       </c>
+      <c r="AM12" s="1" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -3299,7 +3351,12 @@
       </c>
       <c r="AL13" s="1" t="inlineStr">
         <is>
-          <t>bk-interpricep-853375</t>
+          <t>clone-130472-1788640746</t>
+        </is>
+      </c>
+      <c r="AM13" s="1" t="inlineStr">
+        <is>
+          <t>8354178816</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3569,12 @@
       </c>
       <c r="AL14" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-sp3-17</t>
+          <t>,ekrfh0550</t>
+        </is>
+      </c>
+      <c r="AM14" s="1" t="inlineStr">
+        <is>
+          <t>2678907239</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3797,12 @@
       <c r="AK15" s="1" t="inlineStr"/>
       <c r="AL15" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-b4-16v-97882</t>
+          <t>gls-1</t>
+        </is>
+      </c>
+      <c r="AM15" s="1" t="inlineStr">
+        <is>
+          <t>8181970113</t>
         </is>
       </c>
     </row>
@@ -3953,7 +4020,12 @@
       <c r="AK16" s="1" t="inlineStr"/>
       <c r="AL16" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-k3-u-99882</t>
+          <t>gls-11</t>
+        </is>
+      </c>
+      <c r="AM16" s="1" t="inlineStr">
+        <is>
+          <t>8182391576</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4243,12 @@
       <c r="AK17" s="1" t="inlineStr"/>
       <c r="AL17" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-k4-u-99894</t>
+          <t>gls-12</t>
+        </is>
+      </c>
+      <c r="AM17" s="1" t="inlineStr">
+        <is>
+          <t>8182793830</t>
         </is>
       </c>
     </row>
@@ -4404,6 +4481,7 @@
           <t>bk-tonar-t3-13-9888</t>
         </is>
       </c>
+      <c r="AM18" s="1" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -4620,7 +4698,12 @@
       <c r="AK19" s="1" t="inlineStr"/>
       <c r="AL19" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-sl4-34g-9595</t>
+          <t>gls-3</t>
+        </is>
+      </c>
+      <c r="AM19" s="1" t="inlineStr">
+        <is>
+          <t>8182263799</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4932,12 @@
       <c r="AK20" s="1" t="inlineStr"/>
       <c r="AL20" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-9595</t>
+          <t>gls-4</t>
+        </is>
+      </c>
+      <c r="AM20" s="1" t="inlineStr">
+        <is>
+          <t>8182603324</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5158,12 @@
       <c r="AK21" s="1" t="inlineStr"/>
       <c r="AL21" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-sh4-74m-97465</t>
+          <t>gls-5</t>
+        </is>
+      </c>
+      <c r="AM21" s="1" t="inlineStr">
+        <is>
+          <t>8182296576</t>
         </is>
       </c>
     </row>
@@ -5291,6 +5384,7 @@
           <t>bk-tonar-k4-u-99891</t>
         </is>
       </c>
+      <c r="AM22" s="1" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -5498,6 +5592,7 @@
           <t>bk-tonar-b3-16-98881</t>
         </is>
       </c>
+      <c r="AM23" s="1" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -5714,7 +5809,12 @@
       <c r="AK24" s="1" t="inlineStr"/>
       <c r="AL24" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-sh3-33-95892-10965</t>
+          <t>novaia_11</t>
+        </is>
+      </c>
+      <c r="AM24" s="1" t="inlineStr">
+        <is>
+          <t>7382709126</t>
         </is>
       </c>
     </row>
@@ -5931,7 +6031,12 @@
       <c r="AK25" s="1" t="inlineStr"/>
       <c r="AL25" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-sh4-38-95234</t>
+          <t>novaia_13</t>
+        </is>
+      </c>
+      <c r="AM25" s="1" t="inlineStr">
+        <is>
+          <t>7382542432</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6254,12 @@
       <c r="AK26" s="1" t="inlineStr"/>
       <c r="AL26" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-sh4-45-95234</t>
+          <t>novaia_14</t>
+        </is>
+      </c>
+      <c r="AM26" s="1" t="inlineStr">
+        <is>
+          <t>7382525203</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6473,12 @@
       <c r="AK27" s="1" t="inlineStr"/>
       <c r="AL27" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-sh4-60m-sh4-60-952342</t>
+          <t>novaia_15</t>
+        </is>
+      </c>
+      <c r="AM27" s="1" t="inlineStr">
+        <is>
+          <t>7382161564</t>
         </is>
       </c>
     </row>
@@ -6579,6 +6694,7 @@
           <t>bk-tonar-sh3-74m-97464</t>
         </is>
       </c>
+      <c r="AM28" s="1" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -6799,7 +6915,12 @@
       </c>
       <c r="AL29" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-sh3-33-95892</t>
+          <t>novaia_19</t>
+        </is>
+      </c>
+      <c r="AM29" s="1" t="inlineStr">
+        <is>
+          <t>7382810433</t>
         </is>
       </c>
     </row>
@@ -7012,6 +7133,7 @@
           <t>bk-tonar-k3-20-99883</t>
         </is>
       </c>
+      <c r="AM30" s="1" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -7223,6 +7345,7 @@
           <t>bk-tonar-k4-20-9988</t>
         </is>
       </c>
+      <c r="AM31" s="1" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -7431,7 +7554,12 @@
       <c r="AK32" s="1" t="inlineStr"/>
       <c r="AL32" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-k3-40-99881</t>
+          <t>novaia_27</t>
+        </is>
+      </c>
+      <c r="AM32" s="1" t="inlineStr">
+        <is>
+          <t>7382919322</t>
         </is>
       </c>
     </row>
@@ -7641,7 +7769,12 @@
       <c r="AK33" s="1" t="inlineStr"/>
       <c r="AL33" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-k4-40-99893</t>
+          <t>novaia_28</t>
+        </is>
+      </c>
+      <c r="AM33" s="1" t="inlineStr">
+        <is>
+          <t>7382880639</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7993,12 @@
       <c r="AK34" s="1" t="inlineStr"/>
       <c r="AL34" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-r3-13t-97861</t>
+          <t>novaia_31</t>
+        </is>
+      </c>
+      <c r="AM34" s="1" t="inlineStr">
+        <is>
+          <t>7382972002</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8217,12 @@
       <c r="AK35" s="1" t="inlineStr"/>
       <c r="AL35" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-r3-14-97863</t>
+          <t>novaia_32</t>
+        </is>
+      </c>
+      <c r="AM35" s="1" t="inlineStr">
+        <is>
+          <t>7382391396</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8437,12 @@
       <c r="AK36" s="1" t="inlineStr"/>
       <c r="AL36" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-r3-13d-97861</t>
+          <t>novaia_33</t>
+        </is>
+      </c>
+      <c r="AM36" s="1" t="inlineStr">
+        <is>
+          <t>7382937122</t>
         </is>
       </c>
     </row>
@@ -8512,6 +8660,7 @@
           <t>bk-tonar-b4-13v-97883</t>
         </is>
       </c>
+      <c r="AM37" s="1" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -8736,7 +8885,12 @@
       <c r="AK38" s="1" t="inlineStr"/>
       <c r="AL38" s="1" t="inlineStr">
         <is>
-          <t>bk-tonar-t4-13v-97883</t>
+          <t>novaia_8</t>
+        </is>
+      </c>
+      <c r="AM38" s="1" t="inlineStr">
+        <is>
+          <t>7382726366</t>
         </is>
       </c>
     </row>

--- a/avito-feed-main/fleet-main.xlsx
+++ b/avito-feed-main/fleet-main.xlsx
@@ -1798,7 +1798,7 @@
 - &lt;strong&gt;Боковые стенки / борта:&lt;/strong&gt; шторного типа / алюминиевые, 8 шт
 - &lt;strong&gt;Пол:&lt;/strong&gt; настил из ламинированной фанеры толщиной 27 мм
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 4 750 000 ₽
+• &lt;strong&gt;Цена по прайсу производителя&lt;/strong&gt;: 4 750 000 ₽
 • &lt;strong&gt;Скидка от производителя 10%&lt;/strong&gt;: −475 000 ₽
 • &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −475 000 ₽
 • &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 3 800 000 ₽
@@ -2060,7 +2060,7 @@
 — Помощь с оформлением и приобретением техники
 📌 Важно: комплектация, наличие и итоговая стоимость полуприцепа могут меняться. Уточняйте актуальные условия перед покупкой.
 📞 Напишите или позвоните — расскажем подробнее про ИнтерПрицеп 853371, подберем объем кузова и комплектацию под ваши задачи, рассчитаем стоимость и варианты приобретения.
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 2 980 000 ₽</t>
+• &lt;strong&gt;Цена по прайсу производителя&lt;/strong&gt;: 2 980 000 ₽</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
@@ -3209,7 +3209,7 @@
 — Помощь с оформлением и приобретением техники
 📌 Важно: наличие, комплектация и итоговая стоимость могут меняться. Перед покупкой уточните актуальные условия у менеджера.
 📞 Напишите или позвоните — расскажем подробнее про контейнеровоз ИнтерПрицеп 853375, подберем исполнение под ваши задачи, рассчитаем стоимость, лизинг или кредитную программу.
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 2 280 000 ₽</t>
+• &lt;strong&gt;Цена по прайсу производителя&lt;/strong&gt;: 2 280 000 ₽</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
@@ -3406,7 +3406,7 @@
 - &lt;strong&gt;Высота фаркопа автомобиля, мм:&lt;/strong&gt; 650 / 1 000
 - &lt;strong&gt;Диаметр сцепной петли, мм:&lt;/strong&gt; 50, 57 (под беззазорное сцепное устройство)
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 3 900 000 ₽
+• &lt;strong&gt;Цена по прайсу производителя&lt;/strong&gt;: 3 900 000 ₽
 • &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −390 000 ₽
 • &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 3 510 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
@@ -4765,7 +4765,7 @@
 - &lt;strong&gt;Объем кузова, куб.м:&lt;/strong&gt; 34
 - &lt;strong&gt;Минимальный объем масляного бака тягача, л:&lt;/strong&gt; 150
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 4 200 000 ₽
+• &lt;strong&gt;Цена по прайсу производителя&lt;/strong&gt;: 4 200 000 ₽
 • &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −420 000 ₽
 • &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 3 780 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
@@ -8058,7 +8058,7 @@
 - &lt;strong&gt;Пол:&lt;/strong&gt; герметичный; выполнен из сложной сэндвич-панели повышенной прочности; покрытие пола – противоскользящий настил из рифленого алюминия
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 5 000 000 ₽
+• &lt;strong&gt;Цена по прайсу производителя&lt;/strong&gt;: 5 000 000 ₽
 • &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −500 000 ₽
 • &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 4 500 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.

--- a/avito-feed-main/fleet-main.xlsx
+++ b/avito-feed-main/fleet-main.xlsx
@@ -654,10 +654,6 @@
 - &lt;strong&gt;Боковые стенки / борта:&lt;/strong&gt; откидные, крепятся запорами к стойкам / 8 шт
 - &lt;strong&gt;Пол:&lt;/strong&gt; настил из ламинированной фанеры толщиной 27 мм
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 3 150 000 ₽
-• &lt;strong&gt;Скидка от производителя 10%&lt;/strong&gt;: −315 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −315 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 2 520 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -883,9 +879,6 @@
 - &lt;strong&gt;Первая вынесенная ось:&lt;/strong&gt; улучшает распределение нагрузки
 - &lt;strong&gt;Комбинированный задний борт:&lt;/strong&gt; откидной и распашной с разгрузочными лючками
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 5 700 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −500 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 5 200 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -1115,9 +1108,6 @@
 - &lt;strong&gt;Пол:&lt;/strong&gt; герметичный; выполнен из сложной сэндвич-панели повышенной прочности; покрытие пола – противоскользящий настил из рифленого алюминия
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 4 850 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −485 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 4 365 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -1344,10 +1334,6 @@
 - &lt;strong&gt;Объём кузова, куб.м:&lt;/strong&gt; 110,6
 - &lt;strong&gt;Задняя стенка:&lt;/strong&gt; оборудована распашной двустворчатой алюминиевой дверью; на каждой двери по 2 запорных устройства
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 4 150 000 ₽
-• &lt;strong&gt;Скидка от производителя 10%&lt;/strong&gt;: −415 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −415 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 3 320 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -1575,10 +1561,6 @@
 - &lt;strong&gt;Геометрический объём перевозимого груза, куб.м:&lt;/strong&gt; 63
 - &lt;strong&gt;Коники:&lt;/strong&gt; разборные
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 3 200 000 ₽
-• &lt;strong&gt;Скидка от производителя 5%&lt;/strong&gt;: −160 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −320 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 2 720 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -1798,10 +1780,6 @@
 - &lt;strong&gt;Боковые стенки / борта:&lt;/strong&gt; шторного типа / алюминиевые, 8 шт
 - &lt;strong&gt;Пол:&lt;/strong&gt; настил из ламинированной фанеры толщиной 27 мм
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу производителя&lt;/strong&gt;: 4 750 000 ₽
-• &lt;strong&gt;Скидка от производителя 10%&lt;/strong&gt;: −475 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −475 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 3 800 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -2059,8 +2037,7 @@
 — Индивидуальный подбор комплектации
 — Помощь с оформлением и приобретением техники
 📌 Важно: комплектация, наличие и итоговая стоимость полуприцепа могут меняться. Уточняйте актуальные условия перед покупкой.
-📞 Напишите или позвоните — расскажем подробнее про ИнтерПрицеп 853371, подберем объем кузова и комплектацию под ваши задачи, рассчитаем стоимость и варианты приобретения.
-• &lt;strong&gt;Цена по прайсу производителя&lt;/strong&gt;: 2 980 000 ₽</t>
+📞 Напишите или позвоните — расскажем подробнее про ИнтерПрицеп 853371, подберем объем кузова и комплектацию под ваши задачи, рассчитаем стоимость и варианты приобретения.</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
@@ -2275,9 +2252,6 @@
 - &lt;strong&gt;Угол подъема кузова, град:&lt;/strong&gt; 45
 - &lt;strong&gt;Минимальный объём масляного бака тягача, л:&lt;/strong&gt; 150
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 5 400 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −500 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 4 900 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -2499,9 +2473,6 @@
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 - &lt;strong&gt;Крыша:&lt;/strong&gt; сэндвич-панели; 6 потолочных светодиодных фонарей внутреннего освещения обеспечивают высокую яркость и низкое энергопотребление
 • &lt;strong&gt;Наличие&lt;/strong&gt;: 
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 7 365 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −500 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 6 865 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -2731,9 +2702,6 @@
 - &lt;strong&gt;Угол подъёма кузова, град:&lt;/strong&gt; 45
 - &lt;strong&gt;Минимальный объём масляного бака тягача, л:&lt;/strong&gt; 150
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 5 400 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −500 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 4 900 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -2979,8 +2947,7 @@
 — Индивидуальный подбор комплектации
 — Помощь с оформлением и приобретением техники
 📌 Важно: наличие, комплектация и итоговая стоимость могут меняться. Перед покупкой уточните актуальные условия у менеджера.
-📞 Напишите или позвоните — расскажем подробнее про самосвальный полуприцеп ИнтерПрицеп 853372, подберем объем кузова и комплектацию под ваши задачи, рассчитаем стоимость и варианты приобретения.
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 3 690 000 ₽</t>
+📞 Напишите или позвоните — расскажем подробнее про самосвальный полуприцеп ИнтерПрицеп 853372, подберем объем кузова и комплектацию под ваши задачи, рассчитаем стоимость и варианты приобретения.</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
@@ -3208,8 +3175,7 @@
 — Индивидуальный подбор комплектации
 — Помощь с оформлением и приобретением техники
 📌 Важно: наличие, комплектация и итоговая стоимость могут меняться. Перед покупкой уточните актуальные условия у менеджера.
-📞 Напишите или позвоните — расскажем подробнее про контейнеровоз ИнтерПрицеп 853375, подберем исполнение под ваши задачи, рассчитаем стоимость, лизинг или кредитную программу.
-• &lt;strong&gt;Цена по прайсу производителя&lt;/strong&gt;: 2 280 000 ₽</t>
+📞 Напишите или позвоните — расскажем подробнее про контейнеровоз ИнтерПрицеп 853375, подберем исполнение под ваши задачи, рассчитаем стоимость, лизинг или кредитную программу.</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
@@ -3406,9 +3372,6 @@
 - &lt;strong&gt;Высота фаркопа автомобиля, мм:&lt;/strong&gt; 650 / 1 000
 - &lt;strong&gt;Диаметр сцепной петли, мм:&lt;/strong&gt; 50, 57 (под беззазорное сцепное устройство)
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу производителя&lt;/strong&gt;: 3 900 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −390 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 3 510 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -3629,10 +3592,6 @@
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 - &lt;strong&gt;Пол:&lt;/strong&gt; настил из ламинированной фанеры толщиной 27 мм
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 3 800 000 ₽
-• &lt;strong&gt;Скидка от производителя 10%&lt;/strong&gt;: −380 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −380 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 3 040 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -3852,10 +3811,6 @@
 - &lt;strong&gt;Типы перевозимых контейнеров:&lt;/strong&gt; 40° High Cube
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 2 850 000 ₽
-• &lt;strong&gt;Скидка от производителя 5%&lt;/strong&gt;: −142 500 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −285 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 2 422 500 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -4075,10 +4030,6 @@
 - &lt;strong&gt;Типы перевозимых контейнеров:&lt;/strong&gt; 1x20', 2x20', 1x30, 1x40' High Cube. ДОПОГ АТ, FL, EX/II, EX/III
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 3 250 000 ₽
-• &lt;strong&gt;Скидка от производителя 5%&lt;/strong&gt;: −162 500 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −325 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 2 762 500 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -4310,10 +4261,6 @@
 &lt;strong&gt;ГРУЗОПОДЪЁМНОСТЬ:&lt;/strong&gt;
 - Перевозка грузов массой до 31 000 килограммов
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 3 800 000 ₽
-• &lt;strong&gt;Скидка от производителя 10%&lt;/strong&gt;: −380 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −380 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 3 040 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -4535,9 +4482,6 @@
 - &lt;strong&gt;Тип гидросистемы:&lt;/strong&gt; одноконтурный
 - &lt;strong&gt;Угол подъёма кузова, град:&lt;/strong&gt; 46
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 4 200 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −420 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 3 780 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -4765,9 +4709,6 @@
 - &lt;strong&gt;Объем кузова, куб.м:&lt;/strong&gt; 34
 - &lt;strong&gt;Минимальный объем масляного бака тягача, л:&lt;/strong&gt; 150
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу производителя&lt;/strong&gt;: 4 200 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −420 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 3 780 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -4991,9 +4932,6 @@
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 - &lt;strong&gt;Объём кузова, куб.м:&lt;/strong&gt; 74
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 5 200 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −500 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 4 700 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -5213,10 +5151,6 @@
 - &lt;strong&gt;Типы перевозимых контейнеров:&lt;/strong&gt; 20', 2x20', 30', 30' HC, 40', 40'HC
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 3 200 000 ₽
-• &lt;strong&gt;Скидка от производителя 5%&lt;/strong&gt;: −160 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −320 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 2 720 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -5429,10 +5363,6 @@
 - &lt;strong&gt;Пол:&lt;/strong&gt; ламинированная фанера 27 мм
 - &lt;strong&gt;Дополнительные опции:&lt;/strong&gt; коники (12 шт.) с ящиком для хранения
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 3 300 000 ₽
-• &lt;strong&gt;Скидка от производителя 10%&lt;/strong&gt;: −330 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −330 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 2 640 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -5650,9 +5580,6 @@
 - &lt;strong&gt;Колея колёс, мм:&lt;/strong&gt; 2 040
 - &lt;strong&gt;Рабочее давление в системе, bar:&lt;/strong&gt; 160
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 3 900 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −390 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 3 510 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -5872,9 +5799,6 @@
 - &lt;strong&gt;Угол подъёма кузова, град:&lt;/strong&gt; 48
 - &lt;strong&gt;Рабочее давление в системе, bar:&lt;/strong&gt; 160
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 4 700 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −470 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 4 230 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -6095,9 +6019,6 @@
 - &lt;strong&gt;Угол подъёма кузова, град 48:&lt;/strong&gt; 48
 - &lt;strong&gt;Рабочее давление в системе, bar:&lt;/strong&gt; 160
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 4 800 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −480 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 4 320 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -6314,9 +6235,6 @@
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 - &lt;strong&gt;Угол подъема кузова, град:&lt;/strong&gt; 48
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 5 700 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −500 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 5 200 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -6532,9 +6450,6 @@
 - &lt;strong&gt;Объём кузова, куб.м:&lt;/strong&gt; 74
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 4 700 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −470 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 4 230 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -6752,9 +6667,6 @@
 - &lt;strong&gt;Колея колёс, мм:&lt;/strong&gt; 2 040
 - &lt;strong&gt;Рабочее давление в системе, bar:&lt;/strong&gt; 160
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 3 900 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −390 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 3 510 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -6970,10 +6882,6 @@
 - &lt;strong&gt;Типы перевозимых контейнеров:&lt;/strong&gt; 20', 20'HC
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 2 250 000 ₽
-• &lt;strong&gt;Скидка от производителя 5%&lt;/strong&gt;: −112 500 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −225 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 1 912 500 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -7182,10 +7090,6 @@
 - &lt;strong&gt;Типы перевозимых контейнеров:&lt;/strong&gt; 20', 20* Танк. ДОПОГ АТ, FL, EX/II 
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: 
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 2 950 000 ₽
-• &lt;strong&gt;Скидка от производителя 5%&lt;/strong&gt;: −147 500 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −295 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 2 507 500 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -7394,10 +7298,6 @@
 - &lt;strong&gt;Типы перевозимых контейнеров:&lt;/strong&gt; 40' High Cube. ДОПОГ АТ, FL, EX/II, EX/II
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 2 250 000 ₽
-• &lt;strong&gt;Скидка от производителя 5%&lt;/strong&gt;: −112 500 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −225 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 1 912 500 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -7609,10 +7509,6 @@
 - &lt;strong&gt;Типы перевозимых контейнеров:&lt;/strong&gt; 40° СПГ Танк. ДОПОГ АТ, FL, EX/I
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 2 850 000 ₽
-• &lt;strong&gt;Скидка от производителя 5%&lt;/strong&gt;: −142 500 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −285 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 2 422 500 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -7834,9 +7730,6 @@
 - &lt;strong&gt;Пол:&lt;/strong&gt; герметичный; выполнен из сложной сэндвич-панели повышенной прочности; покрытие пола – противоскользящий настил из рифленого алюминия
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 6 450 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −500 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 5 950 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -8058,9 +7951,6 @@
 - &lt;strong&gt;Пол:&lt;/strong&gt; герметичный; выполнен из сложной сэндвич-панели повышенной прочности; покрытие пола – противоскользящий настил из рифленого алюминия
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу производителя&lt;/strong&gt;: 5 000 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −500 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 4 500 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -8282,9 +8172,6 @@
 - &lt;strong&gt;Пол:&lt;/strong&gt; герметичный; выполнен из сложной сэндвич-панели повышенной прочности; покрытие пола – противоскользящий настил из рифленого алюминия
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 5 550 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −500 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 5 050 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -8497,10 +8384,6 @@
 - &lt;strong&gt;Пол:&lt;/strong&gt; настил из ламинированной фанеры толщиной 27 мм
 - &lt;strong&gt;Передний борт:&lt;/strong&gt; металлический, съемный
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 3 700 000 ₽
-• &lt;strong&gt;Скидка от производителя 10%&lt;/strong&gt;: −370 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −370 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 2 960 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
@@ -8721,10 +8604,6 @@
 &lt;strong&gt;ГРУЗОПОДЪЁМНОСТЬ:&lt;/strong&gt;
 - предназначен для перевозки грузов массой до 27 000 килограммов
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
-• &lt;strong&gt;Цена по прайсу завода&lt;/strong&gt;: 4 250 000 ₽
-• &lt;strong&gt;Скидка от производителя 10%&lt;/strong&gt;: −425 000 ₽
-• &lt;strong&gt;При покупке в лизинг — субсидия Минпромторга&lt;/strong&gt; (10%, не более 500 000 ₽): −425 000 ₽
-• &lt;strong&gt;Итоговая цена при лизинге&lt;/strong&gt;: 3 400 000 ₽
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
 &lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
 &lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>

--- a/avito-feed-main/fleet-main.xlsx
+++ b/avito-feed-main/fleet-main.xlsx
@@ -1200,7 +1200,7 @@
       </c>
       <c r="V4" s="1" t="inlineStr">
         <is>
-          <t>38080</t>
+          <t>30410</t>
         </is>
       </c>
       <c r="W4" s="1" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="V6" s="1" t="inlineStr">
         <is>
-          <t>43000</t>
+          <t>36700</t>
         </is>
       </c>
       <c r="W6" s="1" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="V7" s="1" t="inlineStr">
         <is>
-          <t>27000</t>
+          <t>28200</t>
         </is>
       </c>
       <c r="W7" s="1" t="inlineStr">
@@ -2115,7 +2115,7 @@
       <c r="U8" s="1" t="inlineStr"/>
       <c r="V8" s="1" t="inlineStr">
         <is>
-          <t>47000</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="W8" s="1" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="V10" s="1" t="inlineStr">
         <is>
-          <t>38080</t>
+          <t>29480</t>
         </is>
       </c>
       <c r="W10" s="1" t="inlineStr">
@@ -3025,7 +3025,7 @@
       <c r="U12" s="1" t="inlineStr"/>
       <c r="V12" s="1" t="inlineStr">
         <is>
-          <t>47000</t>
+          <t>38800</t>
         </is>
       </c>
       <c r="W12" s="1" t="inlineStr">
@@ -3253,7 +3253,7 @@
       <c r="U13" s="1" t="inlineStr"/>
       <c r="V13" s="1" t="inlineStr">
         <is>
-          <t>47000</t>
+          <t>41600</t>
         </is>
       </c>
       <c r="W13" s="1" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="V14" s="1" t="inlineStr">
         <is>
-          <t>17700</t>
+          <t>19600</t>
         </is>
       </c>
       <c r="W14" s="1" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="V15" s="1" t="inlineStr">
         <is>
-          <t>31800</t>
+          <t>28200</t>
         </is>
       </c>
       <c r="W15" s="1" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="V16" s="1" t="inlineStr">
         <is>
-          <t>38000</t>
+          <t>32600</t>
         </is>
       </c>
       <c r="W16" s="1" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="V17" s="1" t="inlineStr">
         <is>
-          <t>44000</t>
+          <t>37800</t>
         </is>
       </c>
       <c r="W17" s="1" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="V19" s="1" t="inlineStr">
         <is>
-          <t>31800</t>
+          <t>27950</t>
         </is>
       </c>
       <c r="W19" s="1" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="V21" s="1" t="inlineStr">
         <is>
-          <t>49000</t>
+          <t>35500</t>
         </is>
       </c>
       <c r="W21" s="1" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="V22" s="1" t="inlineStr">
         <is>
-          <t>44000</t>
+          <t>37800</t>
         </is>
       </c>
       <c r="W22" s="1" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="V23" s="1" t="inlineStr">
         <is>
-          <t>38600</t>
+          <t>30300</t>
         </is>
       </c>
       <c r="W23" s="1" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="V24" s="1" t="inlineStr">
         <is>
-          <t>37500</t>
+          <t>28800</t>
         </is>
       </c>
       <c r="W24" s="1" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="V25" s="1" t="inlineStr">
         <is>
-          <t>48070</t>
+          <t>37230</t>
         </is>
       </c>
       <c r="W25" s="1" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="V26" s="1" t="inlineStr">
         <is>
-          <t>48070</t>
+          <t>36920</t>
         </is>
       </c>
       <c r="W26" s="1" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="V27" s="1" t="inlineStr">
         <is>
-          <t>51500</t>
+          <t>38040</t>
         </is>
       </c>
       <c r="W27" s="1" t="inlineStr">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="V28" s="1" t="inlineStr">
         <is>
-          <t>39000</t>
+          <t>26450</t>
         </is>
       </c>
       <c r="W28" s="1" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="V30" s="1" t="inlineStr">
         <is>
-          <t>40100</t>
+          <t>35860</t>
         </is>
       </c>
       <c r="W30" s="1" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="V31" s="1" t="inlineStr">
         <is>
-          <t>42000</t>
+          <t>36550</t>
         </is>
       </c>
       <c r="W31" s="1" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="V32" s="1" t="inlineStr">
         <is>
-          <t>42300</t>
+          <t>38040</t>
         </is>
       </c>
       <c r="W32" s="1" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="V33" s="1" t="inlineStr">
         <is>
-          <t>38000</t>
+          <t>32600</t>
         </is>
       </c>
       <c r="W33" s="1" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="V34" s="1" t="inlineStr">
         <is>
-          <t>38080</t>
+          <t>26860</t>
         </is>
       </c>
       <c r="W34" s="1" t="inlineStr">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="V35" s="1" t="inlineStr">
         <is>
-          <t>34500</t>
+          <t>25800</t>
         </is>
       </c>
       <c r="W35" s="1" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="V36" s="1" t="inlineStr">
         <is>
-          <t>38080</t>
+          <t>30160</t>
         </is>
       </c>
       <c r="W36" s="1" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="V37" s="1" t="inlineStr">
         <is>
-          <t>37500</t>
+          <t>29400</t>
         </is>
       </c>
       <c r="W37" s="1" t="inlineStr">
@@ -8692,7 +8692,7 @@
       </c>
       <c r="V38" s="1" t="inlineStr">
         <is>
-          <t>37500</t>
+          <t>29400</t>
         </is>
       </c>
       <c r="W38" s="1" t="inlineStr">

--- a/avito-feed-main/fleet-main.xlsx
+++ b/avito-feed-main/fleet-main.xlsx
@@ -2755,7 +2755,7 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr">
@@ -7484,7 +7484,7 @@
           <t>&lt;strong&gt;Полуприцеп Тонар K4-40 (99893) / 2026 года выпуска&lt;/strong&gt;
 &lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
-- &lt;strong&gt;Количество осей:&lt;/strong&gt; 3, 1-я подъемная
+- &lt;strong&gt;Количество осей:&lt;/strong&gt; 4, 1-я подъемная
 - &lt;strong&gt;Подвеска:&lt;/strong&gt; рычажного типа
 - &lt;strong&gt;ССУ:&lt;/strong&gt; 1100
 - &lt;strong&gt;Тип:&lt;/strong&gt; полуприцеп-контейнеровоз

--- a/avito-feed-main/fleet-main.xlsx
+++ b/avito-feed-main/fleet-main.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM38"/>
+  <dimension ref="A1:AK38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -540,75 +540,65 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>OfficialGuarantee</t>
+          <t>Parking</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>PriceWithVAT</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>PriceWithVAT</t>
+          <t>SuspensionChassis</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>SuspensionChassis</t>
+          <t>TechnicalPassport</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>TechnicalPassport</t>
+          <t>TrailerLength</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>TrailerLength</t>
+          <t>TrailerVolume</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>TrailerVolume</t>
+          <t>TypeOfTrailer</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>TypeOfTrailer</t>
+          <t>TypeOfVehicle</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>TypeOfVehicle</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>LeasingDiscount</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>LeasingDiscount</t>
+          <t>DealerDiscount</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>DealerDiscount</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>AdditionalGuarantee</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>AvitoId</t>
         </is>
@@ -761,48 +751,48 @@
       </c>
       <c r="Y2" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
       <c r="Z2" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA2" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB2" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC2" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD2" s="1" t="inlineStr">
-        <is>
           <t>13625</t>
         </is>
       </c>
-      <c r="AE2" s="1" t="inlineStr"/>
+      <c r="AD2" s="1" t="inlineStr"/>
+      <c r="AE2" s="1" t="inlineStr">
+        <is>
+          <t>Бортовой</t>
+        </is>
+      </c>
       <c r="AF2" s="1" t="inlineStr">
         <is>
-          <t>Бортовой</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG2" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH2" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>315000</t>
         </is>
       </c>
       <c r="AI2" s="1" t="inlineStr">
@@ -812,16 +802,10 @@
       </c>
       <c r="AJ2" s="1" t="inlineStr">
         <is>
-          <t>315000</t>
-        </is>
-      </c>
-      <c r="AK2" s="1" t="inlineStr"/>
-      <c r="AL2" s="1" t="inlineStr">
-        <is>
           <t>8118231548</t>
         </is>
       </c>
-      <c r="AM2" s="1" t="inlineStr">
+      <c r="AK2" s="1" t="inlineStr">
         <is>
           <t>8118231548</t>
         </is>
@@ -986,67 +970,61 @@
       </c>
       <c r="Y3" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
       <c r="Z3" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA3" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB3" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC3" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>12190</t>
         </is>
       </c>
       <c r="AD3" s="1" t="inlineStr">
         <is>
-          <t>12190</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE3" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>Зерновоз</t>
         </is>
       </c>
       <c r="AF3" s="1" t="inlineStr">
         <is>
-          <t>Зерновоз</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG3" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH3" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AI3" s="1" t="inlineStr">
-        <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="AJ3" s="1" t="inlineStr"/>
-      <c r="AK3" s="1" t="inlineStr"/>
-      <c r="AL3" s="1" t="inlineStr">
+      <c r="AI3" s="1" t="inlineStr"/>
+      <c r="AJ3" s="1" t="inlineStr">
         <is>
           <t>8118350682</t>
         </is>
       </c>
-      <c r="AM3" s="1" t="inlineStr">
+      <c r="AK3" s="1" t="inlineStr">
         <is>
           <t>8118350682</t>
         </is>
@@ -1215,67 +1193,61 @@
       </c>
       <c r="Y4" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
       <c r="Z4" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA4" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB4" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC4" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>13500</t>
         </is>
       </c>
       <c r="AD4" s="1" t="inlineStr">
         <is>
-          <t>13500</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AE4" s="1" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>Изотермический</t>
         </is>
       </c>
       <c r="AF4" s="1" t="inlineStr">
         <is>
-          <t>Изотермический</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG4" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH4" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AI4" s="1" t="inlineStr">
-        <is>
           <t>485000</t>
         </is>
       </c>
-      <c r="AJ4" s="1" t="inlineStr"/>
+      <c r="AI4" s="1" t="inlineStr"/>
+      <c r="AJ4" s="1" t="inlineStr">
+        <is>
+          <t>bk-tonar-r3-13</t>
+        </is>
+      </c>
       <c r="AK4" s="1" t="inlineStr"/>
-      <c r="AL4" s="1" t="inlineStr">
-        <is>
-          <t>bk-tonar-r3-13</t>
-        </is>
-      </c>
-      <c r="AM4" s="1" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1441,52 +1413,52 @@
       </c>
       <c r="Y5" s="1" t="inlineStr">
         <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
+      <c r="Z5" s="1" t="inlineStr">
+        <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="Z5" s="1" t="inlineStr">
-        <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
-        </is>
-      </c>
       <c r="AA5" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB5" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC5" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>16500</t>
         </is>
       </c>
       <c r="AD5" s="1" t="inlineStr">
         <is>
-          <t>16500</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AE5" s="1" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>Шторно-бортовой</t>
         </is>
       </c>
       <c r="AF5" s="1" t="inlineStr">
         <is>
-          <t>Шторно-бортовой</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG5" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH5" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>415000</t>
         </is>
       </c>
       <c r="AI5" s="1" t="inlineStr">
@@ -1496,16 +1468,10 @@
       </c>
       <c r="AJ5" s="1" t="inlineStr">
         <is>
-          <t>415000</t>
-        </is>
-      </c>
-      <c r="AK5" s="1" t="inlineStr"/>
-      <c r="AL5" s="1" t="inlineStr">
-        <is>
           <t>8118786818</t>
         </is>
       </c>
-      <c r="AM5" s="1" t="inlineStr">
+      <c r="AK5" s="1" t="inlineStr">
         <is>
           <t>8118786818</t>
         </is>
@@ -1668,71 +1634,65 @@
       </c>
       <c r="Y6" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
       <c r="Z6" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA6" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB6" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC6" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="AD6" s="1" t="inlineStr">
         <is>
-          <t>12800</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AE6" s="1" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>Лесовоз (сортиментовоз)</t>
         </is>
       </c>
       <c r="AF6" s="1" t="inlineStr">
         <is>
-          <t>Лесовоз (сортиментовоз)</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG6" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH6" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="AI6" s="1" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="AJ6" s="1" t="inlineStr">
         <is>
-          <t>160000</t>
-        </is>
-      </c>
-      <c r="AK6" s="1" t="inlineStr"/>
-      <c r="AL6" s="1" t="inlineStr">
-        <is>
           <t>8118826997</t>
         </is>
       </c>
-      <c r="AM6" s="1" t="inlineStr">
+      <c r="AK6" s="1" t="inlineStr">
         <is>
           <t>8118826997</t>
         </is>
@@ -1887,52 +1847,52 @@
       </c>
       <c r="Y7" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
       <c r="Z7" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA7" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB7" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC7" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>16500</t>
         </is>
       </c>
       <c r="AD7" s="1" t="inlineStr">
         <is>
-          <t>16500</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AE7" s="1" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>Шторно-бортовой</t>
         </is>
       </c>
       <c r="AF7" s="1" t="inlineStr">
         <is>
-          <t>Шторно-бортовой</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG7" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH7" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>475000</t>
         </is>
       </c>
       <c r="AI7" s="1" t="inlineStr">
@@ -1942,16 +1902,10 @@
       </c>
       <c r="AJ7" s="1" t="inlineStr">
         <is>
-          <t>475000</t>
-        </is>
-      </c>
-      <c r="AK7" s="1" t="inlineStr"/>
-      <c r="AL7" s="1" t="inlineStr">
-        <is>
           <t>8150616785</t>
         </is>
       </c>
-      <c r="AM7" s="1" t="inlineStr">
+      <c r="AK7" s="1" t="inlineStr">
         <is>
           <t>8150616785</t>
         </is>
@@ -1974,7 +1928,6 @@
           <t>Полуприцеп зерновоз ИнтерПрицеп 853371, 4 оси / 2026 года выпуска
 Новый полуприцеп зерновоз ИнтерПрицеп 853371 для перевозки зерна и сельскохозяйственных грузов. Объем кузова — 52–61 м³, грузоподъемность — 39 100 кг, разрешенная максимальная масса — 47 000 кг.
 Четырехосный зерновоз оснащается пневматической подвеской с функцией подъема осей. Высота борта и объем кузова могут быть подобраны под задачи заказчика.
-Гарантия — 24 месяца без ограничения пробега.
 🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:
 — Тип: полуприцеп зерновоз
 — Модель: ИнтерПрицеп 853371
@@ -2031,7 +1984,6 @@
 — Инструментальный ящик DAKEN с замком
 — Рукомойник для водителя LOKHEN
 💼 УСЛОВИЯ ПОКУПКИ:
-— Гарантия 24 месяца без ограничения пробега
 — Лизинг
 — Кредитные программы
 — Индивидуальный подбор комплектации
@@ -2112,7 +2064,11 @@
         </is>
       </c>
       <c r="T8" s="1" t="inlineStr"/>
-      <c r="U8" s="1" t="inlineStr"/>
+      <c r="U8" s="1" t="inlineStr">
+        <is>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
+        </is>
+      </c>
       <c r="V8" s="1" t="inlineStr">
         <is>
           <t>39100</t>
@@ -2128,65 +2084,59 @@
           <t>853371</t>
         </is>
       </c>
-      <c r="Y8" s="1" t="inlineStr"/>
+      <c r="Y8" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
       <c r="Z8" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA8" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB8" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC8" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="AD8" s="1" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AE8" s="1" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>Зерновоз</t>
         </is>
       </c>
       <c r="AF8" s="1" t="inlineStr">
         <is>
-          <t>Зерновоз</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG8" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
-        </is>
-      </c>
-      <c r="AH8" s="1" t="inlineStr">
-        <is>
           <t>2026</t>
         </is>
       </c>
+      <c r="AH8" s="1" t="inlineStr"/>
       <c r="AI8" s="1" t="inlineStr"/>
-      <c r="AJ8" s="1" t="inlineStr"/>
+      <c r="AJ8" s="1" t="inlineStr">
+        <is>
+          <t>V9B8DU2N22</t>
+        </is>
+      </c>
       <c r="AK8" s="1" t="inlineStr">
-        <is>
-          <t>Без ограничения по пробегу</t>
-        </is>
-      </c>
-      <c r="AL8" s="1" t="inlineStr">
-        <is>
-          <t>V9B8DU2N22</t>
-        </is>
-      </c>
-      <c r="AM8" s="1" t="inlineStr">
         <is>
           <t>8252327002</t>
         </is>
@@ -2353,65 +2303,63 @@
           <t>95941</t>
         </is>
       </c>
-      <c r="Y9" s="1" t="inlineStr"/>
+      <c r="Y9" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
       <c r="Z9" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA9" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB9" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC9" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>12166</t>
         </is>
       </c>
       <c r="AD9" s="1" t="inlineStr">
         <is>
-          <t>12166</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE9" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>Зерновоз</t>
         </is>
       </c>
       <c r="AF9" s="1" t="inlineStr">
         <is>
-          <t>Зерновоз</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG9" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH9" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AI9" s="1" t="inlineStr">
-        <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="AJ9" s="1" t="inlineStr"/>
-      <c r="AK9" s="1" t="inlineStr"/>
-      <c r="AL9" s="1" t="inlineStr">
+      <c r="AI9" s="1" t="inlineStr"/>
+      <c r="AJ9" s="1" t="inlineStr">
         <is>
           <t>ad-57304</t>
         </is>
       </c>
-      <c r="AM9" s="1" t="inlineStr">
+      <c r="AK9" s="1" t="inlineStr">
         <is>
           <t>8214338881</t>
         </is>
@@ -2580,67 +2528,61 @@
       </c>
       <c r="Y10" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
       <c r="Z10" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA10" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB10" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC10" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>13500</t>
         </is>
       </c>
       <c r="AD10" s="1" t="inlineStr">
         <is>
-          <t>13500</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AE10" s="1" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>Рефрижератор</t>
         </is>
       </c>
       <c r="AF10" s="1" t="inlineStr">
         <is>
-          <t>Рефрижератор</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG10" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH10" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AI10" s="1" t="inlineStr">
-        <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="AJ10" s="1" t="inlineStr"/>
-      <c r="AK10" s="1" t="inlineStr"/>
-      <c r="AL10" s="1" t="inlineStr">
+      <c r="AI10" s="1" t="inlineStr"/>
+      <c r="AJ10" s="1" t="inlineStr">
         <is>
           <t>ad-57373</t>
         </is>
       </c>
-      <c r="AM10" s="1" t="inlineStr">
+      <c r="AK10" s="1" t="inlineStr">
         <is>
           <t>8214676066</t>
         </is>
@@ -2803,65 +2745,63 @@
           <t>95941</t>
         </is>
       </c>
-      <c r="Y11" s="1" t="inlineStr"/>
+      <c r="Y11" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
       <c r="Z11" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA11" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB11" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC11" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>9834</t>
         </is>
       </c>
       <c r="AD11" s="1" t="inlineStr">
         <is>
-          <t>9834</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AE11" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>Зерновоз</t>
         </is>
       </c>
       <c r="AF11" s="1" t="inlineStr">
         <is>
-          <t>Зерновоз</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG11" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH11" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AI11" s="1" t="inlineStr">
-        <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="AJ11" s="1" t="inlineStr"/>
-      <c r="AK11" s="1" t="inlineStr"/>
-      <c r="AL11" s="1" t="inlineStr">
+      <c r="AI11" s="1" t="inlineStr"/>
+      <c r="AJ11" s="1" t="inlineStr">
         <is>
           <t>b_63</t>
         </is>
       </c>
-      <c r="AM11" s="1" t="inlineStr">
+      <c r="AK11" s="1" t="inlineStr">
         <is>
           <t>4438523678</t>
         </is>
@@ -2884,7 +2824,6 @@
           <t>Полуприцеп самосвальный ИнтерПрицеп 853372, 4 оси / 2026 года выпуска
 Новый самосвальный полуприцеп ИнтерПрицеп 853372 с задней разгрузкой. Четырехосный полуприцеп-самосвал с объемом кузова 45–55 м³ и грузоподъемностью 38 800 кг.
 Разгрузка — задний свал. Установлен 1 обратный гидроцилиндр Mariz/Binotto (Италия). Собственная масса полуприцепа — 8 200 кг, технически допустимая масса — 47 000 кг.
-Гарантия — 24 месяца без ограничения пробега.
 🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:
 — Тип: самосвальный полуприцеп
 — Модель: ИнтерПрицеп 853372
@@ -2941,7 +2880,6 @@
 — Гидроцилиндр Mariz/Binotto (Италия)
 — Фитинги Camozzi (Италия)
 💼 УСЛОВИЯ ПОКУПКИ:
-— Гарантия 24 месяца без ограничения пробега
 — Лизинг
 — Кредитные программы
 — Индивидуальный подбор комплектации
@@ -3022,7 +2960,11 @@
         </is>
       </c>
       <c r="T12" s="1" t="inlineStr"/>
-      <c r="U12" s="1" t="inlineStr"/>
+      <c r="U12" s="1" t="inlineStr">
+        <is>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
+        </is>
+      </c>
       <c r="V12" s="1" t="inlineStr">
         <is>
           <t>38800</t>
@@ -3038,65 +2980,59 @@
           <t>853372</t>
         </is>
       </c>
-      <c r="Y12" s="1" t="inlineStr"/>
+      <c r="Y12" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
       <c r="Z12" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA12" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB12" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC12" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>12250</t>
         </is>
       </c>
       <c r="AD12" s="1" t="inlineStr">
         <is>
-          <t>12250</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE12" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>Самосвальный</t>
         </is>
       </c>
       <c r="AF12" s="1" t="inlineStr">
         <is>
-          <t>Самосвальный</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG12" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
-        </is>
-      </c>
-      <c r="AH12" s="1" t="inlineStr">
-        <is>
           <t>2026</t>
         </is>
       </c>
+      <c r="AH12" s="1" t="inlineStr"/>
       <c r="AI12" s="1" t="inlineStr"/>
-      <c r="AJ12" s="1" t="inlineStr"/>
-      <c r="AK12" s="1" t="inlineStr">
-        <is>
-          <t>Без ограничения по пробегу</t>
-        </is>
-      </c>
-      <c r="AL12" s="1" t="inlineStr">
+      <c r="AJ12" s="1" t="inlineStr">
         <is>
           <t>bk-interpricep-853372</t>
         </is>
       </c>
-      <c r="AM12" s="1" t="inlineStr"/>
+      <c r="AK12" s="1" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -3116,7 +3052,6 @@
 Новый полуприцеп контейнеровоз ИнтерПрицеп 853375 для перевозки морских и грузовых контейнеров. Рассчитан на размещение 1 контейнера 40FT или 2 контейнеров 20FT.
 Четырехосный контейнеровоз грузоподъемностью 41 600 кг оснащен пневматической подвеской с подъемными осями и контейнерными замками JOST / AKKAR / LN. Собственная масса полуприцепа — 5 400 кг.
 Модель изготавливается как со стандартным расположением осей, так и с вынесенной первой осью.
-Гарантия — 24 месяца без ограничения пробега.
 🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:
 — Тип: полуприцеп контейнеровоз
 — Модель: ИнтерПрицеп 853375
@@ -3169,7 +3104,6 @@
 — Рукомойник для водителя LOKHEN
 — Запасное колесо
 💼 УСЛОВИЯ ПОКУПКИ:
-— Гарантия 24 месяца без ограничения пробега
 — Лизинг
 — Кредитные программы
 — Индивидуальный подбор комплектации
@@ -3250,7 +3184,11 @@
         </is>
       </c>
       <c r="T13" s="1" t="inlineStr"/>
-      <c r="U13" s="1" t="inlineStr"/>
+      <c r="U13" s="1" t="inlineStr">
+        <is>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Ингушетия | Иркутская область | Кабардино-Балкария | Калининградская область | Калмыкия | Калужская область | Камчатский край | Карачаево-Черкесия | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Дагестан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Северная Осетия | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Ставропольский край | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Чеченская Республика | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
+        </is>
+      </c>
       <c r="V13" s="1" t="inlineStr">
         <is>
           <t>41600</t>
@@ -3266,61 +3204,55 @@
           <t>853375</t>
         </is>
       </c>
-      <c r="Y13" s="1" t="inlineStr"/>
+      <c r="Y13" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
       <c r="Z13" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA13" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB13" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC13" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="AD13" s="1" t="inlineStr">
-        <is>
           <t>12600</t>
         </is>
       </c>
-      <c r="AE13" s="1" t="inlineStr"/>
+      <c r="AD13" s="1" t="inlineStr"/>
+      <c r="AE13" s="1" t="inlineStr">
+        <is>
+          <t>Контейнеровоз</t>
+        </is>
+      </c>
       <c r="AF13" s="1" t="inlineStr">
         <is>
-          <t>Контейнеровоз</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG13" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
-        </is>
-      </c>
-      <c r="AH13" s="1" t="inlineStr">
-        <is>
           <t>2026</t>
         </is>
       </c>
+      <c r="AH13" s="1" t="inlineStr"/>
       <c r="AI13" s="1" t="inlineStr"/>
-      <c r="AJ13" s="1" t="inlineStr"/>
+      <c r="AJ13" s="1" t="inlineStr">
+        <is>
+          <t>clone-130472-1788640746</t>
+        </is>
+      </c>
       <c r="AK13" s="1" t="inlineStr">
-        <is>
-          <t>Без ограничения по пробегу</t>
-        </is>
-      </c>
-      <c r="AL13" s="1" t="inlineStr">
-        <is>
-          <t>clone-130472-1788640746</t>
-        </is>
-      </c>
-      <c r="AM13" s="1" t="inlineStr">
         <is>
           <t>8354178816</t>
         </is>
@@ -3473,69 +3405,63 @@
           <t>SP3-17</t>
         </is>
       </c>
-      <c r="Y14" s="1" t="inlineStr"/>
+      <c r="Y14" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
       <c r="Z14" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA14" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB14" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC14" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>9450</t>
         </is>
       </c>
       <c r="AD14" s="1" t="inlineStr">
         <is>
-          <t>9450</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE14" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>Самосвальный</t>
         </is>
       </c>
       <c r="AF14" s="1" t="inlineStr">
         <is>
-          <t>Самосвальный</t>
+          <t>Прицеп</t>
         </is>
       </c>
       <c r="AG14" s="1" t="inlineStr">
         <is>
-          <t>Прицеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH14" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AI14" s="1" t="inlineStr">
-        <is>
           <t>390000</t>
         </is>
       </c>
-      <c r="AJ14" s="1" t="inlineStr"/>
+      <c r="AI14" s="1" t="inlineStr"/>
+      <c r="AJ14" s="1" t="inlineStr">
+        <is>
+          <t>,ekrfh0550</t>
+        </is>
+      </c>
       <c r="AK14" s="1" t="inlineStr">
-        <is>
-          <t>Без ограничения по пробегу</t>
-        </is>
-      </c>
-      <c r="AL14" s="1" t="inlineStr">
-        <is>
-          <t>,ekrfh0550</t>
-        </is>
-      </c>
-      <c r="AM14" s="1" t="inlineStr">
         <is>
           <t>2678907239</t>
         </is>
@@ -3699,48 +3625,48 @@
       </c>
       <c r="Y15" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
       <c r="Z15" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA15" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB15" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC15" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD15" s="1" t="inlineStr">
-        <is>
           <t>16510</t>
         </is>
       </c>
-      <c r="AE15" s="1" t="inlineStr"/>
+      <c r="AD15" s="1" t="inlineStr"/>
+      <c r="AE15" s="1" t="inlineStr">
+        <is>
+          <t>Бортовой</t>
+        </is>
+      </c>
       <c r="AF15" s="1" t="inlineStr">
         <is>
-          <t>Бортовой</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG15" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH15" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>380000</t>
         </is>
       </c>
       <c r="AI15" s="1" t="inlineStr">
@@ -3750,16 +3676,10 @@
       </c>
       <c r="AJ15" s="1" t="inlineStr">
         <is>
-          <t>380000</t>
-        </is>
-      </c>
-      <c r="AK15" s="1" t="inlineStr"/>
-      <c r="AL15" s="1" t="inlineStr">
-        <is>
           <t>gls-1</t>
         </is>
       </c>
-      <c r="AM15" s="1" t="inlineStr">
+      <c r="AK15" s="1" t="inlineStr">
         <is>
           <t>8181970113</t>
         </is>
@@ -3918,67 +3838,61 @@
       </c>
       <c r="Y16" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
       <c r="Z16" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA16" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB16" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC16" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD16" s="1" t="inlineStr">
-        <is>
           <t>12750</t>
         </is>
       </c>
-      <c r="AE16" s="1" t="inlineStr"/>
+      <c r="AD16" s="1" t="inlineStr"/>
+      <c r="AE16" s="1" t="inlineStr">
+        <is>
+          <t>Контейнеровоз</t>
+        </is>
+      </c>
       <c r="AF16" s="1" t="inlineStr">
         <is>
-          <t>Контейнеровоз</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG16" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH16" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>285000</t>
         </is>
       </c>
       <c r="AI16" s="1" t="inlineStr">
         <is>
-          <t>285000</t>
+          <t>142500</t>
         </is>
       </c>
       <c r="AJ16" s="1" t="inlineStr">
         <is>
-          <t>142500</t>
-        </is>
-      </c>
-      <c r="AK16" s="1" t="inlineStr"/>
-      <c r="AL16" s="1" t="inlineStr">
-        <is>
           <t>gls-11</t>
         </is>
       </c>
-      <c r="AM16" s="1" t="inlineStr">
+      <c r="AK16" s="1" t="inlineStr">
         <is>
           <t>8182391576</t>
         </is>
@@ -4137,67 +4051,61 @@
       </c>
       <c r="Y17" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
       <c r="Z17" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA17" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB17" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC17" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD17" s="1" t="inlineStr">
-        <is>
           <t>12192</t>
         </is>
       </c>
-      <c r="AE17" s="1" t="inlineStr"/>
+      <c r="AD17" s="1" t="inlineStr"/>
+      <c r="AE17" s="1" t="inlineStr">
+        <is>
+          <t>Контейнеровоз</t>
+        </is>
+      </c>
       <c r="AF17" s="1" t="inlineStr">
         <is>
-          <t>Контейнеровоз</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG17" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH17" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="AI17" s="1" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>162500</t>
         </is>
       </c>
       <c r="AJ17" s="1" t="inlineStr">
         <is>
-          <t>162500</t>
-        </is>
-      </c>
-      <c r="AK17" s="1" t="inlineStr"/>
-      <c r="AL17" s="1" t="inlineStr">
-        <is>
           <t>gls-12</t>
         </is>
       </c>
-      <c r="AM17" s="1" t="inlineStr">
+      <c r="AK17" s="1" t="inlineStr">
         <is>
           <t>8182793830</t>
         </is>
@@ -4368,48 +4276,48 @@
       </c>
       <c r="Y18" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
       <c r="Z18" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA18" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB18" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC18" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD18" s="1" t="inlineStr">
-        <is>
           <t>13600</t>
         </is>
       </c>
-      <c r="AE18" s="1" t="inlineStr"/>
+      <c r="AD18" s="1" t="inlineStr"/>
+      <c r="AE18" s="1" t="inlineStr">
+        <is>
+          <t>Шторно-бортовой</t>
+        </is>
+      </c>
       <c r="AF18" s="1" t="inlineStr">
         <is>
-          <t>Шторно-бортовой</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG18" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH18" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>380000</t>
         </is>
       </c>
       <c r="AI18" s="1" t="inlineStr">
@@ -4419,16 +4327,10 @@
       </c>
       <c r="AJ18" s="1" t="inlineStr">
         <is>
-          <t>380000</t>
+          <t>bk-tonar-t3-13-9888</t>
         </is>
       </c>
       <c r="AK18" s="1" t="inlineStr"/>
-      <c r="AL18" s="1" t="inlineStr">
-        <is>
-          <t>bk-tonar-t3-13-9888</t>
-        </is>
-      </c>
-      <c r="AM18" s="1" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -4589,63 +4491,57 @@
       </c>
       <c r="Y19" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
       <c r="Z19" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA19" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB19" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC19" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD19" s="1" t="inlineStr">
-        <is>
           <t>10450</t>
         </is>
       </c>
-      <c r="AE19" s="1" t="inlineStr"/>
+      <c r="AD19" s="1" t="inlineStr"/>
+      <c r="AE19" s="1" t="inlineStr">
+        <is>
+          <t>Самосвальный</t>
+        </is>
+      </c>
       <c r="AF19" s="1" t="inlineStr">
         <is>
-          <t>Самосвальный</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG19" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH19" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AI19" s="1" t="inlineStr">
-        <is>
           <t>420000</t>
         </is>
       </c>
-      <c r="AJ19" s="1" t="inlineStr"/>
-      <c r="AK19" s="1" t="inlineStr"/>
-      <c r="AL19" s="1" t="inlineStr">
+      <c r="AI19" s="1" t="inlineStr"/>
+      <c r="AJ19" s="1" t="inlineStr">
         <is>
           <t>gls-3</t>
         </is>
       </c>
-      <c r="AM19" s="1" t="inlineStr">
+      <c r="AK19" s="1" t="inlineStr">
         <is>
           <t>8182263799</t>
         </is>
@@ -4816,67 +4712,61 @@
       </c>
       <c r="Y20" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
       <c r="Z20" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA20" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB20" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC20" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="AD20" s="1" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE20" s="1" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>Самосвальный</t>
         </is>
       </c>
       <c r="AF20" s="1" t="inlineStr">
         <is>
-          <t>Самосвальный</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG20" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH20" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AI20" s="1" t="inlineStr">
-        <is>
           <t>420000</t>
         </is>
       </c>
-      <c r="AJ20" s="1" t="inlineStr"/>
-      <c r="AK20" s="1" t="inlineStr"/>
-      <c r="AL20" s="1" t="inlineStr">
+      <c r="AI20" s="1" t="inlineStr"/>
+      <c r="AJ20" s="1" t="inlineStr">
         <is>
           <t>gls-4</t>
         </is>
       </c>
-      <c r="AM20" s="1" t="inlineStr">
+      <c r="AK20" s="1" t="inlineStr">
         <is>
           <t>8182603324</t>
         </is>
@@ -5039,67 +4929,61 @@
       </c>
       <c r="Y21" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
       <c r="Z21" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA21" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB21" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC21" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>14134</t>
         </is>
       </c>
       <c r="AD21" s="1" t="inlineStr">
         <is>
-          <t>14134</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE21" s="1" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>Ломовоз</t>
         </is>
       </c>
       <c r="AF21" s="1" t="inlineStr">
         <is>
-          <t>Ломовоз</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG21" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH21" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AI21" s="1" t="inlineStr">
-        <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="AJ21" s="1" t="inlineStr"/>
-      <c r="AK21" s="1" t="inlineStr"/>
-      <c r="AL21" s="1" t="inlineStr">
+      <c r="AI21" s="1" t="inlineStr"/>
+      <c r="AJ21" s="1" t="inlineStr">
         <is>
           <t>gls-5</t>
         </is>
       </c>
-      <c r="AM21" s="1" t="inlineStr">
+      <c r="AK21" s="1" t="inlineStr">
         <is>
           <t>8182296576</t>
         </is>
@@ -5258,67 +5142,61 @@
       </c>
       <c r="Y22" s="1" t="inlineStr">
         <is>
-          <t>3 года или больше</t>
+          <t>Москва, Ижорская ул., 15/16с6</t>
         </is>
       </c>
       <c r="Z22" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA22" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB22" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC22" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD22" s="1" t="inlineStr">
-        <is>
           <t>12192</t>
         </is>
       </c>
-      <c r="AE22" s="1" t="inlineStr"/>
+      <c r="AD22" s="1" t="inlineStr"/>
+      <c r="AE22" s="1" t="inlineStr">
+        <is>
+          <t>Контейнеровоз</t>
+        </is>
+      </c>
       <c r="AF22" s="1" t="inlineStr">
         <is>
-          <t>Контейнеровоз</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG22" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH22" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="AI22" s="1" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="AJ22" s="1" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>bk-tonar-k4-u-99891</t>
         </is>
       </c>
       <c r="AK22" s="1" t="inlineStr"/>
-      <c r="AL22" s="1" t="inlineStr">
-        <is>
-          <t>bk-tonar-k4-u-99891</t>
-        </is>
-      </c>
-      <c r="AM22" s="1" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -5464,46 +5342,50 @@
           <t>B3-16 (98881)</t>
         </is>
       </c>
-      <c r="Y23" s="1" t="inlineStr"/>
+      <c r="Y23" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
       <c r="Z23" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA23" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB23" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC23" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD23" s="1" t="inlineStr">
-        <is>
           <t>16500</t>
         </is>
       </c>
-      <c r="AE23" s="1" t="inlineStr"/>
+      <c r="AD23" s="1" t="inlineStr"/>
+      <c r="AE23" s="1" t="inlineStr">
+        <is>
+          <t>Бортовой</t>
+        </is>
+      </c>
       <c r="AF23" s="1" t="inlineStr">
         <is>
-          <t>Бортовой</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG23" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH23" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>330000</t>
         </is>
       </c>
       <c r="AI23" s="1" t="inlineStr">
@@ -5513,16 +5395,10 @@
       </c>
       <c r="AJ23" s="1" t="inlineStr">
         <is>
-          <t>330000</t>
+          <t>bk-tonar-b3-16-98881</t>
         </is>
       </c>
       <c r="AK23" s="1" t="inlineStr"/>
-      <c r="AL23" s="1" t="inlineStr">
-        <is>
-          <t>bk-tonar-b3-16-98881</t>
-        </is>
-      </c>
-      <c r="AM23" s="1" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -5681,65 +5557,63 @@
           <t>SH3-33 (95892)</t>
         </is>
       </c>
-      <c r="Y24" s="1" t="inlineStr"/>
+      <c r="Y24" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
       <c r="Z24" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA24" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB24" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC24" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>10965</t>
         </is>
       </c>
       <c r="AD24" s="1" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE24" s="1" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>Самосвальный</t>
         </is>
       </c>
       <c r="AF24" s="1" t="inlineStr">
         <is>
-          <t>Самосвальный</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG24" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH24" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AI24" s="1" t="inlineStr">
-        <is>
           <t>390000</t>
         </is>
       </c>
-      <c r="AJ24" s="1" t="inlineStr"/>
-      <c r="AK24" s="1" t="inlineStr"/>
-      <c r="AL24" s="1" t="inlineStr">
+      <c r="AI24" s="1" t="inlineStr"/>
+      <c r="AJ24" s="1" t="inlineStr">
         <is>
           <t>novaia_11</t>
         </is>
       </c>
-      <c r="AM24" s="1" t="inlineStr">
+      <c r="AK24" s="1" t="inlineStr">
         <is>
           <t>7382709126</t>
         </is>
@@ -5900,65 +5774,63 @@
           <t>SH4-38 (95234)</t>
         </is>
       </c>
-      <c r="Y25" s="1" t="inlineStr"/>
+      <c r="Y25" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
       <c r="Z25" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA25" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB25" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC25" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>11996</t>
         </is>
       </c>
       <c r="AD25" s="1" t="inlineStr">
         <is>
-          <t>11996</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE25" s="1" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>Самосвальный</t>
         </is>
       </c>
       <c r="AF25" s="1" t="inlineStr">
         <is>
-          <t>Самосвальный</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG25" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH25" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AI25" s="1" t="inlineStr">
-        <is>
           <t>470000</t>
         </is>
       </c>
-      <c r="AJ25" s="1" t="inlineStr"/>
-      <c r="AK25" s="1" t="inlineStr"/>
-      <c r="AL25" s="1" t="inlineStr">
+      <c r="AI25" s="1" t="inlineStr"/>
+      <c r="AJ25" s="1" t="inlineStr">
         <is>
           <t>novaia_13</t>
         </is>
       </c>
-      <c r="AM25" s="1" t="inlineStr">
+      <c r="AK25" s="1" t="inlineStr">
         <is>
           <t>7382542432</t>
         </is>
@@ -6120,65 +5992,63 @@
           <t>SH4-45 (95234)</t>
         </is>
       </c>
-      <c r="Y26" s="1" t="inlineStr"/>
+      <c r="Y26" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
       <c r="Z26" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA26" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB26" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC26" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>11996</t>
         </is>
       </c>
       <c r="AD26" s="1" t="inlineStr">
         <is>
-          <t>11996</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE26" s="1" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>Самосвальный</t>
         </is>
       </c>
       <c r="AF26" s="1" t="inlineStr">
         <is>
-          <t>Самосвальный</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG26" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH26" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AI26" s="1" t="inlineStr">
-        <is>
           <t>480000</t>
         </is>
       </c>
-      <c r="AJ26" s="1" t="inlineStr"/>
-      <c r="AK26" s="1" t="inlineStr"/>
-      <c r="AL26" s="1" t="inlineStr">
+      <c r="AI26" s="1" t="inlineStr"/>
+      <c r="AJ26" s="1" t="inlineStr">
         <is>
           <t>novaia_14</t>
         </is>
       </c>
-      <c r="AM26" s="1" t="inlineStr">
+      <c r="AK26" s="1" t="inlineStr">
         <is>
           <t>7382525203</t>
         </is>
@@ -6336,65 +6206,63 @@
           <t>SH4-60M/SH4-60 (952342)</t>
         </is>
       </c>
-      <c r="Y27" s="1" t="inlineStr"/>
+      <c r="Y27" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
       <c r="Z27" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA27" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB27" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC27" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="AD27" s="1" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE27" s="1" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>Самосвальный</t>
         </is>
       </c>
       <c r="AF27" s="1" t="inlineStr">
         <is>
-          <t>Самосвальный</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG27" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH27" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AI27" s="1" t="inlineStr">
-        <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="AJ27" s="1" t="inlineStr"/>
-      <c r="AK27" s="1" t="inlineStr"/>
-      <c r="AL27" s="1" t="inlineStr">
+      <c r="AI27" s="1" t="inlineStr"/>
+      <c r="AJ27" s="1" t="inlineStr">
         <is>
           <t>novaia_15</t>
         </is>
       </c>
-      <c r="AM27" s="1" t="inlineStr">
+      <c r="AK27" s="1" t="inlineStr">
         <is>
           <t>7382161564</t>
         </is>
@@ -6551,65 +6419,63 @@
           <t>SH3-74M (97464)</t>
         </is>
       </c>
-      <c r="Y28" s="1" t="inlineStr"/>
+      <c r="Y28" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
       <c r="Z28" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA28" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB28" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC28" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>13865</t>
         </is>
       </c>
       <c r="AD28" s="1" t="inlineStr">
         <is>
-          <t>13865</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AE28" s="1" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>Ломовоз</t>
         </is>
       </c>
       <c r="AF28" s="1" t="inlineStr">
         <is>
-          <t>Ломовоз</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG28" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH28" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AI28" s="1" t="inlineStr">
-        <is>
           <t>470000</t>
         </is>
       </c>
-      <c r="AJ28" s="1" t="inlineStr"/>
+      <c r="AI28" s="1" t="inlineStr"/>
+      <c r="AJ28" s="1" t="inlineStr">
+        <is>
+          <t>bk-tonar-sh3-74m-97464</t>
+        </is>
+      </c>
       <c r="AK28" s="1" t="inlineStr"/>
-      <c r="AL28" s="1" t="inlineStr">
-        <is>
-          <t>bk-tonar-sh3-74m-97464</t>
-        </is>
-      </c>
-      <c r="AM28" s="1" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -6768,69 +6634,63 @@
           <t>SH3-33 (95892)</t>
         </is>
       </c>
-      <c r="Y29" s="1" t="inlineStr"/>
+      <c r="Y29" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
       <c r="Z29" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA29" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB29" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC29" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>10965</t>
         </is>
       </c>
       <c r="AD29" s="1" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE29" s="1" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>Самосвальный</t>
         </is>
       </c>
       <c r="AF29" s="1" t="inlineStr">
         <is>
-          <t>Самосвальный</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG29" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH29" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AI29" s="1" t="inlineStr">
-        <is>
           <t>390000</t>
         </is>
       </c>
-      <c r="AJ29" s="1" t="inlineStr"/>
+      <c r="AI29" s="1" t="inlineStr"/>
+      <c r="AJ29" s="1" t="inlineStr">
+        <is>
+          <t>novaia_19</t>
+        </is>
+      </c>
       <c r="AK29" s="1" t="inlineStr">
-        <is>
-          <t>Без ограничения по пробегу</t>
-        </is>
-      </c>
-      <c r="AL29" s="1" t="inlineStr">
-        <is>
-          <t>novaia_19</t>
-        </is>
-      </c>
-      <c r="AM29" s="1" t="inlineStr">
         <is>
           <t>7382810433</t>
         </is>
@@ -6983,65 +6843,63 @@
           <t>K3-20 (99883)</t>
         </is>
       </c>
-      <c r="Y30" s="1" t="inlineStr"/>
+      <c r="Y30" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
       <c r="Z30" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA30" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB30" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC30" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD30" s="1" t="inlineStr">
-        <is>
           <t>9076</t>
         </is>
       </c>
-      <c r="AE30" s="1" t="inlineStr"/>
+      <c r="AD30" s="1" t="inlineStr"/>
+      <c r="AE30" s="1" t="inlineStr">
+        <is>
+          <t>Контейнеровоз</t>
+        </is>
+      </c>
       <c r="AF30" s="1" t="inlineStr">
         <is>
-          <t>Контейнеровоз</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG30" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH30" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>225000</t>
         </is>
       </c>
       <c r="AI30" s="1" t="inlineStr">
         <is>
-          <t>225000</t>
+          <t>112500</t>
         </is>
       </c>
       <c r="AJ30" s="1" t="inlineStr">
         <is>
-          <t>112500</t>
+          <t>bk-tonar-k3-20-99883</t>
         </is>
       </c>
       <c r="AK30" s="1" t="inlineStr"/>
-      <c r="AL30" s="1" t="inlineStr">
-        <is>
-          <t>bk-tonar-k3-20-99883</t>
-        </is>
-      </c>
-      <c r="AM30" s="1" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -7191,65 +7049,63 @@
           <t>K4-20 (9988)</t>
         </is>
       </c>
-      <c r="Y31" s="1" t="inlineStr"/>
+      <c r="Y31" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
       <c r="Z31" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA31" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB31" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC31" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD31" s="1" t="inlineStr">
-        <is>
           <t>9485</t>
         </is>
       </c>
-      <c r="AE31" s="1" t="inlineStr"/>
+      <c r="AD31" s="1" t="inlineStr"/>
+      <c r="AE31" s="1" t="inlineStr">
+        <is>
+          <t>Контейнеровоз</t>
+        </is>
+      </c>
       <c r="AF31" s="1" t="inlineStr">
         <is>
-          <t>Контейнеровоз</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG31" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH31" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>295000</t>
         </is>
       </c>
       <c r="AI31" s="1" t="inlineStr">
         <is>
-          <t>295000</t>
+          <t>147500</t>
         </is>
       </c>
       <c r="AJ31" s="1" t="inlineStr">
         <is>
-          <t>147500</t>
+          <t>bk-tonar-k4-20-9988</t>
         </is>
       </c>
       <c r="AK31" s="1" t="inlineStr"/>
-      <c r="AL31" s="1" t="inlineStr">
-        <is>
-          <t>bk-tonar-k4-20-9988</t>
-        </is>
-      </c>
-      <c r="AM31" s="1" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -7399,65 +7255,63 @@
           <t>K3-40 (99881)</t>
         </is>
       </c>
-      <c r="Y32" s="1" t="inlineStr"/>
+      <c r="Y32" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
       <c r="Z32" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA32" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB32" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC32" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD32" s="1" t="inlineStr">
-        <is>
           <t>12580</t>
         </is>
       </c>
-      <c r="AE32" s="1" t="inlineStr"/>
+      <c r="AD32" s="1" t="inlineStr"/>
+      <c r="AE32" s="1" t="inlineStr">
+        <is>
+          <t>Контейнеровоз</t>
+        </is>
+      </c>
       <c r="AF32" s="1" t="inlineStr">
         <is>
-          <t>Контейнеровоз</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG32" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH32" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>225000</t>
         </is>
       </c>
       <c r="AI32" s="1" t="inlineStr">
         <is>
-          <t>225000</t>
+          <t>112500</t>
         </is>
       </c>
       <c r="AJ32" s="1" t="inlineStr">
         <is>
-          <t>112500</t>
-        </is>
-      </c>
-      <c r="AK32" s="1" t="inlineStr"/>
-      <c r="AL32" s="1" t="inlineStr">
-        <is>
           <t>novaia_27</t>
         </is>
       </c>
-      <c r="AM32" s="1" t="inlineStr">
+      <c r="AK32" s="1" t="inlineStr">
         <is>
           <t>7382919322</t>
         </is>
@@ -7610,65 +7464,63 @@
           <t>K4-40 (99893)</t>
         </is>
       </c>
-      <c r="Y33" s="1" t="inlineStr"/>
+      <c r="Y33" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
       <c r="Z33" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA33" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB33" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC33" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD33" s="1" t="inlineStr">
-        <is>
           <t>12750</t>
         </is>
       </c>
-      <c r="AE33" s="1" t="inlineStr"/>
+      <c r="AD33" s="1" t="inlineStr"/>
+      <c r="AE33" s="1" t="inlineStr">
+        <is>
+          <t>Контейнеровоз</t>
+        </is>
+      </c>
       <c r="AF33" s="1" t="inlineStr">
         <is>
-          <t>Контейнеровоз</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG33" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH33" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>285000</t>
         </is>
       </c>
       <c r="AI33" s="1" t="inlineStr">
         <is>
-          <t>285000</t>
+          <t>142500</t>
         </is>
       </c>
       <c r="AJ33" s="1" t="inlineStr">
         <is>
-          <t>142500</t>
-        </is>
-      </c>
-      <c r="AK33" s="1" t="inlineStr"/>
-      <c r="AL33" s="1" t="inlineStr">
-        <is>
           <t>novaia_28</t>
         </is>
       </c>
-      <c r="AM33" s="1" t="inlineStr">
+      <c r="AK33" s="1" t="inlineStr">
         <is>
           <t>7382880639</t>
         </is>
@@ -7831,65 +7683,63 @@
           <t>R3-13T (97861)</t>
         </is>
       </c>
-      <c r="Y34" s="1" t="inlineStr"/>
+      <c r="Y34" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
       <c r="Z34" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA34" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB34" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC34" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>14186</t>
         </is>
       </c>
       <c r="AD34" s="1" t="inlineStr">
         <is>
-          <t>14186</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE34" s="1" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>Тушевоз</t>
         </is>
       </c>
       <c r="AF34" s="1" t="inlineStr">
         <is>
-          <t>Тушевоз</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG34" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH34" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AI34" s="1" t="inlineStr">
-        <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="AJ34" s="1" t="inlineStr"/>
-      <c r="AK34" s="1" t="inlineStr"/>
-      <c r="AL34" s="1" t="inlineStr">
+      <c r="AI34" s="1" t="inlineStr"/>
+      <c r="AJ34" s="1" t="inlineStr">
         <is>
           <t>novaia_31</t>
         </is>
       </c>
-      <c r="AM34" s="1" t="inlineStr">
+      <c r="AK34" s="1" t="inlineStr">
         <is>
           <t>7382972002</t>
         </is>
@@ -8052,65 +7902,63 @@
           <t>R3-14 (97863)</t>
         </is>
       </c>
-      <c r="Y35" s="1" t="inlineStr"/>
+      <c r="Y35" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
       <c r="Z35" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA35" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB35" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC35" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>14610</t>
         </is>
       </c>
       <c r="AD35" s="1" t="inlineStr">
         <is>
-          <t>14610</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AE35" s="1" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>Изотермический</t>
         </is>
       </c>
       <c r="AF35" s="1" t="inlineStr">
         <is>
-          <t>Изотермический</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG35" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH35" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AI35" s="1" t="inlineStr">
-        <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="AJ35" s="1" t="inlineStr"/>
-      <c r="AK35" s="1" t="inlineStr"/>
-      <c r="AL35" s="1" t="inlineStr">
+      <c r="AI35" s="1" t="inlineStr"/>
+      <c r="AJ35" s="1" t="inlineStr">
         <is>
           <t>novaia_32</t>
         </is>
       </c>
-      <c r="AM35" s="1" t="inlineStr">
+      <c r="AK35" s="1" t="inlineStr">
         <is>
           <t>7382391396</t>
         </is>
@@ -8273,61 +8121,59 @@
           <t>R3-13D (97861)</t>
         </is>
       </c>
-      <c r="Y36" s="1" t="inlineStr"/>
+      <c r="Y36" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
       <c r="Z36" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA36" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB36" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC36" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD36" s="1" t="inlineStr">
-        <is>
           <t>13500</t>
         </is>
       </c>
-      <c r="AE36" s="1" t="inlineStr"/>
+      <c r="AD36" s="1" t="inlineStr"/>
+      <c r="AE36" s="1" t="inlineStr">
+        <is>
+          <t>Изотермический</t>
+        </is>
+      </c>
       <c r="AF36" s="1" t="inlineStr">
         <is>
-          <t>Изотермический</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG36" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH36" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AI36" s="1" t="inlineStr">
-        <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="AJ36" s="1" t="inlineStr"/>
-      <c r="AK36" s="1" t="inlineStr"/>
-      <c r="AL36" s="1" t="inlineStr">
+      <c r="AI36" s="1" t="inlineStr"/>
+      <c r="AJ36" s="1" t="inlineStr">
         <is>
           <t>novaia_33</t>
         </is>
       </c>
-      <c r="AM36" s="1" t="inlineStr">
+      <c r="AK36" s="1" t="inlineStr">
         <is>
           <t>7382937122</t>
         </is>
@@ -8485,46 +8331,50 @@
           <t>B4-13V (97883)</t>
         </is>
       </c>
-      <c r="Y37" s="1" t="inlineStr"/>
+      <c r="Y37" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
       <c r="Z37" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA37" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB37" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC37" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="AD37" s="1" t="inlineStr">
-        <is>
           <t>13690</t>
         </is>
       </c>
-      <c r="AE37" s="1" t="inlineStr"/>
+      <c r="AD37" s="1" t="inlineStr"/>
+      <c r="AE37" s="1" t="inlineStr">
+        <is>
+          <t>Бортовой</t>
+        </is>
+      </c>
       <c r="AF37" s="1" t="inlineStr">
         <is>
-          <t>Бортовой</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG37" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH37" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="AI37" s="1" t="inlineStr">
@@ -8534,16 +8384,10 @@
       </c>
       <c r="AJ37" s="1" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>bk-tonar-b4-13v-97883</t>
         </is>
       </c>
       <c r="AK37" s="1" t="inlineStr"/>
-      <c r="AL37" s="1" t="inlineStr">
-        <is>
-          <t>bk-tonar-b4-13v-97883</t>
-        </is>
-      </c>
-      <c r="AM37" s="1" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -8705,50 +8549,54 @@
           <t>T4-13V (97883)</t>
         </is>
       </c>
-      <c r="Y38" s="1" t="inlineStr"/>
+      <c r="Y38" s="1" t="inlineStr">
+        <is>
+          <t>Москва, Ижорская ул., 15/16с6</t>
+        </is>
+      </c>
       <c r="Z38" s="1" t="inlineStr">
         <is>
-          <t>Москва, Ижорская ул., 15/16с6</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="AA38" s="1" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Пневматическая</t>
         </is>
       </c>
       <c r="AB38" s="1" t="inlineStr">
         <is>
-          <t>Пневматическая</t>
+          <t>В наличии</t>
         </is>
       </c>
       <c r="AC38" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>13600</t>
         </is>
       </c>
       <c r="AD38" s="1" t="inlineStr">
         <is>
-          <t>13600</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AE38" s="1" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>Шторно-бортовой</t>
         </is>
       </c>
       <c r="AF38" s="1" t="inlineStr">
         <is>
-          <t>Шторно-бортовой</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="AG38" s="1" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AH38" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>425000</t>
         </is>
       </c>
       <c r="AI38" s="1" t="inlineStr">
@@ -8758,16 +8606,10 @@
       </c>
       <c r="AJ38" s="1" t="inlineStr">
         <is>
-          <t>425000</t>
-        </is>
-      </c>
-      <c r="AK38" s="1" t="inlineStr"/>
-      <c r="AL38" s="1" t="inlineStr">
-        <is>
           <t>novaia_8</t>
         </is>
       </c>
-      <c r="AM38" s="1" t="inlineStr">
+      <c r="AK38" s="1" t="inlineStr">
         <is>
           <t>7382726366</t>
         </is>

--- a/avito-feed-main/fleet-main.xlsx
+++ b/avito-feed-main/fleet-main.xlsx
@@ -623,7 +623,7 @@
       <c r="D2" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар B3-13 (9888) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Борт:&lt;/strong&gt; Алюминий
 - &lt;strong&gt;Длина (внутренние размеры), мм:&lt;/strong&gt; 13 625
@@ -645,8 +645,8 @@
 - &lt;strong&gt;Пол:&lt;/strong&gt; настил из ламинированной фанеры толщиной 27 мм
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
@@ -830,7 +830,7 @@
       <c r="D3" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар 9599 / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Тип техники:&lt;/strong&gt; самосвальный полуприцеп-зерновоз
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 4 (1-я и 2-я оси подъемные)
@@ -864,8 +864,8 @@
 - &lt;strong&gt;Комбинированный задний борт:&lt;/strong&gt; откидной и распашной с разгрузочными лючками
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
@@ -1049,7 +1049,7 @@
       <c r="D4" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар R3-13 / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 3
 - &lt;strong&gt;Кузов:&lt;/strong&gt; сложная сэндвич-панель, с алюминиевым полом, образующий с боковой отбортовкой герметичную ванну
@@ -1087,8 +1087,8 @@
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
@@ -1268,7 +1268,7 @@
       <c r="D5" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар T3-16 (98881) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 3
 - &lt;strong&gt;Кузов:&lt;/strong&gt; со сдвижной крышей и сдвижными боковинами; с элементами крепления груза
@@ -1307,8 +1307,8 @@
 - &lt;strong&gt;Задняя стенка:&lt;/strong&gt; оборудована распашной двустворчатой алюминиевой дверью; на каждой двери по 2 запорных устройства
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
@@ -1496,7 +1496,7 @@
       <c r="D6" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар L3 (9445) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 3, 1-я подъемная
 - &lt;strong&gt;Кузов:&lt;/strong&gt; коники разборные
@@ -1528,8 +1528,8 @@
 - &lt;strong&gt;Коники:&lt;/strong&gt; разборные
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
@@ -1717,7 +1717,7 @@
       <c r="D7" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар T4-16V / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Борта:&lt;/strong&gt; Алюминий
 - &lt;strong&gt;Длина (внутренние размеры), мм:&lt;/strong&gt; 16500
@@ -1741,8 +1741,8 @@
 - &lt;strong&gt;Пол:&lt;/strong&gt; настил из ламинированной фанеры толщиной 27 мм
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
@@ -1988,7 +1988,7 @@
 — Кредитные программы
 — Индивидуальный подбор комплектации
 — Помощь с оформлением и приобретением техники
-📌 Важно: комплектация, наличие и итоговая стоимость полуприцепа могут меняться. Уточняйте актуальные условия перед покупкой.
+📌 Важно: комплектация и итоговая стоимость полуприцепа могут меняться. Уточняйте актуальные условия перед покупкой.
 📞 Напишите или позвоните — расскажем подробнее про ИнтерПрицеп 853371, подберем объем кузова и комплектацию под ваши задачи, рассчитаем стоимость и варианты приобретения.</t>
         </is>
       </c>
@@ -2161,7 +2161,7 @@
       <c r="D9" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар 95941 / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 3, 1-я подъемная
 - &lt;strong&gt;Кузов:&lt;/strong&gt; алюминиевый прямоугольный кузов; комбинированный задний борт (откидной и распашной) дополнительно оснащен разгрузочными лючками
@@ -2203,8 +2203,8 @@
 - &lt;strong&gt;Минимальный объём масляного бака тягача, л:&lt;/strong&gt; 150
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
@@ -2384,7 +2384,7 @@
       <c r="D10" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар R3-13  / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 3
 - &lt;strong&gt;Кузов:&lt;/strong&gt; сложная сэндвич-панель, с алюминиевым полом, образующий с боковой отбортовкой герметичную ванну.
@@ -2420,10 +2420,10 @@
 - &lt;strong&gt;Пол:&lt;/strong&gt; герметичный; выполнен из сложной сэндвич-панели повышенной прочности; покрытие пола – противоскользящий настил из рифленого алюминия
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 - &lt;strong&gt;Крыша:&lt;/strong&gt; сэндвич-панели; 6 потолочных светодиодных фонарей внутреннего освещения обеспечивают высокую яркость и низкое энергопотребление
-• &lt;strong&gt;Наличие&lt;/strong&gt;: 
+• &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -2607,7 +2607,7 @@
       <c r="D11" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар 95941 / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 4, 1-я подъемная
 - &lt;strong&gt;Кузов:&lt;/strong&gt; прямоугольным кузов, комбинированный задний борт (откидной и распашной) дополнительно оснащен разгрузочными лючками; с возможностью боковой разгрузки
@@ -2645,8 +2645,8 @@
 - &lt;strong&gt;Минимальный объём масляного бака тягача, л:&lt;/strong&gt; 150
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
@@ -2884,7 +2884,7 @@
 — Кредитные программы
 — Индивидуальный подбор комплектации
 — Помощь с оформлением и приобретением техники
-📌 Важно: наличие, комплектация и итоговая стоимость могут меняться. Перед покупкой уточните актуальные условия у менеджера.
+📌 Важно: комплектация и итоговая стоимость могут меняться. Перед покупкой уточните актуальные условия у менеджера.
 📞 Напишите или позвоните — расскажем подробнее про самосвальный полуприцеп ИнтерПрицеп 853372, подберем объем кузова и комплектацию под ваши задачи, рассчитаем стоимость и варианты приобретения.</t>
         </is>
       </c>
@@ -3108,7 +3108,7 @@
 — Кредитные программы
 — Индивидуальный подбор комплектации
 — Помощь с оформлением и приобретением техники
-📌 Важно: наличие, комплектация и итоговая стоимость могут меняться. Перед покупкой уточните актуальные условия у менеджера.
+📌 Важно: комплектация и итоговая стоимость могут меняться. Перед покупкой уточните актуальные условия у менеджера.
 📞 Напишите или позвоните — расскажем подробнее про контейнеровоз ИнтерПрицеп 853375, подберем исполнение под ваши задачи, рассчитаем стоимость, лизинг или кредитную программу.</t>
         </is>
       </c>
@@ -3277,7 +3277,7 @@
       <c r="D14" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар SP3-17 (85792) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Кузов:&lt;/strong&gt; с задней разгрузкой
 - &lt;strong&gt;Объем:&lt;/strong&gt; 16,7 куб.м / 22,8 куб.м (с надставными бортами)
@@ -3305,8 +3305,8 @@
 - &lt;strong&gt;Диаметр сцепной петли, мм:&lt;/strong&gt; 50, 57 (под беззазорное сцепное устройство)
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
@@ -3486,7 +3486,7 @@
       <c r="D15" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар B4-16V (97882) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Борт:&lt;/strong&gt; алюминий
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 4, 1-я и 2-я подъемные
@@ -3519,8 +3519,8 @@
 - &lt;strong&gt;Пол:&lt;/strong&gt; настил из ламинированной фанеры толщиной 27 мм
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
@@ -3704,7 +3704,7 @@
       <c r="D16" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар K3-U (99882) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 3, 1-я подъемная
 - &lt;strong&gt;Подвеска:&lt;/strong&gt; рычажного типа
@@ -3732,8 +3732,8 @@
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
@@ -3917,7 +3917,7 @@
       <c r="D17" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар K4-U (99894) ДОПОГ / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 4, 1-я и 2-я подъемные
 - &lt;strong&gt;Подвеска:&lt;/strong&gt; рычажного типа
@@ -3945,8 +3945,8 @@
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
@@ -4130,7 +4130,7 @@
       <c r="D18" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар T3-13 (9888) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 3
 - &lt;strong&gt;Кузов:&lt;/strong&gt; со сдвижной крышей и сдвижными боковинами; с элементами крепления груза
@@ -4170,8 +4170,8 @@
 - Перевозка грузов массой до 31 000 килограммов
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
@@ -4351,7 +4351,7 @@
       <c r="D19" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар SL4-34G (9595) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 4
 - &lt;strong&gt;Кузов:&lt;/strong&gt; полукруглый кузов, выполнен из высокопрочных и износостойких сталей
@@ -4385,8 +4385,8 @@
 - &lt;strong&gt;Угол подъёма кузова, град:&lt;/strong&gt; 46
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
@@ -4566,7 +4566,7 @@
       <c r="D20" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар 9595 / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 4
 - &lt;strong&gt;Кузов:&lt;/strong&gt; полукруглый кузов, выполнен из высокопрочных сталей
@@ -4606,8 +4606,8 @@
 - &lt;strong&gt;Минимальный объем масляного бака тягача, л:&lt;/strong&gt; 150
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
@@ -4791,7 +4791,7 @@
       <c r="D21" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар SH4-74M (97465) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 4
 - &lt;strong&gt;Кузов:&lt;/strong&gt; с распашными воротами, для перевозки металлолома
@@ -4823,8 +4823,8 @@
 - &lt;strong&gt;Объём кузова, куб.м:&lt;/strong&gt; 74
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
@@ -5008,7 +5008,7 @@
       <c r="D22" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар K4-U (99891) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 4, 1-я и 2-я подъемные
 - &lt;strong&gt;Подвеска:&lt;/strong&gt; рычажного типа
@@ -5036,8 +5036,8 @@
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
@@ -5217,7 +5217,7 @@
       <c r="D23" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар B3-16 (98881) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Тип техники:&lt;/strong&gt; бортовой полуприцеп
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 3 (1-я ось подъемная)
@@ -5242,8 +5242,8 @@
 - &lt;strong&gt;Дополнительные опции:&lt;/strong&gt; коники (12 шт.) с ящиком для хранения
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
@@ -5419,7 +5419,7 @@
       <c r="D24" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар SH3-33 (95892) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 3, 1-я подъемная
 - &lt;strong&gt;Кузов:&lt;/strong&gt; изготовлен из высокопрочных и устойчивых к износу сталей, обеспечивает защиту поверхности от абразивного изнашивания
@@ -5457,8 +5457,8 @@
 - &lt;strong&gt;Рабочее давление в системе, bar:&lt;/strong&gt; 160
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
@@ -5638,7 +5638,7 @@
       <c r="D25" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар SH4-38 (95234) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 4
 - &lt;strong&gt;Объем:&lt;/strong&gt; 38 куб.м
@@ -5674,8 +5674,8 @@
 - &lt;strong&gt;Рабочее давление в системе, bar:&lt;/strong&gt; 160
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
@@ -5855,7 +5855,7 @@
       <c r="D26" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар SH4-45 (95234) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 4
 - &lt;strong&gt;Кузов:&lt;/strong&gt; цельнометаллический, оснащен задним откидным бортом
@@ -5892,8 +5892,8 @@
 - &lt;strong&gt;Рабочее давление в системе, bar:&lt;/strong&gt; 160
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
@@ -6073,7 +6073,7 @@
       <c r="D27" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар SH4-60M/SH4-60 (952342) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 4
 - &lt;strong&gt;Кузов:&lt;/strong&gt; с распашными воротами, для перевозки металлолома
@@ -6106,8 +6106,8 @@
 - &lt;strong&gt;Угол подъема кузова, град:&lt;/strong&gt; 48
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
@@ -6287,7 +6287,7 @@
       <c r="D28" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар SH3-74M (97464) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 3
 - &lt;strong&gt;Кузов:&lt;/strong&gt; с распашными воротами, для перевозки металлолома
@@ -6319,8 +6319,8 @@
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
@@ -6496,7 +6496,7 @@
       <c r="D29" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар SH3-33G (95892) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 3, 1-я подъемная
 - &lt;strong&gt;Кузов:&lt;/strong&gt; изготовлен из высокопрочных и устойчивых к износу сталей, обеспечивает защиту поверхности от абразивного изнашивания
@@ -6534,8 +6534,8 @@
 - &lt;strong&gt;Рабочее давление в системе, bar:&lt;/strong&gt; 160
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
@@ -6715,7 +6715,7 @@
       <c r="D30" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар K3-20 (99883) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 3, 1-я подъемная
 - &lt;strong&gt;Подвеска:&lt;/strong&gt; рычажного типа
@@ -6743,8 +6743,8 @@
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
@@ -6920,7 +6920,7 @@
       <c r="D31" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Прицепы Тонар K4-20 (9988) ДОПОГ / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 4, 1-я и 2-я подъемные
 - &lt;strong&gt;Подвеска:&lt;/strong&gt; рычажного типа
@@ -6947,10 +6947,10 @@
 &lt;strong&gt;ОСТАЛЬНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Типы перевозимых контейнеров:&lt;/strong&gt; 20', 20* Танк. ДОПОГ АТ, FL, EX/II 
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
-• &lt;strong&gt;Наличие&lt;/strong&gt;: 
+• &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
@@ -7126,7 +7126,7 @@
       <c r="D32" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар K3-40 (99881) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - ДОПОГ
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 3, 1-я подъемная
@@ -7155,8 +7155,8 @@
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
@@ -7336,7 +7336,7 @@
       <c r="D33" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар K4-40 (99893) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 4, 1-я подъемная
 - &lt;strong&gt;Подвеска:&lt;/strong&gt; рычажного типа
@@ -7364,8 +7364,8 @@
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
@@ -7545,7 +7545,7 @@
       <c r="D34" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар R3-13T (97861) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 3
 - &lt;strong&gt;Кузов:&lt;/strong&gt; сложная сэндвич-панель, с алюминиевым полом, образующий с боковой отбортовкой герметичную ванну
@@ -7583,8 +7583,8 @@
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
@@ -7764,7 +7764,7 @@
       <c r="D35" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар R3-14 (97863) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 3
 - &lt;strong&gt;Кузов:&lt;/strong&gt; сложная сэндвич-панель, с алюминиевым полом, образующий с боковой отбортовкой герметичную ванну
@@ -7802,8 +7802,8 @@
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
@@ -7983,7 +7983,7 @@
       <c r="D36" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар R3-13D (97861) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 3
 - &lt;strong&gt;Кузов:&lt;/strong&gt; сложная сэндвич-панель, с алюминиевым полом, образующий с боковой отбортовкой герметичную ванну; с двухъярусной загрузкой
@@ -8021,8 +8021,8 @@
 - &lt;strong&gt;Опорное устройство:&lt;/strong&gt; на 24 т
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
@@ -8198,7 +8198,7 @@
       <c r="D37" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар B4-13V (97883) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Борт:&lt;/strong&gt; алюминий
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 4, 1-я и 2-я подъемные
@@ -8231,8 +8231,8 @@
 - &lt;strong&gt;Передний борт:&lt;/strong&gt; металлический, съемный
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
@@ -8408,7 +8408,7 @@
       <c r="D38" s="1" t="inlineStr">
         <is>
           <t>&lt;strong&gt;Полуприцеп Тонар T4-13V (97883) / 2026 года выпуска&lt;/strong&gt;
-&lt;strong&gt;В наличии и под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
+&lt;strong&gt;Под заказ&lt;/strong&gt; — седельные тягачи, грузовики, самосвалы, контейнеровозы, бортовые и самосвальные полуприцепы, щеповозы и другая техника.
 &lt;strong&gt;🚚 ОСНОВНЫЕ ХАРАКТЕРИСТИКИ:&lt;/strong&gt;
 - &lt;strong&gt;Количество осей:&lt;/strong&gt; 4
 - &lt;strong&gt;Кузов:&lt;/strong&gt; со сдвижной крышей и сдвижными боковинами; с элементами крепления груза
@@ -8449,8 +8449,8 @@
 - предназначен для перевозки грузов массой до 27 000 килограммов
 • &lt;strong&gt;Наличие&lt;/strong&gt;: Под заказ
 &lt;strong&gt;💼 Условия покупки&lt;/strong&gt;: работаем с юридическими и физическими лицами, поможем с подбором, оформлением и доставкой техники по России.
-&lt;strong&gt;📌 Важно&lt;/strong&gt;: наличие, комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
-&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по наличию, комплектации и срокам поставки.</t>
+&lt;strong&gt;📌 Важно&lt;/strong&gt;: комплектация и финальная стоимость могут меняться. Перед приездом уточните актуальные условия у менеджера.
+&lt;strong&gt;📞 Напишите или позвоните&lt;/strong&gt; — подскажем по комплектации и срокам поставки.</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">

--- a/avito-feed-main/fleet-main.xlsx
+++ b/avito-feed-main/fleet-main.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Объявления" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объявления" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/12.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/13.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/14.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/09.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/01.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/04.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/05.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/06.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/07.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/08.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/10.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/11.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/12.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/13.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/ad-57373/14.jpg</t>
         </is>
       </c>
       <c r="H10" s="1" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-4/01.png | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-4/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-4/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-4/04.jpg</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-4/02.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-4/01.png | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-4/03.jpg | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-main/photos/gls-4/04.jpg</t>
         </is>
       </c>
       <c r="H20" s="1" t="inlineStr">

--- a/avito-feed-main/fleet-main.xlsx
+++ b/avito-feed-main/fleet-main.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объявления" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Объявления" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="U4" s="1" t="inlineStr">
         <is>
-          <t>Москва и Московская область | Белгородская область | Брянская область | Владимирская область | Воронежская область | Ивановская область | Калужская область | Костромская область | Курская область | Липецкая область | Орловская область | Рязанская область | Смоленская область | Тамбовская область | Тверская область | Тульская область | Ярославская область | Адыгея | Калмыкия | Крым | Краснодарский край | Астраханская область | Волгоградская область | Ростовская область</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Иркутская область | Калининградская область | Калмыкия | Калужская область | Камчатский край | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V4" s="1" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="U6" s="1" t="inlineStr">
         <is>
-          <t>Москва и Московская область | Белгородская область | Брянская область | Владимирская область | Воронежская область | Ивановская область | Калужская область | Костромская область | Курская область | Липецкая область | Орловская область | Рязанская область | Смоленская область | Тамбовская область | Тверская область | Тульская область | Ярославская область | Санкт-Петербург и Ленинградская область | Архангельская область | Вологодская область | Калининградская область | Мурманская область | Ненецкий АО | Новгородская область | Псковская область | Карелия | Коми | Башкортостан | Марий Эл | Мордовия | Татарстан | Удмуртия | Чувашия | Кировская область | Нижегородская область | Оренбургская область | Пензенская область | Пермский край | Самарская область | Саратовская область | Ульяновская область</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Иркутская область | Калининградская область | Калмыкия | Калужская область | Камчатский край | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V6" s="1" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="U7" s="1" t="inlineStr">
         <is>
-          <t>Москва и Московская область | Белгородская область | Брянская область | Владимирская область | Воронежская область | Ивановская область | Калужская область | Костромская область | Курская область | Липецкая область | Орловская область | Рязанская область | Смоленская область | Тамбовская область | Тверская область | Тульская область | Ярославская область | Башкортостан | Марий Эл | Мордовия | Татарстан | Удмуртия | Чувашия | Кировская область | Нижегородская область | Оренбургская область | Пензенская область | Пермский край | Самарская область | Саратовская область | Ульяновская область</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Иркутская область | Калининградская область | Калмыкия | Калужская область | Камчатский край | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V7" s="1" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="U9" s="1" t="inlineStr">
         <is>
-          <t>Москва и Московская область | Белгородская область | Брянская область | Владимирская область | Воронежская область | Ивановская область | Калужская область | Костромская область | Курская область | Липецкая область | Орловская область | Рязанская область | Смоленская область | Тамбовская область | Тверская область | Тульская область | Ярославская область | Башкортостан | Марий Эл | Мордовия | Татарстан | Удмуртия | Чувашия | Кировская область | Нижегородская область | Оренбургская область | Пензенская область | Пермский край | Самарская область | Саратовская область | Ульяновская область | Адыгея | Калмыкия | Крым | Краснодарский край | Астраханская область | Волгоградская область | Ростовская область</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Иркутская область | Калининградская область | Калмыкия | Калужская область | Камчатский край | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V9" s="1" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="U10" s="1" t="inlineStr">
         <is>
-          <t>Москва и Московская область | Белгородская область | Брянская область | Владимирская область | Воронежская область | Ивановская область | Калужская область | Костромская область | Курская область | Липецкая область | Орловская область | Рязанская область | Смоленская область | Тамбовская область | Тверская область | Тульская область | Ярославская область | Адыгея | Калмыкия | Крым | Краснодарский край | Астраханская область | Волгоградская область | Ростовская область</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Иркутская область | Калининградская область | Калмыкия | Калужская область | Камчатский край | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V10" s="1" t="inlineStr">
@@ -3280,7 +3280,7 @@
       <c r="T13" s="1" t="inlineStr"/>
       <c r="U13" s="1" t="inlineStr">
         <is>
-          <t>Москва и Московская область | Белгородская область | Брянская область | Владимирская область | Воронежская область | Ивановская область | Калужская область | Костромская область | Курская область | Липецкая область | Орловская область | Рязанская область | Смоленская область | Тамбовская область | Тверская область | Тульская область | Ярославская область | Санкт-Петербург и Ленинградская область | Архангельская область | Вологодская область | Калининградская область | Мурманская область | Ненецкий АО | Новгородская область | Псковская область | Карелия | Коми | Адыгея | Калмыкия | Крым | Краснодарский край | Астраханская область | Волгоградская область | Ростовская область</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Иркутская область | Калининградская область | Калмыкия | Калужская область | Камчатский край | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V13" s="1" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="U15" s="1" t="inlineStr">
         <is>
-          <t>Москва и Московская область | Белгородская область | Брянская область | Владимирская область | Воронежская область | Ивановская область | Калужская область | Костромская область | Курская область | Липецкая область | Орловская область | Рязанская область | Смоленская область | Тамбовская область | Тверская область | Тульская область | Ярославская область | Санкт-Петербург и Ленинградская область | Архангельская область | Вологодская область | Калининградская область | Мурманская область | Ненецкий АО | Новгородская область | Псковская область | Карелия | Коми | Башкортостан | Марий Эл | Мордовия | Татарстан | Удмуртия | Чувашия | Кировская область | Нижегородская область | Оренбургская область | Пензенская область | Пермский край | Самарская область | Саратовская область | Ульяновская область | Адыгея | Калмыкия | Крым | Краснодарский край | Астраханская область | Волгоградская область | Ростовская область</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Иркутская область | Калининградская область | Калмыкия | Калужская область | Камчатский край | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V15" s="1" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="U16" s="1" t="inlineStr">
         <is>
-          <t>Москва и Московская область | Белгородская область | Брянская область | Владимирская область | Воронежская область | Ивановская область | Калужская область | Костромская область | Курская область | Липецкая область | Орловская область | Рязанская область | Смоленская область | Тамбовская область | Тверская область | Тульская область | Ярославская область | Санкт-Петербург и Ленинградская область | Архангельская область | Вологодская область | Калининградская область | Мурманская область | Ненецкий АО | Новгородская область | Псковская область | Карелия | Коми | Адыгея | Калмыкия | Крым | Краснодарский край | Астраханская область | Волгоградская область | Ростовская область</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Иркутская область | Калининградская область | Калмыкия | Калужская область | Камчатский край | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V16" s="1" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="U19" s="1" t="inlineStr">
         <is>
-          <t>Москва и Московская область | Белгородская область | Брянская область | Владимирская область | Воронежская область | Ивановская область | Калужская область | Костромская область | Курская область | Липецкая область | Орловская область | Рязанская область | Смоленская область | Тамбовская область | Тверская область | Тульская область | Ярославская область</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Иркутская область | Калининградская область | Калмыкия | Калужская область | Камчатский край | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V19" s="1" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="U23" s="1" t="inlineStr">
         <is>
-          <t>Москва и Московская область | Белгородская область | Брянская область | Владимирская область | Воронежская область | Ивановская область | Калужская область | Костромская область | Курская область | Липецкая область | Орловская область | Рязанская область | Смоленская область | Тамбовская область | Тверская область | Тульская область | Ярославская область | Санкт-Петербург и Ленинградская область | Архангельская область | Вологодская область | Калининградская область | Мурманская область | Ненецкий АО | Новгородская область | Псковская область | Карелия | Коми | Башкортостан | Марий Эл | Мордовия | Татарстан | Удмуртия | Чувашия | Кировская область | Нижегородская область | Оренбургская область | Пензенская область | Пермский край | Самарская область | Саратовская область | Ульяновская область | Адыгея | Калмыкия | Крым | Краснодарский край | Астраханская область | Волгоградская область | Ростовская область</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Иркутская область | Калининградская область | Калмыкия | Калужская область | Камчатский край | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V23" s="1" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="U25" s="1" t="inlineStr">
         <is>
-          <t>Москва и Московская область | Белгородская область | Брянская область | Владимирская область | Воронежская область | Ивановская область | Калужская область | Костромская область | Курская область | Липецкая область | Орловская область | Рязанская область | Смоленская область | Тамбовская область | Тверская область | Тульская область | Ярославская область</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Иркутская область | Калининградская область | Калмыкия | Калужская область | Камчатский край | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V25" s="1" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="U26" s="1" t="inlineStr">
         <is>
-          <t>Москва и Московская область | Белгородская область | Брянская область | Владимирская область | Воронежская область | Ивановская область | Калужская область | Костромская область | Курская область | Липецкая область | Орловская область | Рязанская область | Смоленская область | Тамбовская область | Тверская область | Тульская область | Ярославская область</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Иркутская область | Калининградская область | Калмыкия | Калужская область | Камчатский край | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V26" s="1" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="U27" s="1" t="inlineStr">
         <is>
-          <t>Москва и Московская область | Белгородская область | Брянская область | Владимирская область | Воронежская область | Ивановская область | Калужская область | Костромская область | Курская область | Липецкая область | Орловская область | Рязанская область | Смоленская область | Тамбовская область | Тверская область | Тульская область | Ярославская область</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Иркутская область | Калининградская область | Калмыкия | Калужская область | Камчатский край | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V27" s="1" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="U28" s="1" t="inlineStr">
         <is>
-          <t>Москва и Московская область | Белгородская область | Брянская область | Владимирская область | Воронежская область | Ивановская область | Калужская область | Костромская область | Курская область | Липецкая область | Орловская область | Рязанская область | Смоленская область | Тамбовская область | Тверская область | Тульская область | Ярославская область | Башкортостан | Марий Эл | Мордовия | Татарстан | Удмуртия | Чувашия | Кировская область | Нижегородская область | Оренбургская область | Пензенская область | Пермский край | Самарская область | Саратовская область | Ульяновская область</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Иркутская область | Калининградская область | Калмыкия | Калужская область | Камчатский край | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V28" s="1" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="U30" s="1" t="inlineStr">
         <is>
-          <t>Москва и Московская область | Белгородская область | Брянская область | Владимирская область | Воронежская область | Ивановская область | Калужская область | Костромская область | Курская область | Липецкая область | Орловская область | Рязанская область | Смоленская область | Тамбовская область | Тверская область | Тульская область | Ярославская область | Санкт-Петербург и Ленинградская область | Архангельская область | Вологодская область | Калининградская область | Мурманская область | Ненецкий АО | Новгородская область | Псковская область | Карелия | Коми | Адыгея | Калмыкия | Крым | Краснодарский край | Астраханская область | Волгоградская область | Ростовская область</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Иркутская область | Калининградская область | Калмыкия | Калужская область | Камчатский край | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V30" s="1" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="U33" s="1" t="inlineStr">
         <is>
-          <t>Москва и Московская область | Белгородская область | Брянская область | Владимирская область | Воронежская область | Ивановская область | Калужская область | Костромская область | Курская область | Липецкая область | Орловская область | Рязанская область | Смоленская область | Тамбовская область | Тверская область | Тульская область | Ярославская область | Санкт-Петербург и Ленинградская область | Архангельская область | Вологодская область | Калининградская область | Мурманская область | Ненецкий АО | Новгородская область | Псковская область | Карелия | Коми | Адыгея | Калмыкия | Крым | Краснодарский край | Астраханская область | Волгоградская область | Ростовская область</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Иркутская область | Калининградская область | Калмыкия | Калужская область | Камчатский край | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V33" s="1" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="U38" s="1" t="inlineStr">
         <is>
-          <t>Москва и Московская область | Белгородская область | Брянская область | Владимирская область | Воронежская область | Ивановская область | Калужская область | Костромская область | Курская область | Липецкая область | Орловская область | Рязанская область | Смоленская область | Тамбовская область | Тверская область | Тульская область | Ярославская область | Башкортостан | Марий Эл | Мордовия | Татарстан | Удмуртия | Чувашия | Кировская область | Нижегородская область | Оренбургская область | Пензенская область | Пермский край | Самарская область | Саратовская область | Ульяновская область</t>
+          <t>Москва и Московская область | Санкт-Петербург и Ленинградская область | Крым | Алтайский край | Амурская область | Архангельская область | Астраханская область | Белгородская область | Брянская область | Бурятия | Владимирская область | Волгоградская область | Вологодская область | Воронежская область | Еврейская АО | Ивановская область | Иркутская область | Калининградская область | Калмыкия | Калужская область | Камчатский край | Кемеровская область | Кировская область | Костромская область | Краснодарский край | Красноярский край | Курганская область | Курская область | Липецкая область | Магаданская область | Мурманская область | Ненецкий АО | Нижегородская область | Новгородская область | Новосибирская область | Омская область | Оренбургская область | Орловская область | Пензенская область | Пермский край | Приморский край | Псковская область | Адыгея | Башкортостан | Карелия | Коми | Марий Эл | Мордовия | Саха (Якутия) | Татарстан | Тыва | Хакасия | Ростовская область | Рязанская область | Самарская область | Саратовская область | Сахалинская область | Свердловская область | Смоленская область | Тамбовская область | Тверская область | Томская область | Тульская область | Тюменская область | Удмуртия | Ульяновская область | Хабаровский край | Ханты-Мансийский АО | Челябинская область | Забайкальский край | Чувашия | Чукотский АО | Ямало-Ненецкий АО | Ярославская область | Республика Алтай</t>
         </is>
       </c>
       <c r="V38" s="1" t="inlineStr">
